--- a/inputs/House Model Data.xlsx
+++ b/inputs/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/house_model_python/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19A25A19-C367-B74A-8F0A-ADFFB14E2735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{2FF1B396-FA7C-E34C-84EA-535747473A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -2951,15 +2951,16 @@
         <v>694</v>
       </c>
       <c r="E2" s="3">
-        <v>-55.1</v>
+        <f>31.2-67.5</f>
+        <v>-36.299999999999997</v>
       </c>
       <c r="F2" s="3">
-        <f>24.2-74.5</f>
-        <v>-50.3</v>
+        <f>34.4-64.6</f>
+        <v>-30.199999999999996</v>
       </c>
       <c r="G2" s="3">
         <f t="shared" ref="G2:G65" si="0">E2+6.9+1.5</f>
-        <v>-46.7</v>
+        <v>-27.9</v>
       </c>
       <c r="K2" t="s">
         <v>674</v>
@@ -2988,15 +2989,16 @@
         <v>695</v>
       </c>
       <c r="E3" s="3">
-        <v>8.1999999999999993</v>
+        <f>40.8-58.1</f>
+        <v>-17.300000000000004</v>
       </c>
       <c r="F3" s="3">
-        <f>55.6-43.2</f>
-        <v>12.399999999999999</v>
+        <f>43.5-55.3</f>
+        <v>-11.799999999999997</v>
       </c>
       <c r="G3" s="3">
         <f t="shared" si="0"/>
-        <v>16.600000000000001</v>
+        <v>-8.9000000000000039</v>
       </c>
       <c r="K3" t="s">
         <v>674</v>
@@ -3025,15 +3027,16 @@
         <v>694</v>
       </c>
       <c r="E4" s="3">
-        <v>-46.5</v>
+        <f>26.5-72.4</f>
+        <v>-45.900000000000006</v>
       </c>
       <c r="F4" s="3">
-        <f>28.9-69.8</f>
-        <v>-40.9</v>
+        <f>29.3-69.4</f>
+        <v>-40.100000000000009</v>
       </c>
       <c r="G4" s="3">
         <f t="shared" si="0"/>
-        <v>-38.1</v>
+        <v>-37.500000000000007</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>11</v>
@@ -3068,15 +3071,16 @@
         <v>694</v>
       </c>
       <c r="E5" s="3">
-        <v>-67.099999999999994</v>
+        <f>15.6-83.4</f>
+        <v>-67.800000000000011</v>
       </c>
       <c r="F5" s="3">
-        <f>18.4-80.4</f>
-        <v>-62.000000000000007</v>
+        <f>17.6-81.3</f>
+        <v>-63.699999999999996</v>
       </c>
       <c r="G5" s="3">
         <f t="shared" si="0"/>
-        <v>-58.699999999999996</v>
+        <v>-59.400000000000013</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>13</v>
@@ -3111,15 +3115,16 @@
         <v>694</v>
       </c>
       <c r="E6" s="3">
-        <v>-29.8</v>
+        <f>34.6-63.6</f>
+        <v>-29</v>
       </c>
       <c r="F6" s="3">
-        <f>35.5-62.5</f>
-        <v>-27</v>
+        <f>35.4-62.5</f>
+        <v>-27.1</v>
       </c>
       <c r="G6" s="3">
         <f t="shared" si="0"/>
-        <v>-21.4</v>
+        <v>-20.6</v>
       </c>
       <c r="K6" t="s">
         <v>674</v>
@@ -3148,15 +3153,16 @@
         <v>694</v>
       </c>
       <c r="E7" s="3">
-        <v>-38.799999999999997</v>
+        <f>31.6-66.6</f>
+        <v>-34.999999999999993</v>
       </c>
       <c r="F7" s="3">
-        <f>30.2-68.2</f>
-        <v>-38</v>
+        <f>31.8-66.4</f>
+        <v>-34.600000000000009</v>
       </c>
       <c r="G7" s="3">
         <f t="shared" si="0"/>
-        <v>-30.4</v>
+        <v>-26.599999999999994</v>
       </c>
       <c r="I7" t="s">
         <v>14</v>
@@ -3188,15 +3194,16 @@
         <v>695</v>
       </c>
       <c r="E8" s="3">
-        <v>23.9</v>
+        <f>61.9-37.1</f>
+        <v>24.799999999999997</v>
       </c>
       <c r="F8" s="3">
-        <f>63.9-34.9</f>
-        <v>29</v>
+        <f>64.7-34.4</f>
+        <v>30.300000000000004</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="0"/>
-        <v>32.299999999999997</v>
+        <v>33.199999999999996</v>
       </c>
       <c r="K8" t="s">
         <v>674</v>

--- a/inputs/House Model Data.xlsx
+++ b/inputs/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/house_model_python/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{2FF1B396-FA7C-E34C-84EA-535747473A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{E4A5315F-EEDF-1E40-A9B3-AD4523402644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5195" uniqueCount="782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5197" uniqueCount="784">
   <si>
     <t>State</t>
   </si>
@@ -2420,6 +2420,12 @@
   </si>
   <si>
     <t>Burley, Brian</t>
+  </si>
+  <si>
+    <t>Meyers, Scott</t>
+  </si>
+  <si>
+    <t>Brignano, Houston</t>
   </si>
 </sst>
 </file>
@@ -5519,6 +5525,9 @@
       <c r="H52" t="s">
         <v>63</v>
       </c>
+      <c r="I52" s="4" t="s">
+        <v>782</v>
+      </c>
       <c r="K52" t="s">
         <v>667</v>
       </c>
@@ -5541,7 +5550,7 @@
         <v>699</v>
       </c>
       <c r="T52" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.2">
@@ -5841,6 +5850,9 @@
       <c r="H58" t="s">
         <v>69</v>
       </c>
+      <c r="I58" s="4" t="s">
+        <v>783</v>
+      </c>
       <c r="K58" t="s">
         <v>667</v>
       </c>
@@ -5863,7 +5875,7 @@
         <v>699</v>
       </c>
       <c r="T58" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.2">

--- a/inputs/House Model Data.xlsx
+++ b/inputs/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/house_model_python/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{E4A5315F-EEDF-1E40-A9B3-AD4523402644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A68012F0-C419-FA49-BF3D-ECE67F07A754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -74,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5197" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5225" uniqueCount="806">
   <si>
     <t>State</t>
   </si>
@@ -2426,6 +2425,72 @@
   </si>
   <si>
     <t>Brignano, Houston</t>
+  </si>
+  <si>
+    <t>Vang, Mai</t>
+  </si>
+  <si>
+    <t>Clyburn, James</t>
+  </si>
+  <si>
+    <t>Biggs, Sherri</t>
+  </si>
+  <si>
+    <t>McClain, Courtney</t>
+  </si>
+  <si>
+    <t>Climer, Wes</t>
+  </si>
+  <si>
+    <t>Vincent, John</t>
+  </si>
+  <si>
+    <t>Mota, Samantha</t>
+  </si>
+  <si>
+    <t>Duenas, Angelica</t>
+  </si>
+  <si>
+    <t>Pan, Richard</t>
+  </si>
+  <si>
+    <t>Fedorchuk, Julie</t>
+  </si>
+  <si>
+    <t>Peterson, John</t>
+  </si>
+  <si>
+    <t>Villegas, Randy</t>
+  </si>
+  <si>
+    <t>Kim, Young</t>
+  </si>
+  <si>
+    <t>R_vs_R</t>
+  </si>
+  <si>
+    <t>LePage, Paul</t>
+  </si>
+  <si>
+    <t>Ditmer, Mallory</t>
+  </si>
+  <si>
+    <t>Lehmacher, Eunice</t>
+  </si>
+  <si>
+    <t>Hosford, Steven</t>
+  </si>
+  <si>
+    <t>Whipple, Cody</t>
+  </si>
+  <si>
+    <t>Benitez-Thompson, Teresa</t>
+  </si>
+  <si>
+    <t>Buck, Carrie</t>
+  </si>
+  <si>
+    <t>O'Donnell, Marty</t>
   </si>
 </sst>
 </file>
@@ -4226,6 +4291,12 @@
         <f t="shared" si="0"/>
         <v>16.700000000000003</v>
       </c>
+      <c r="H28" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="I28" t="s">
+        <v>744</v>
+      </c>
       <c r="K28" t="s">
         <v>667</v>
       </c>
@@ -4278,6 +4349,9 @@
       <c r="H29" t="s">
         <v>40</v>
       </c>
+      <c r="J29" s="4" t="s">
+        <v>784</v>
+      </c>
       <c r="K29" t="s">
         <v>667</v>
       </c>
@@ -4300,7 +4374,7 @@
         <v>699</v>
       </c>
       <c r="T29" t="s">
-        <v>703</v>
+        <v>728</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.2">
@@ -5086,6 +5160,9 @@
         <f t="shared" si="0"/>
         <v>6.6000000000000005</v>
       </c>
+      <c r="H44" s="4" t="s">
+        <v>795</v>
+      </c>
       <c r="I44" t="s">
         <v>55</v>
       </c>
@@ -5111,7 +5188,7 @@
         <v>699</v>
       </c>
       <c r="T44" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.2">
@@ -5473,6 +5550,9 @@
       <c r="H51" t="s">
         <v>62</v>
       </c>
+      <c r="J51" s="4" t="s">
+        <v>791</v>
+      </c>
       <c r="K51" t="s">
         <v>667</v>
       </c>
@@ -5495,7 +5575,7 @@
         <v>699</v>
       </c>
       <c r="T51" t="s">
-        <v>703</v>
+        <v>728</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.2">
@@ -5905,6 +5985,9 @@
       <c r="H59" t="s">
         <v>70</v>
       </c>
+      <c r="J59" s="4" t="s">
+        <v>790</v>
+      </c>
       <c r="K59" t="s">
         <v>667</v>
       </c>
@@ -5927,7 +6010,7 @@
         <v>699</v>
       </c>
       <c r="T59" t="s">
-        <v>703</v>
+        <v>728</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.2">
@@ -6069,6 +6152,9 @@
       <c r="I62" s="6" t="s">
         <v>758</v>
       </c>
+      <c r="J62" t="s">
+        <v>796</v>
+      </c>
       <c r="K62" t="s">
         <v>667</v>
       </c>
@@ -6091,7 +6177,7 @@
         <v>699</v>
       </c>
       <c r="T62" t="s">
-        <v>703</v>
+        <v>797</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.2">
@@ -12264,6 +12350,9 @@
         <f t="shared" si="2"/>
         <v>30.200000000000003</v>
       </c>
+      <c r="H181" t="s">
+        <v>241</v>
+      </c>
       <c r="K181" t="s">
         <v>663</v>
       </c>
@@ -12313,6 +12402,9 @@
         <f t="shared" si="2"/>
         <v>-1.0999999999999996</v>
       </c>
+      <c r="I182" s="4" t="s">
+        <v>798</v>
+      </c>
       <c r="K182" t="s">
         <v>663</v>
       </c>
@@ -15115,6 +15207,12 @@
         <f t="shared" si="3"/>
         <v>10.7</v>
       </c>
+      <c r="H238" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="I238" s="4" t="s">
+        <v>804</v>
+      </c>
       <c r="K238" t="s">
         <v>666</v>
       </c>
@@ -15164,6 +15262,9 @@
         <f t="shared" si="3"/>
         <v>-5.6</v>
       </c>
+      <c r="H239" s="4" t="s">
+        <v>803</v>
+      </c>
       <c r="K239" t="s">
         <v>666</v>
       </c>
@@ -15213,6 +15314,12 @@
         <f t="shared" si="3"/>
         <v>7.7</v>
       </c>
+      <c r="H240" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="I240" s="4" t="s">
+        <v>805</v>
+      </c>
       <c r="K240" t="s">
         <v>666</v>
       </c>
@@ -15262,6 +15369,12 @@
         <f t="shared" si="3"/>
         <v>11.2</v>
       </c>
+      <c r="H241" t="s">
+        <v>801</v>
+      </c>
+      <c r="I241" s="4" t="s">
+        <v>802</v>
+      </c>
       <c r="K241" t="s">
         <v>666</v>
       </c>
@@ -18284,6 +18397,9 @@
         <f t="shared" si="4"/>
         <v>-28.4</v>
       </c>
+      <c r="I299" t="s">
+        <v>793</v>
+      </c>
       <c r="K299" t="s">
         <v>679</v>
       </c>
@@ -20797,6 +20913,7 @@
         <f t="shared" si="5"/>
         <v>-4.6999999999999993</v>
       </c>
+      <c r="H345" s="4"/>
       <c r="K345" t="s">
         <v>677</v>
       </c>
@@ -20846,6 +20963,9 @@
         <f t="shared" si="5"/>
         <v>-5.6</v>
       </c>
+      <c r="I346" t="s">
+        <v>467</v>
+      </c>
       <c r="K346" t="s">
         <v>677</v>
       </c>
@@ -20895,6 +21015,12 @@
         <f t="shared" si="5"/>
         <v>-34.6</v>
       </c>
+      <c r="H347" t="s">
+        <v>800</v>
+      </c>
+      <c r="I347" t="s">
+        <v>786</v>
+      </c>
       <c r="K347" t="s">
         <v>677</v>
       </c>
@@ -20944,6 +21070,12 @@
         <f t="shared" si="5"/>
         <v>-15.200000000000003</v>
       </c>
+      <c r="H348" s="4" t="s">
+        <v>787</v>
+      </c>
+      <c r="I348" t="s">
+        <v>469</v>
+      </c>
       <c r="K348" t="s">
         <v>677</v>
       </c>
@@ -20993,6 +21125,12 @@
         <f t="shared" si="5"/>
         <v>-14.4</v>
       </c>
+      <c r="H349" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="I349" s="4" t="s">
+        <v>788</v>
+      </c>
       <c r="K349" t="s">
         <v>677</v>
       </c>
@@ -21015,7 +21153,7 @@
         <v>700</v>
       </c>
       <c r="T349" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="350" spans="1:20" x14ac:dyDescent="0.2">
@@ -21042,6 +21180,12 @@
         <f t="shared" si="5"/>
         <v>31.200000000000003</v>
       </c>
+      <c r="H350" t="s">
+        <v>785</v>
+      </c>
+      <c r="I350" s="4" t="s">
+        <v>794</v>
+      </c>
       <c r="K350" t="s">
         <v>677</v>
       </c>
@@ -21090,6 +21234,12 @@
       <c r="G351" s="3">
         <f t="shared" si="5"/>
         <v>-18</v>
+      </c>
+      <c r="H351" s="4" t="s">
+        <v>789</v>
+      </c>
+      <c r="I351" t="s">
+        <v>472</v>
       </c>
       <c r="K351" t="s">
         <v>677</v>

--- a/inputs/House Model Data.xlsx
+++ b/inputs/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/house_model_python/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A68012F0-C419-FA49-BF3D-ECE67F07A754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F4F77E3-E186-8440-A97B-0A3A2B7B4F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5225" uniqueCount="806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5229" uniqueCount="810">
   <si>
     <t>State</t>
   </si>
@@ -2491,6 +2491,18 @@
   </si>
   <si>
     <t>O'Donnell, Marty</t>
+  </si>
+  <si>
+    <t>Flippo, David</t>
+  </si>
+  <si>
+    <t>Russell, Ronald</t>
+  </si>
+  <si>
+    <t>Gonzales-Torres, Angela</t>
+  </si>
+  <si>
+    <t>top_two_rcv</t>
   </si>
 </sst>
 </file>
@@ -2926,14 +2938,14 @@
     <col min="7" max="7" width="30.1640625" style="3" customWidth="1"/>
     <col min="8" max="8" width="23.33203125" customWidth="1"/>
     <col min="9" max="10" width="24.1640625" customWidth="1"/>
-    <col min="11" max="11" width="13.6640625" customWidth="1"/>
-    <col min="12" max="12" width="18.6640625" customWidth="1"/>
-    <col min="13" max="13" width="28" customWidth="1"/>
-    <col min="14" max="14" width="21" customWidth="1"/>
-    <col min="15" max="15" width="29.1640625" customWidth="1"/>
-    <col min="16" max="16" width="19.5" customWidth="1"/>
-    <col min="17" max="17" width="21.33203125" customWidth="1"/>
-    <col min="18" max="18" width="23.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="18.6640625" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="28" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="21" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="29.1640625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="19.5" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="21.33203125" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="23.83203125" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="16.1640625" customWidth="1"/>
     <col min="20" max="20" width="29.6640625" customWidth="1"/>
     <col min="21" max="21" width="22" customWidth="1"/>
@@ -4319,7 +4331,7 @@
         <v>699</v>
       </c>
       <c r="T28" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.2">
@@ -4968,7 +4980,7 @@
         <v>699</v>
       </c>
       <c r="T40" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.2">
@@ -5822,6 +5834,12 @@
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
+      <c r="H56" t="s">
+        <v>67</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>808</v>
+      </c>
       <c r="K56" t="s">
         <v>667</v>
       </c>
@@ -5844,7 +5862,7 @@
         <v>699</v>
       </c>
       <c r="T56" t="s">
-        <v>703</v>
+        <v>728</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.2">
@@ -6287,7 +6305,7 @@
         <v>699</v>
       </c>
       <c r="T64" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.2">
@@ -6395,7 +6413,7 @@
         <v>699</v>
       </c>
       <c r="T66" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.2">
@@ -6505,7 +6523,7 @@
         <v>699</v>
       </c>
       <c r="T68" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.2">
@@ -12353,6 +12371,9 @@
       <c r="H181" t="s">
         <v>241</v>
       </c>
+      <c r="I181" s="4" t="s">
+        <v>807</v>
+      </c>
       <c r="K181" t="s">
         <v>663</v>
       </c>
@@ -12372,10 +12393,10 @@
         <v>688</v>
       </c>
       <c r="S181" t="s">
-        <v>700</v>
+        <v>809</v>
       </c>
       <c r="T181" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="182" spans="1:20" x14ac:dyDescent="0.2">
@@ -12424,7 +12445,7 @@
         <v>688</v>
       </c>
       <c r="S182" t="s">
-        <v>700</v>
+        <v>809</v>
       </c>
       <c r="T182" t="s">
         <v>703</v>
@@ -15235,7 +15256,7 @@
         <v>700</v>
       </c>
       <c r="T238" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="239" spans="1:20" x14ac:dyDescent="0.2">
@@ -15265,6 +15286,9 @@
       <c r="H239" s="4" t="s">
         <v>803</v>
       </c>
+      <c r="I239" s="4" t="s">
+        <v>806</v>
+      </c>
       <c r="K239" t="s">
         <v>666</v>
       </c>
@@ -15287,7 +15311,7 @@
         <v>700</v>
       </c>
       <c r="T239" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="240" spans="1:20" x14ac:dyDescent="0.2">
@@ -15342,7 +15366,7 @@
         <v>700</v>
       </c>
       <c r="T240" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="241" spans="1:20" x14ac:dyDescent="0.2">
@@ -15397,7 +15421,7 @@
         <v>700</v>
       </c>
       <c r="T241" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="242" spans="1:20" x14ac:dyDescent="0.2">
@@ -15936,7 +15960,7 @@
         <v>700</v>
       </c>
       <c r="T251" t="s">
-        <v>703</v>
+        <v>771</v>
       </c>
     </row>
     <row r="252" spans="1:20" x14ac:dyDescent="0.2">
@@ -21043,7 +21067,7 @@
         <v>700</v>
       </c>
       <c r="T347" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="348" spans="1:20" x14ac:dyDescent="0.2">
@@ -21098,7 +21122,7 @@
         <v>700</v>
       </c>
       <c r="T348" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="349" spans="1:20" x14ac:dyDescent="0.2">
@@ -21208,7 +21232,7 @@
         <v>700</v>
       </c>
       <c r="T350" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="351" spans="1:20" x14ac:dyDescent="0.2">
@@ -21263,7 +21287,7 @@
         <v>700</v>
       </c>
       <c r="T351" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="352" spans="1:20" x14ac:dyDescent="0.2">

--- a/inputs/House Model Data.xlsx
+++ b/inputs/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/house_model_python/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F4F77E3-E186-8440-A97B-0A3A2B7B4F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C0E781-EE13-D24C-A32C-E2EA433F972D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5229" uniqueCount="810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5232" uniqueCount="813">
   <si>
     <t>State</t>
   </si>
@@ -2503,6 +2503,15 @@
   </si>
   <si>
     <t>top_two_rcv</t>
+  </si>
+  <si>
+    <t>Littau, Robert</t>
+  </si>
+  <si>
+    <t>Recile, Rudy</t>
+  </si>
+  <si>
+    <t>Bartie, Thurmond</t>
   </si>
 </sst>
 </file>
@@ -4091,6 +4100,9 @@
       <c r="H24" s="4" t="s">
         <v>37</v>
       </c>
+      <c r="I24" s="4" t="s">
+        <v>810</v>
+      </c>
       <c r="K24" t="s">
         <v>667</v>
       </c>
@@ -4113,7 +4125,7 @@
         <v>699</v>
       </c>
       <c r="T24" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.2">
@@ -4416,6 +4428,9 @@
       <c r="H30" t="s">
         <v>41</v>
       </c>
+      <c r="I30" s="4" t="s">
+        <v>811</v>
+      </c>
       <c r="K30" t="s">
         <v>667</v>
       </c>
@@ -4438,7 +4453,7 @@
         <v>699</v>
       </c>
       <c r="T30" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.2">
@@ -4711,7 +4726,7 @@
         <v>699</v>
       </c>
       <c r="T35" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.2">
@@ -22539,6 +22554,9 @@
       <c r="G375" s="3">
         <f t="shared" si="5"/>
         <v>-15.799999999999997</v>
+      </c>
+      <c r="H375" s="4" t="s">
+        <v>812</v>
       </c>
       <c r="I375" t="s">
         <v>513</v>

--- a/inputs/House Model Data.xlsx
+++ b/inputs/House Model Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/house_model_python/inputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/Desktop - Ben’s MacBook Air/house_model_python/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C0E781-EE13-D24C-A32C-E2EA433F972D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9F29D5-7359-3640-BA9E-CB071328F0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5232" uniqueCount="813">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5234" uniqueCount="813">
   <si>
     <t>State</t>
   </si>
@@ -21309,8 +21309,8 @@
       <c r="A352" t="s">
         <v>649</v>
       </c>
-      <c r="B352" s="5">
-        <v>1</v>
+      <c r="B352" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="C352" t="s">
         <v>473</v>
@@ -24123,8 +24123,8 @@
       <c r="A404" t="s">
         <v>653</v>
       </c>
-      <c r="B404">
-        <v>1</v>
+      <c r="B404" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="C404" t="s">
         <v>574</v>

--- a/inputs/House Model Data.xlsx
+++ b/inputs/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/Desktop - Ben’s MacBook Air/house_model_python/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9F29D5-7359-3640-BA9E-CB071328F0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAB5DC30-0C5D-914F-936B-C4393B01B63A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5234" uniqueCount="813">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5362" uniqueCount="898">
   <si>
     <t>State</t>
   </si>
@@ -2512,6 +2512,261 @@
   </si>
   <si>
     <t>Bartie, Thurmond</t>
+  </si>
+  <si>
+    <t>Nez, Jonathan</t>
+  </si>
+  <si>
+    <t>Jasser, Zuhdi</t>
+  </si>
+  <si>
+    <t>Mendoza, JoAnn</t>
+  </si>
+  <si>
+    <t>Butierez, Daniel</t>
+  </si>
+  <si>
+    <t>Hamadeh, Abraham</t>
+  </si>
+  <si>
+    <t>Sterbinsky, Danielle</t>
+  </si>
+  <si>
+    <t>Jones, Eric</t>
+  </si>
+  <si>
+    <t>Frese, Jeffrey</t>
+  </si>
+  <si>
+    <t>Hernandez, Melissa</t>
+  </si>
+  <si>
+    <t>Soule, Peter</t>
+  </si>
+  <si>
+    <t>Morales, Christian</t>
+  </si>
+  <si>
+    <t>Hollowell, Amanda</t>
+  </si>
+  <si>
+    <t>Kingston, James</t>
+  </si>
+  <si>
+    <t>Martin, Kevin</t>
+  </si>
+  <si>
+    <t>Kozycki, Tony</t>
+  </si>
+  <si>
+    <t>DeLancy, Pamela</t>
+  </si>
+  <si>
+    <t>Cowan, John</t>
+  </si>
+  <si>
+    <t>Smith, Ceretta</t>
+  </si>
+  <si>
+    <t>Dunlap, Matthew</t>
+  </si>
+  <si>
+    <t>Pino, Rosemary</t>
+  </si>
+  <si>
+    <t>Gallant, Christopher</t>
+  </si>
+  <si>
+    <t>Halpin, Patrick</t>
+  </si>
+  <si>
+    <t>LePetri, Michael</t>
+  </si>
+  <si>
+    <t>Driscoll, Jeanine</t>
+  </si>
+  <si>
+    <t>Marsh, George</t>
+  </si>
+  <si>
+    <t>Chou, Joseph</t>
+  </si>
+  <si>
+    <t>Valdez, Claire</t>
+  </si>
+  <si>
+    <t>Rivera, Mevlin</t>
+  </si>
+  <si>
+    <t>Mizrahi, Lewis</t>
+  </si>
+  <si>
+    <t>Anabilah-Azuman, Joel</t>
+  </si>
+  <si>
+    <t>Lander, Brad</t>
+  </si>
+  <si>
+    <t>Moore, Jennifer</t>
+  </si>
+  <si>
+    <t>DeCillis, Michael</t>
+  </si>
+  <si>
+    <t>Lasher, Micah</t>
+  </si>
+  <si>
+    <t>Shinkle, Caroline</t>
+  </si>
+  <si>
+    <t>Chavalier, Daraliza Avila</t>
+  </si>
+  <si>
+    <t>Williams, Manual</t>
+  </si>
+  <si>
+    <t>Hysanaj, Diamant</t>
+  </si>
+  <si>
+    <t>Sapaskis, Stylo</t>
+  </si>
+  <si>
+    <t>Cinquemani, Joseph</t>
+  </si>
+  <si>
+    <t>Conley, Cait</t>
+  </si>
+  <si>
+    <t>Auringer, Jackie</t>
+  </si>
+  <si>
+    <t>Oberacker, Peter</t>
+  </si>
+  <si>
+    <t>Ambrosio, Ralph</t>
+  </si>
+  <si>
+    <t>Gendebien, Blake</t>
+  </si>
+  <si>
+    <t>Constantino, Anthony</t>
+  </si>
+  <si>
+    <t>Buller, Kailee</t>
+  </si>
+  <si>
+    <t>Gies, Aaron</t>
+  </si>
+  <si>
+    <t>Ellman, Alissa</t>
+  </si>
+  <si>
+    <t>Morelle, Joseph</t>
+  </si>
+  <si>
+    <t>McIntyre, Virginia</t>
+  </si>
+  <si>
+    <t>Hannon, Dennis</t>
+  </si>
+  <si>
+    <t>Scwhartz, Dan</t>
+  </si>
+  <si>
+    <t>Boafo, Adrian</t>
+  </si>
+  <si>
+    <t>Wallace, Dave</t>
+  </si>
+  <si>
+    <t>Flowers, Bernard</t>
+  </si>
+  <si>
+    <t>McDermott, George</t>
+  </si>
+  <si>
+    <t>Chaffee, Chris</t>
+  </si>
+  <si>
+    <t>Ficker, Robin</t>
+  </si>
+  <si>
+    <t>Collier, Scott</t>
+  </si>
+  <si>
+    <t>Riley, Cheryl</t>
+  </si>
+  <si>
+    <t>Lacore, Nancy</t>
+  </si>
+  <si>
+    <t>Honeycutt, Jenny</t>
+  </si>
+  <si>
+    <t>Khalifa, Zyon</t>
+  </si>
+  <si>
+    <t>McAdams, Ben</t>
+  </si>
+  <si>
+    <t>Owen, Riley</t>
+  </si>
+  <si>
+    <t>Crosby, Peter</t>
+  </si>
+  <si>
+    <t>Udell, Kent</t>
+  </si>
+  <si>
+    <t>Larsen, Jonny</t>
+  </si>
+  <si>
+    <t>Feely, Jay</t>
+  </si>
+  <si>
+    <t>Lamb, Mike</t>
+  </si>
+  <si>
+    <t>Lee, Elizabeth</t>
+  </si>
+  <si>
+    <t>Greene-Placentia, Bernadette</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glenn, Nicholas </t>
+  </si>
+  <si>
+    <t>Kiros, Melat</t>
+  </si>
+  <si>
+    <t>Peterson, Christy</t>
+  </si>
+  <si>
+    <t>Dennison, Kelley</t>
+  </si>
+  <si>
+    <t>Romero, Dwayne</t>
+  </si>
+  <si>
+    <t>Laubaucher, Eileen</t>
+  </si>
+  <si>
+    <t>Killin, Jessica</t>
+  </si>
+  <si>
+    <t>Tewahade, Mel</t>
+  </si>
+  <si>
+    <t>Bennett, Timothy</t>
+  </si>
+  <si>
+    <t>Rutinel, Manny</t>
+  </si>
+  <si>
+    <t>Shah, Amish</t>
+  </si>
+  <si>
+    <t>Hammer, Trygve</t>
   </si>
 </sst>
 </file>
@@ -2945,7 +3200,7 @@
     <col min="3" max="4" width="29.83203125" customWidth="1"/>
     <col min="5" max="6" width="20.6640625" style="3" customWidth="1"/>
     <col min="7" max="7" width="30.1640625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="23.33203125" customWidth="1"/>
+    <col min="8" max="8" width="36.5" customWidth="1"/>
     <col min="9" max="10" width="24.1640625" customWidth="1"/>
     <col min="11" max="11" width="13.6640625" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="18.6640625" hidden="1" customWidth="1"/>
@@ -3380,6 +3635,12 @@
         <f t="shared" si="0"/>
         <v>5.3000000000000007</v>
       </c>
+      <c r="H10" s="4" t="s">
+        <v>896</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>882</v>
+      </c>
       <c r="K10" t="s">
         <v>675</v>
       </c>
@@ -3402,7 +3663,7 @@
         <v>700</v>
       </c>
       <c r="T10" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.2">
@@ -3429,6 +3690,12 @@
         <f t="shared" si="0"/>
         <v>-6.5</v>
       </c>
+      <c r="H11" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="I11" t="s">
+        <v>20</v>
+      </c>
       <c r="K11" t="s">
         <v>675</v>
       </c>
@@ -3451,7 +3718,7 @@
         <v>700</v>
       </c>
       <c r="T11" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
@@ -3478,6 +3745,12 @@
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
+      <c r="H12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>886</v>
+      </c>
       <c r="K12" t="s">
         <v>675</v>
       </c>
@@ -3500,7 +3773,7 @@
         <v>700</v>
       </c>
       <c r="T12" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.2">
@@ -3527,6 +3800,12 @@
         <f t="shared" si="0"/>
         <v>15.7</v>
       </c>
+      <c r="H13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>814</v>
+      </c>
       <c r="K13" t="s">
         <v>675</v>
       </c>
@@ -3549,7 +3828,7 @@
         <v>700</v>
       </c>
       <c r="T13" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
@@ -3576,6 +3855,12 @@
         <f t="shared" si="0"/>
         <v>-11.499999999999998</v>
       </c>
+      <c r="H14" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>883</v>
+      </c>
       <c r="K14" t="s">
         <v>675</v>
       </c>
@@ -3598,7 +3883,7 @@
         <v>700</v>
       </c>
       <c r="T14" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
@@ -3625,6 +3910,12 @@
         <f t="shared" si="0"/>
         <v>7.7</v>
       </c>
+      <c r="H15" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="I15" t="s">
+        <v>24</v>
+      </c>
       <c r="K15" t="s">
         <v>675</v>
       </c>
@@ -3647,7 +3938,7 @@
         <v>700</v>
       </c>
       <c r="T15" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
@@ -3674,6 +3965,12 @@
         <f t="shared" si="0"/>
         <v>30.5</v>
       </c>
+      <c r="H16" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>816</v>
+      </c>
       <c r="K16" t="s">
         <v>675</v>
       </c>
@@ -3696,7 +3993,7 @@
         <v>700</v>
       </c>
       <c r="T16" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.2">
@@ -3723,6 +4020,12 @@
         <f t="shared" si="0"/>
         <v>-7.9</v>
       </c>
+      <c r="H17" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="I17" t="s">
+        <v>817</v>
+      </c>
       <c r="K17" t="s">
         <v>675</v>
       </c>
@@ -3745,7 +4048,7 @@
         <v>700</v>
       </c>
       <c r="T17" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.2">
@@ -3772,6 +4075,12 @@
         <f t="shared" si="0"/>
         <v>-22.6</v>
       </c>
+      <c r="H18" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="I18" t="s">
+        <v>27</v>
+      </c>
       <c r="K18" t="s">
         <v>675</v>
       </c>
@@ -3794,7 +4103,7 @@
         <v>700</v>
       </c>
       <c r="T18" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.2">
@@ -4211,6 +4520,9 @@
       <c r="H26" s="6" t="s">
         <v>38</v>
       </c>
+      <c r="J26" s="4" t="s">
+        <v>819</v>
+      </c>
       <c r="K26" t="s">
         <v>667</v>
       </c>
@@ -4233,7 +4545,7 @@
         <v>699</v>
       </c>
       <c r="T26" t="s">
-        <v>703</v>
+        <v>728</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.2">
@@ -4539,6 +4851,9 @@
       <c r="H32" t="s">
         <v>43</v>
       </c>
+      <c r="I32" s="4" t="s">
+        <v>820</v>
+      </c>
       <c r="K32" t="s">
         <v>667</v>
       </c>
@@ -4561,7 +4876,7 @@
         <v>699</v>
       </c>
       <c r="T32" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.2">
@@ -4756,6 +5071,9 @@
       <c r="H36" s="4" t="s">
         <v>750</v>
       </c>
+      <c r="J36" s="4" t="s">
+        <v>821</v>
+      </c>
       <c r="K36" t="s">
         <v>667</v>
       </c>
@@ -4778,7 +5096,7 @@
         <v>699</v>
       </c>
       <c r="T36" t="s">
-        <v>703</v>
+        <v>728</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.2">
@@ -4863,6 +5181,9 @@
       <c r="H38" t="s">
         <v>49</v>
       </c>
+      <c r="I38" s="4" t="s">
+        <v>822</v>
+      </c>
       <c r="K38" t="s">
         <v>667</v>
       </c>
@@ -4885,7 +5206,7 @@
         <v>699</v>
       </c>
       <c r="T38" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.2">
@@ -6350,6 +6671,9 @@
       <c r="H65" t="s">
         <v>75</v>
       </c>
+      <c r="I65" s="4" t="s">
+        <v>823</v>
+      </c>
       <c r="K65" t="s">
         <v>667</v>
       </c>
@@ -6372,7 +6696,7 @@
         <v>699</v>
       </c>
       <c r="T65" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.2">
@@ -6896,6 +7220,12 @@
         <f t="shared" si="1"/>
         <v>64.3</v>
       </c>
+      <c r="H75" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="I75" s="4" t="s">
+        <v>888</v>
+      </c>
       <c r="K75" t="s">
         <v>666</v>
       </c>
@@ -6918,7 +7248,7 @@
         <v>700</v>
       </c>
       <c r="T75" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.2">
@@ -6945,6 +7275,12 @@
         <f t="shared" si="1"/>
         <v>48.199999999999996</v>
       </c>
+      <c r="H76" t="s">
+        <v>86</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>889</v>
+      </c>
       <c r="K76" t="s">
         <v>666</v>
       </c>
@@ -6967,7 +7303,7 @@
         <v>700</v>
       </c>
       <c r="T76" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.2">
@@ -6994,6 +7330,12 @@
         <f t="shared" si="1"/>
         <v>-1.2999999999999989</v>
       </c>
+      <c r="H77" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>87</v>
+      </c>
       <c r="K77" t="s">
         <v>666</v>
       </c>
@@ -7016,7 +7358,7 @@
         <v>700</v>
       </c>
       <c r="T77" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.2">
@@ -7043,6 +7385,12 @@
         <f t="shared" si="1"/>
         <v>-9.9</v>
       </c>
+      <c r="H78" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>88</v>
+      </c>
       <c r="K78" t="s">
         <v>679</v>
       </c>
@@ -7065,7 +7413,7 @@
         <v>700</v>
       </c>
       <c r="T78" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.2">
@@ -7092,6 +7440,12 @@
         <f t="shared" si="1"/>
         <v>-0.69999999999999929</v>
       </c>
+      <c r="H79" s="4" t="s">
+        <v>892</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>89</v>
+      </c>
       <c r="K79" t="s">
         <v>666</v>
       </c>
@@ -7114,7 +7468,7 @@
         <v>700</v>
       </c>
       <c r="T79" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.2">
@@ -7141,6 +7495,12 @@
         <f t="shared" si="1"/>
         <v>28.200000000000003</v>
       </c>
+      <c r="H80" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>893</v>
+      </c>
       <c r="K80" t="s">
         <v>666</v>
       </c>
@@ -7163,7 +7523,7 @@
         <v>700</v>
       </c>
       <c r="T80" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.2">
@@ -7190,6 +7550,12 @@
         <f t="shared" si="1"/>
         <v>23.4</v>
       </c>
+      <c r="H81" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I81" s="4" t="s">
+        <v>894</v>
+      </c>
       <c r="K81" t="s">
         <v>666</v>
       </c>
@@ -7212,7 +7578,7 @@
         <v>700</v>
       </c>
       <c r="T81" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.2">
@@ -7239,6 +7605,12 @@
         <f t="shared" si="1"/>
         <v>6.6000000000000005</v>
       </c>
+      <c r="H82" s="4" t="s">
+        <v>895</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>92</v>
+      </c>
       <c r="K82" t="s">
         <v>666</v>
       </c>
@@ -7261,7 +7633,7 @@
         <v>700</v>
       </c>
       <c r="T82" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.2">
@@ -8982,6 +9354,12 @@
         <f t="shared" si="1"/>
         <v>-7.2999999999999989</v>
       </c>
+      <c r="H117" s="4" t="s">
+        <v>824</v>
+      </c>
+      <c r="I117" s="4" t="s">
+        <v>825</v>
+      </c>
       <c r="K117" t="s">
         <v>677</v>
       </c>
@@ -9257,6 +9635,9 @@
       <c r="H122" t="s">
         <v>135</v>
       </c>
+      <c r="I122" s="4" t="s">
+        <v>826</v>
+      </c>
       <c r="K122" t="s">
         <v>677</v>
       </c>
@@ -9306,6 +9687,9 @@
         <f t="shared" si="1"/>
         <v>-12.700000000000001</v>
       </c>
+      <c r="H123" s="4" t="s">
+        <v>827</v>
+      </c>
       <c r="I123" s="6" t="s">
         <v>136</v>
       </c>
@@ -9471,6 +9855,9 @@
         <f t="shared" si="1"/>
         <v>-13.499999999999998</v>
       </c>
+      <c r="H126" s="4" t="s">
+        <v>828</v>
+      </c>
       <c r="I126" s="4" t="s">
         <v>142</v>
       </c>
@@ -9527,6 +9914,9 @@
       <c r="H127" s="4" t="s">
         <v>144</v>
       </c>
+      <c r="I127" s="4" t="s">
+        <v>829</v>
+      </c>
       <c r="K127" t="s">
         <v>677</v>
       </c>
@@ -9576,6 +9966,9 @@
         <f t="shared" si="1"/>
         <v>-5.6999999999999993</v>
       </c>
+      <c r="H128" s="4" t="s">
+        <v>830</v>
+      </c>
       <c r="I128" t="s">
         <v>145</v>
       </c>
@@ -12438,6 +12831,9 @@
         <f t="shared" si="2"/>
         <v>-1.0999999999999996</v>
       </c>
+      <c r="H182" s="4" t="s">
+        <v>831</v>
+      </c>
       <c r="I182" s="4" t="s">
         <v>798</v>
       </c>
@@ -12463,7 +12859,7 @@
         <v>809</v>
       </c>
       <c r="T182" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="183" spans="1:20" x14ac:dyDescent="0.2">
@@ -12490,6 +12886,12 @@
         <f t="shared" si="2"/>
         <v>-8.4</v>
       </c>
+      <c r="H183" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="I183" t="s">
+        <v>243</v>
+      </c>
       <c r="K183" t="s">
         <v>676</v>
       </c>
@@ -12512,7 +12914,7 @@
         <v>700</v>
       </c>
       <c r="T183" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="184" spans="1:20" x14ac:dyDescent="0.2">
@@ -12539,6 +12941,12 @@
         <f t="shared" si="2"/>
         <v>26.700000000000003</v>
       </c>
+      <c r="H184" t="s">
+        <v>244</v>
+      </c>
+      <c r="I184" s="4" t="s">
+        <v>867</v>
+      </c>
       <c r="K184" t="s">
         <v>676</v>
       </c>
@@ -12561,7 +12969,7 @@
         <v>700</v>
       </c>
       <c r="T184" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="185" spans="1:20" x14ac:dyDescent="0.2">
@@ -12588,6 +12996,12 @@
         <f t="shared" si="2"/>
         <v>31.9</v>
       </c>
+      <c r="H185" t="s">
+        <v>245</v>
+      </c>
+      <c r="I185" s="4" t="s">
+        <v>868</v>
+      </c>
       <c r="K185" t="s">
         <v>676</v>
       </c>
@@ -12610,7 +13024,7 @@
         <v>700</v>
       </c>
       <c r="T185" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="186" spans="1:20" x14ac:dyDescent="0.2">
@@ -12637,6 +13051,12 @@
         <f t="shared" si="2"/>
         <v>81.600000000000009</v>
       </c>
+      <c r="H186" t="s">
+        <v>246</v>
+      </c>
+      <c r="I186" s="4" t="s">
+        <v>869</v>
+      </c>
       <c r="K186" t="s">
         <v>676</v>
       </c>
@@ -12659,7 +13079,7 @@
         <v>700</v>
       </c>
       <c r="T186" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="187" spans="1:20" x14ac:dyDescent="0.2">
@@ -12686,6 +13106,12 @@
         <f t="shared" si="2"/>
         <v>41.5</v>
       </c>
+      <c r="H187" t="s">
+        <v>866</v>
+      </c>
+      <c r="I187" s="4" t="s">
+        <v>870</v>
+      </c>
       <c r="K187" t="s">
         <v>676</v>
       </c>
@@ -12708,7 +13134,7 @@
         <v>700</v>
       </c>
       <c r="T187" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="188" spans="1:20" x14ac:dyDescent="0.2">
@@ -12735,6 +13161,12 @@
         <f t="shared" si="2"/>
         <v>14.100000000000001</v>
       </c>
+      <c r="H188" t="s">
+        <v>248</v>
+      </c>
+      <c r="I188" s="4" t="s">
+        <v>871</v>
+      </c>
       <c r="K188" t="s">
         <v>676</v>
       </c>
@@ -12757,7 +13189,7 @@
         <v>700</v>
       </c>
       <c r="T188" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="189" spans="1:20" x14ac:dyDescent="0.2">
@@ -12784,6 +13216,12 @@
         <f t="shared" si="2"/>
         <v>67</v>
       </c>
+      <c r="H189" t="s">
+        <v>249</v>
+      </c>
+      <c r="I189" s="4" t="s">
+        <v>872</v>
+      </c>
       <c r="K189" t="s">
         <v>676</v>
       </c>
@@ -12806,7 +13244,7 @@
         <v>700</v>
       </c>
       <c r="T189" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="190" spans="1:20" x14ac:dyDescent="0.2">
@@ -12833,6 +13271,12 @@
         <f t="shared" si="2"/>
         <v>64.199999999999989</v>
       </c>
+      <c r="H190" t="s">
+        <v>250</v>
+      </c>
+      <c r="I190" s="4" t="s">
+        <v>873</v>
+      </c>
       <c r="K190" t="s">
         <v>676</v>
       </c>
@@ -12855,7 +13299,7 @@
         <v>700</v>
       </c>
       <c r="T190" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="191" spans="1:20" x14ac:dyDescent="0.2">
@@ -16005,6 +16449,9 @@
       <c r="H252" t="s">
         <v>319</v>
       </c>
+      <c r="I252" s="4" t="s">
+        <v>832</v>
+      </c>
       <c r="K252" t="s">
         <v>676</v>
       </c>
@@ -16027,7 +16474,7 @@
         <v>700</v>
       </c>
       <c r="T252" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="253" spans="1:20" x14ac:dyDescent="0.2">
@@ -16387,6 +16834,12 @@
         <f t="shared" si="4"/>
         <v>-1.6999999999999993</v>
       </c>
+      <c r="H259" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="I259" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="K259" t="s">
         <v>676</v>
       </c>
@@ -16436,6 +16889,12 @@
         <f t="shared" si="4"/>
         <v>-5.5</v>
       </c>
+      <c r="H260" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="I260" s="6" t="s">
+        <v>327</v>
+      </c>
       <c r="K260" t="s">
         <v>676</v>
       </c>
@@ -16485,6 +16944,12 @@
         <f t="shared" si="4"/>
         <v>4.1000000000000005</v>
       </c>
+      <c r="H261" t="s">
+        <v>328</v>
+      </c>
+      <c r="I261" s="4" t="s">
+        <v>835</v>
+      </c>
       <c r="K261" t="s">
         <v>676</v>
       </c>
@@ -16534,6 +16999,12 @@
         <f t="shared" si="4"/>
         <v>9.7000000000000011</v>
       </c>
+      <c r="H262" t="s">
+        <v>329</v>
+      </c>
+      <c r="I262" s="4" t="s">
+        <v>836</v>
+      </c>
       <c r="K262" t="s">
         <v>676</v>
       </c>
@@ -16583,6 +17054,12 @@
         <f t="shared" si="4"/>
         <v>50.6</v>
       </c>
+      <c r="H263" t="s">
+        <v>330</v>
+      </c>
+      <c r="I263" s="4" t="s">
+        <v>837</v>
+      </c>
       <c r="K263" t="s">
         <v>676</v>
       </c>
@@ -16632,6 +17109,12 @@
         <f t="shared" si="4"/>
         <v>14.8</v>
       </c>
+      <c r="H264" t="s">
+        <v>331</v>
+      </c>
+      <c r="I264" s="4" t="s">
+        <v>838</v>
+      </c>
       <c r="K264" t="s">
         <v>676</v>
       </c>
@@ -16681,6 +17164,12 @@
         <f t="shared" si="4"/>
         <v>54.3</v>
       </c>
+      <c r="H265" s="4" t="s">
+        <v>839</v>
+      </c>
+      <c r="I265" s="4" t="s">
+        <v>840</v>
+      </c>
       <c r="K265" t="s">
         <v>676</v>
       </c>
@@ -16730,6 +17219,12 @@
         <f t="shared" si="4"/>
         <v>52.4</v>
       </c>
+      <c r="H266" t="s">
+        <v>333</v>
+      </c>
+      <c r="I266" s="4" t="s">
+        <v>841</v>
+      </c>
       <c r="K266" t="s">
         <v>676</v>
       </c>
@@ -16779,6 +17274,12 @@
         <f t="shared" si="4"/>
         <v>49</v>
       </c>
+      <c r="H267" t="s">
+        <v>334</v>
+      </c>
+      <c r="I267" s="4" t="s">
+        <v>842</v>
+      </c>
       <c r="K267" t="s">
         <v>676</v>
       </c>
@@ -16828,6 +17329,12 @@
         <f t="shared" si="4"/>
         <v>68.8</v>
       </c>
+      <c r="H268" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="I268" s="4" t="s">
+        <v>844</v>
+      </c>
       <c r="K268" t="s">
         <v>676</v>
       </c>
@@ -16877,6 +17384,12 @@
         <f t="shared" si="4"/>
         <v>-16</v>
       </c>
+      <c r="H269" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="I269" s="6" t="s">
+        <v>336</v>
+      </c>
       <c r="K269" t="s">
         <v>676</v>
       </c>
@@ -16926,6 +17439,12 @@
         <f t="shared" si="4"/>
         <v>72</v>
       </c>
+      <c r="H270" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="I270" s="4" t="s">
+        <v>847</v>
+      </c>
       <c r="K270" t="s">
         <v>676</v>
       </c>
@@ -16975,6 +17494,12 @@
         <f t="shared" si="4"/>
         <v>67.7</v>
       </c>
+      <c r="H271" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="I271" s="4" t="s">
+        <v>849</v>
+      </c>
       <c r="K271" t="s">
         <v>676</v>
       </c>
@@ -17024,6 +17549,12 @@
         <f t="shared" si="4"/>
         <v>40.200000000000003</v>
       </c>
+      <c r="H272" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="I272" s="4" t="s">
+        <v>850</v>
+      </c>
       <c r="K272" t="s">
         <v>676</v>
       </c>
@@ -17073,6 +17604,12 @@
         <f t="shared" si="4"/>
         <v>56.699999999999996</v>
       </c>
+      <c r="H273" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="I273" s="4" t="s">
+        <v>851</v>
+      </c>
       <c r="K273" t="s">
         <v>676</v>
       </c>
@@ -17122,6 +17659,12 @@
         <f t="shared" si="4"/>
         <v>41.5</v>
       </c>
+      <c r="H274" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="I274" s="4" t="s">
+        <v>852</v>
+      </c>
       <c r="K274" t="s">
         <v>663</v>
       </c>
@@ -17171,6 +17714,12 @@
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
+      <c r="H275" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="I275" s="6" t="s">
+        <v>342</v>
+      </c>
       <c r="K275" t="s">
         <v>663</v>
       </c>
@@ -17220,6 +17769,12 @@
         <f t="shared" si="4"/>
         <v>11.7</v>
       </c>
+      <c r="H276" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="I276" s="4" t="s">
+        <v>854</v>
+      </c>
       <c r="K276" t="s">
         <v>663</v>
       </c>
@@ -17269,6 +17824,12 @@
         <f t="shared" si="4"/>
         <v>10.200000000000001</v>
       </c>
+      <c r="H277" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="I277" s="4" t="s">
+        <v>855</v>
+      </c>
       <c r="K277" t="s">
         <v>663</v>
       </c>
@@ -17319,6 +17880,12 @@
         <f t="shared" si="4"/>
         <v>22.6</v>
       </c>
+      <c r="H278" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="I278" s="4" t="s">
+        <v>856</v>
+      </c>
       <c r="K278" t="s">
         <v>663</v>
       </c>
@@ -17368,6 +17935,12 @@
         <f t="shared" si="4"/>
         <v>-12.299999999999999</v>
       </c>
+      <c r="H279" s="4" t="s">
+        <v>857</v>
+      </c>
+      <c r="I279" s="4" t="s">
+        <v>858</v>
+      </c>
       <c r="K279" t="s">
         <v>663</v>
       </c>
@@ -17417,6 +17990,12 @@
         <f t="shared" si="4"/>
         <v>16.100000000000001</v>
       </c>
+      <c r="H280" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="I280" s="4" t="s">
+        <v>859</v>
+      </c>
       <c r="K280" t="s">
         <v>663</v>
       </c>
@@ -17466,6 +18045,12 @@
         <f t="shared" si="4"/>
         <v>-12.6</v>
       </c>
+      <c r="H281" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="I281" s="6" t="s">
+        <v>348</v>
+      </c>
       <c r="K281" t="s">
         <v>663</v>
       </c>
@@ -17515,6 +18100,12 @@
         <f t="shared" si="4"/>
         <v>-14.700000000000003</v>
       </c>
+      <c r="H282" s="4" t="s">
+        <v>861</v>
+      </c>
+      <c r="I282" s="6" t="s">
+        <v>349</v>
+      </c>
       <c r="K282" t="s">
         <v>663</v>
       </c>
@@ -17564,6 +18155,12 @@
         <f t="shared" si="4"/>
         <v>26.799999999999997</v>
       </c>
+      <c r="H283" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="I283" s="4" t="s">
+        <v>863</v>
+      </c>
       <c r="K283" t="s">
         <v>663</v>
       </c>
@@ -17613,6 +18210,12 @@
         <f t="shared" si="4"/>
         <v>27.700000000000003</v>
       </c>
+      <c r="H284" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="I284" s="4" t="s">
+        <v>864</v>
+      </c>
       <c r="K284" t="s">
         <v>663</v>
       </c>
@@ -18436,6 +19039,9 @@
         <f t="shared" si="4"/>
         <v>-28.4</v>
       </c>
+      <c r="H299" s="4" t="s">
+        <v>897</v>
+      </c>
       <c r="I299" t="s">
         <v>793</v>
       </c>
@@ -18461,7 +19067,7 @@
         <v>700</v>
       </c>
       <c r="T299" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="300" spans="1:20" x14ac:dyDescent="0.2">
@@ -20952,7 +21558,12 @@
         <f t="shared" si="5"/>
         <v>-4.6999999999999993</v>
       </c>
-      <c r="H345" s="4"/>
+      <c r="H345" s="4" t="s">
+        <v>874</v>
+      </c>
+      <c r="I345" t="s">
+        <v>875</v>
+      </c>
       <c r="K345" t="s">
         <v>677</v>
       </c>
@@ -20975,7 +21586,7 @@
         <v>700</v>
       </c>
       <c r="T345" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="346" spans="1:20" x14ac:dyDescent="0.2">
@@ -21002,6 +21613,9 @@
         <f t="shared" si="5"/>
         <v>-5.6</v>
       </c>
+      <c r="H346" s="4" t="s">
+        <v>876</v>
+      </c>
       <c r="I346" t="s">
         <v>467</v>
       </c>
@@ -21027,7 +21641,7 @@
         <v>700</v>
       </c>
       <c r="T346" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="347" spans="1:20" x14ac:dyDescent="0.2">
@@ -21054,7 +21668,7 @@
         <f t="shared" si="5"/>
         <v>-34.6</v>
       </c>
-      <c r="H347" t="s">
+      <c r="H347" s="4" t="s">
         <v>800</v>
       </c>
       <c r="I347" t="s">
@@ -23947,6 +24561,12 @@
         <f t="shared" si="6"/>
         <v>32</v>
       </c>
+      <c r="H400" s="4" t="s">
+        <v>877</v>
+      </c>
+      <c r="I400" s="4" t="s">
+        <v>878</v>
+      </c>
       <c r="K400" t="s">
         <v>666</v>
       </c>
@@ -23969,7 +24589,7 @@
         <v>700</v>
       </c>
       <c r="T400" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="401" spans="1:20" x14ac:dyDescent="0.2">
@@ -23996,6 +24616,12 @@
         <f t="shared" si="6"/>
         <v>-20.5</v>
       </c>
+      <c r="H401" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="I401" s="6" t="s">
+        <v>570</v>
+      </c>
       <c r="K401" t="s">
         <v>666</v>
       </c>
@@ -24018,7 +24644,7 @@
         <v>700</v>
       </c>
       <c r="T401" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="402" spans="1:20" x14ac:dyDescent="0.2">
@@ -24045,6 +24671,12 @@
         <f t="shared" si="6"/>
         <v>-32.9</v>
       </c>
+      <c r="H402" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="I402" s="6" t="s">
+        <v>571</v>
+      </c>
       <c r="K402" t="s">
         <v>666</v>
       </c>
@@ -24067,7 +24699,7 @@
         <v>700</v>
       </c>
       <c r="T402" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="403" spans="1:20" x14ac:dyDescent="0.2">
@@ -24094,6 +24726,12 @@
         <f t="shared" si="6"/>
         <v>-24</v>
       </c>
+      <c r="H403" s="4" t="s">
+        <v>881</v>
+      </c>
+      <c r="I403" s="6" t="s">
+        <v>572</v>
+      </c>
       <c r="K403" t="s">
         <v>666</v>
       </c>
@@ -24116,7 +24754,7 @@
         <v>700</v>
       </c>
       <c r="T403" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="404" spans="1:20" x14ac:dyDescent="0.2">

--- a/inputs/House Model Data.xlsx
+++ b/inputs/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Developer/house_model_python/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A35A67-2CF5-1344-842A-3E1FF508F16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B26862-EA74-AA41-BAF0-695928DC390A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5450" uniqueCount="947">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5468" uniqueCount="959">
   <si>
     <t>State</t>
   </si>
@@ -2914,6 +2914,42 @@
   </si>
   <si>
     <t>McKinney, Donavan</t>
+  </si>
+  <si>
+    <t>Burke, Kristi</t>
+  </si>
+  <si>
+    <t>Barnett, Michaela</t>
+  </si>
+  <si>
+    <t>Golladay, Anna</t>
+  </si>
+  <si>
+    <t>Pearson, Justin</t>
+  </si>
+  <si>
+    <t>Garrett, Johny</t>
+  </si>
+  <si>
+    <t>Kuhn, Heidi</t>
+  </si>
+  <si>
+    <t>Taylor, Brent</t>
+  </si>
+  <si>
+    <t>Copeland, Darden</t>
+  </si>
+  <si>
+    <t>Broderick, Victoria</t>
+  </si>
+  <si>
+    <t>Croley, Mike</t>
+  </si>
+  <si>
+    <t>Hatcher, Charlie</t>
+  </si>
+  <si>
+    <t>Molder, Chaz</t>
   </si>
 </sst>
 </file>
@@ -12194,7 +12230,7 @@
         <v>699</v>
       </c>
       <c r="T165" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="166" spans="1:20" x14ac:dyDescent="0.2">
@@ -12249,7 +12285,7 @@
         <v>699</v>
       </c>
       <c r="T166" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="167" spans="1:20" x14ac:dyDescent="0.2">
@@ -12304,7 +12340,7 @@
         <v>699</v>
       </c>
       <c r="T167" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="168" spans="1:20" x14ac:dyDescent="0.2">
@@ -12359,7 +12395,7 @@
         <v>699</v>
       </c>
       <c r="T168" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="169" spans="1:20" x14ac:dyDescent="0.2">
@@ -13966,7 +14002,7 @@
         <v>699</v>
       </c>
       <c r="T200" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="201" spans="1:20" x14ac:dyDescent="0.2">
@@ -14018,7 +14054,7 @@
         <v>699</v>
       </c>
       <c r="T201" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="202" spans="1:20" x14ac:dyDescent="0.2">
@@ -14073,7 +14109,7 @@
         <v>699</v>
       </c>
       <c r="T202" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="203" spans="1:20" x14ac:dyDescent="0.2">
@@ -14128,7 +14164,7 @@
         <v>699</v>
       </c>
       <c r="T203" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="204" spans="1:20" x14ac:dyDescent="0.2">
@@ -14183,7 +14219,7 @@
         <v>699</v>
       </c>
       <c r="T204" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="205" spans="1:20" x14ac:dyDescent="0.2">
@@ -14238,7 +14274,7 @@
         <v>699</v>
       </c>
       <c r="T205" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="206" spans="1:20" x14ac:dyDescent="0.2">
@@ -14293,7 +14329,7 @@
         <v>699</v>
       </c>
       <c r="T206" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="207" spans="1:20" x14ac:dyDescent="0.2">
@@ -14348,7 +14384,7 @@
         <v>699</v>
       </c>
       <c r="T207" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="208" spans="1:20" x14ac:dyDescent="0.2">
@@ -14403,7 +14439,7 @@
         <v>699</v>
       </c>
       <c r="T208" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="209" spans="1:20" x14ac:dyDescent="0.2">
@@ -14458,7 +14494,7 @@
         <v>699</v>
       </c>
       <c r="T209" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="210" spans="1:20" x14ac:dyDescent="0.2">
@@ -14513,7 +14549,7 @@
         <v>699</v>
       </c>
       <c r="T210" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="211" spans="1:20" x14ac:dyDescent="0.2">
@@ -14568,7 +14604,7 @@
         <v>699</v>
       </c>
       <c r="T211" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="212" spans="1:20" x14ac:dyDescent="0.2">
@@ -14623,7 +14659,7 @@
         <v>699</v>
       </c>
       <c r="T212" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="213" spans="1:20" x14ac:dyDescent="0.2">
@@ -15291,7 +15327,7 @@
         <v>699</v>
       </c>
       <c r="T225" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="226" spans="1:20" x14ac:dyDescent="0.2">
@@ -15346,7 +15382,7 @@
         <v>699</v>
       </c>
       <c r="T226" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="227" spans="1:20" x14ac:dyDescent="0.2">
@@ -15401,7 +15437,7 @@
         <v>699</v>
       </c>
       <c r="T227" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="228" spans="1:20" x14ac:dyDescent="0.2">
@@ -15456,7 +15492,7 @@
         <v>699</v>
       </c>
       <c r="T228" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="229" spans="1:20" x14ac:dyDescent="0.2">
@@ -15511,7 +15547,7 @@
         <v>699</v>
       </c>
       <c r="T229" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="230" spans="1:20" x14ac:dyDescent="0.2">
@@ -15566,7 +15602,7 @@
         <v>699</v>
       </c>
       <c r="T230" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="231" spans="1:20" x14ac:dyDescent="0.2">
@@ -15621,7 +15657,7 @@
         <v>699</v>
       </c>
       <c r="T231" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="232" spans="1:20" x14ac:dyDescent="0.2">
@@ -15676,7 +15712,7 @@
         <v>699</v>
       </c>
       <c r="T232" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="233" spans="1:20" x14ac:dyDescent="0.2">
@@ -17156,7 +17192,7 @@
         <v>699</v>
       </c>
       <c r="T259" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="260" spans="1:20" x14ac:dyDescent="0.2">
@@ -17211,7 +17247,7 @@
         <v>699</v>
       </c>
       <c r="T260" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="261" spans="1:20" x14ac:dyDescent="0.2">
@@ -17266,7 +17302,7 @@
         <v>699</v>
       </c>
       <c r="T261" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="262" spans="1:20" x14ac:dyDescent="0.2">
@@ -17321,7 +17357,7 @@
         <v>699</v>
       </c>
       <c r="T262" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="263" spans="1:20" x14ac:dyDescent="0.2">
@@ -17376,7 +17412,7 @@
         <v>699</v>
       </c>
       <c r="T263" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="264" spans="1:20" x14ac:dyDescent="0.2">
@@ -17431,7 +17467,7 @@
         <v>699</v>
       </c>
       <c r="T264" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="265" spans="1:20" x14ac:dyDescent="0.2">
@@ -17486,7 +17522,7 @@
         <v>699</v>
       </c>
       <c r="T265" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="266" spans="1:20" x14ac:dyDescent="0.2">
@@ -17541,7 +17577,7 @@
         <v>699</v>
       </c>
       <c r="T266" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="267" spans="1:20" x14ac:dyDescent="0.2">
@@ -17596,7 +17632,7 @@
         <v>699</v>
       </c>
       <c r="T267" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="268" spans="1:20" x14ac:dyDescent="0.2">
@@ -17651,7 +17687,7 @@
         <v>699</v>
       </c>
       <c r="T268" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="269" spans="1:20" x14ac:dyDescent="0.2">
@@ -17706,7 +17742,7 @@
         <v>699</v>
       </c>
       <c r="T269" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="270" spans="1:20" x14ac:dyDescent="0.2">
@@ -17761,7 +17797,7 @@
         <v>699</v>
       </c>
       <c r="T270" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="271" spans="1:20" x14ac:dyDescent="0.2">
@@ -17816,7 +17852,7 @@
         <v>699</v>
       </c>
       <c r="T271" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="272" spans="1:20" x14ac:dyDescent="0.2">
@@ -17871,7 +17907,7 @@
         <v>699</v>
       </c>
       <c r="T272" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="273" spans="1:20" x14ac:dyDescent="0.2">
@@ -17926,7 +17962,7 @@
         <v>699</v>
       </c>
       <c r="T273" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="274" spans="1:20" x14ac:dyDescent="0.2">
@@ -17981,7 +18017,7 @@
         <v>699</v>
       </c>
       <c r="T274" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="275" spans="1:20" x14ac:dyDescent="0.2">
@@ -18036,7 +18072,7 @@
         <v>699</v>
       </c>
       <c r="T275" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="276" spans="1:20" x14ac:dyDescent="0.2">
@@ -18091,7 +18127,7 @@
         <v>699</v>
       </c>
       <c r="T276" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="277" spans="1:20" x14ac:dyDescent="0.2">
@@ -18146,7 +18182,7 @@
         <v>699</v>
       </c>
       <c r="T277" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="278" spans="1:20" x14ac:dyDescent="0.2">
@@ -18202,7 +18238,7 @@
         <v>699</v>
       </c>
       <c r="T278" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="279" spans="1:20" x14ac:dyDescent="0.2">
@@ -18257,7 +18293,7 @@
         <v>699</v>
       </c>
       <c r="T279" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="280" spans="1:20" x14ac:dyDescent="0.2">
@@ -18312,7 +18348,7 @@
         <v>699</v>
       </c>
       <c r="T280" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="281" spans="1:20" x14ac:dyDescent="0.2">
@@ -18367,7 +18403,7 @@
         <v>699</v>
       </c>
       <c r="T281" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="282" spans="1:20" x14ac:dyDescent="0.2">
@@ -18422,7 +18458,7 @@
         <v>699</v>
       </c>
       <c r="T282" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="283" spans="1:20" x14ac:dyDescent="0.2">
@@ -18477,7 +18513,7 @@
         <v>699</v>
       </c>
       <c r="T283" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="284" spans="1:20" x14ac:dyDescent="0.2">
@@ -18532,7 +18568,7 @@
         <v>699</v>
       </c>
       <c r="T284" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="285" spans="1:20" x14ac:dyDescent="0.2">
@@ -22291,6 +22327,12 @@
         <f t="shared" si="5"/>
         <v>-49.800000000000004</v>
       </c>
+      <c r="H353" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="I353" s="6" t="s">
+        <v>473</v>
+      </c>
       <c r="K353" t="s">
         <v>679</v>
       </c>
@@ -22313,7 +22355,7 @@
         <v>699</v>
       </c>
       <c r="T353" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="354" spans="1:20" x14ac:dyDescent="0.2">
@@ -22341,6 +22383,12 @@
         <f t="shared" si="5"/>
         <v>-25.800000000000004</v>
       </c>
+      <c r="H354" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="I354" s="6" t="s">
+        <v>474</v>
+      </c>
       <c r="K354" t="s">
         <v>679</v>
       </c>
@@ -22363,7 +22411,7 @@
         <v>699</v>
       </c>
       <c r="T354" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="355" spans="1:20" x14ac:dyDescent="0.2">
@@ -22391,6 +22439,12 @@
         <f t="shared" si="5"/>
         <v>-27.700000000000003</v>
       </c>
+      <c r="H355" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="I355" s="6" t="s">
+        <v>475</v>
+      </c>
       <c r="K355" t="s">
         <v>679</v>
       </c>
@@ -22413,7 +22467,7 @@
         <v>699</v>
       </c>
       <c r="T355" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="356" spans="1:20" x14ac:dyDescent="0.2">
@@ -22441,6 +22495,12 @@
         <f t="shared" si="5"/>
         <v>-15.900000000000006</v>
       </c>
+      <c r="H356" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="I356" s="6" t="s">
+        <v>476</v>
+      </c>
       <c r="K356" t="s">
         <v>680</v>
       </c>
@@ -22491,6 +22551,12 @@
         <f t="shared" si="5"/>
         <v>-15.100000000000001</v>
       </c>
+      <c r="H357" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="I357" s="4" t="s">
+        <v>957</v>
+      </c>
       <c r="K357" t="s">
         <v>680</v>
       </c>
@@ -22541,6 +22607,12 @@
         <f t="shared" si="5"/>
         <v>-18.5</v>
       </c>
+      <c r="H358" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="I358" s="4" t="s">
+        <v>951</v>
+      </c>
       <c r="K358" t="s">
         <v>680</v>
       </c>
@@ -22591,6 +22663,12 @@
         <f t="shared" si="5"/>
         <v>-14.399999999999999</v>
       </c>
+      <c r="H359" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="I359" t="s">
+        <v>479</v>
+      </c>
       <c r="K359" t="s">
         <v>680</v>
       </c>
@@ -22641,6 +22719,12 @@
         <f t="shared" si="5"/>
         <v>-12.199999999999996</v>
       </c>
+      <c r="H360" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="I360" t="s">
+        <v>480</v>
+      </c>
       <c r="K360" t="s">
         <v>680</v>
       </c>
@@ -22690,6 +22774,12 @@
       <c r="G361" s="3">
         <f t="shared" si="5"/>
         <v>-13.100000000000001</v>
+      </c>
+      <c r="H361" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="I361" s="4" t="s">
+        <v>953</v>
       </c>
       <c r="K361" t="s">
         <v>680</v>

--- a/inputs/House Model Data.xlsx
+++ b/inputs/House Model Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Developer/house_model_python/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B26862-EA74-AA41-BAF0-695928DC390A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB28557-0F2A-034E-8FBD-5098043A63C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5468" uniqueCount="959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5473" uniqueCount="962">
   <si>
     <t>State</t>
   </si>
@@ -2950,6 +2950,15 @@
   </si>
   <si>
     <t>Molder, Chaz</t>
+  </si>
+  <si>
+    <t>Lam, Adriel</t>
+  </si>
+  <si>
+    <t>Awa, Brenton</t>
+  </si>
+  <si>
+    <t>Ambrose, Ben</t>
   </si>
 </sst>
 </file>
@@ -10315,6 +10324,12 @@
         <f t="shared" ref="G131:G194" si="2">E131+6.5+1.5</f>
         <v>32.700000000000003</v>
       </c>
+      <c r="H131" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I131" s="4" t="s">
+        <v>959</v>
+      </c>
       <c r="K131" t="s">
         <v>677</v>
       </c>
@@ -10364,6 +10379,12 @@
         <f t="shared" si="2"/>
         <v>29.6</v>
       </c>
+      <c r="H132" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="I132" s="4" t="s">
+        <v>960</v>
+      </c>
       <c r="K132" t="s">
         <v>677</v>
       </c>
@@ -14028,6 +14049,9 @@
       <c r="G201" s="3">
         <f t="shared" si="3"/>
         <v>-21.9</v>
+      </c>
+      <c r="H201" s="4" t="s">
+        <v>961</v>
       </c>
       <c r="I201" t="s">
         <v>260</v>

--- a/inputs/House Model Data.xlsx
+++ b/inputs/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Developer/house_model_python/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB28557-0F2A-034E-8FBD-5098043A63C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4D67E0-6CEC-6D4A-8023-DCDE95E0ED95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5473" uniqueCount="962">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5474" uniqueCount="963">
   <si>
     <t>State</t>
   </si>
@@ -2959,6 +2959,9 @@
   </si>
   <si>
     <t>Ambrose, Ben</t>
+  </si>
+  <si>
+    <t>Balkcom, Jennifer</t>
   </si>
 </sst>
 </file>
@@ -19175,6 +19178,9 @@
       <c r="H295" s="4" t="s">
         <v>374</v>
       </c>
+      <c r="I295" s="4" t="s">
+        <v>962</v>
+      </c>
       <c r="K295" t="s">
         <v>679</v>
       </c>

--- a/inputs/House Model Data.xlsx
+++ b/inputs/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Developer/house_model_python/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4D67E0-6CEC-6D4A-8023-DCDE95E0ED95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB9F942-EA02-774C-BC57-F1738C67CFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5474" uniqueCount="963">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5526" uniqueCount="996">
   <si>
     <t>State</t>
   </si>
@@ -2962,6 +2962,105 @@
   </si>
   <si>
     <t>Balkcom, Jennifer</t>
+  </si>
+  <si>
+    <t>Conroy, Carmela</t>
+  </si>
+  <si>
+    <t>Jones, Clyde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figures, Shomari </t>
+  </si>
+  <si>
+    <t>Marques, Rhett</t>
+  </si>
+  <si>
+    <t>Chai, Amy</t>
+  </si>
+  <si>
+    <t>Austin, Joseph Patrick</t>
+  </si>
+  <si>
+    <t>Lancia, Christopher</t>
+  </si>
+  <si>
+    <t>Malloy, Gerald</t>
+  </si>
+  <si>
+    <t>Shea, Chris</t>
+  </si>
+  <si>
+    <t>Carl, Jerry</t>
+  </si>
+  <si>
+    <t>Goldstein, Michael</t>
+  </si>
+  <si>
+    <t>Bronin, Luke</t>
+  </si>
+  <si>
+    <t>Berman, Mitchell</t>
+  </si>
+  <si>
+    <t>Akin, Ammie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rogers, Tim </t>
+  </si>
+  <si>
+    <t>Alfonso, Michael</t>
+  </si>
+  <si>
+    <t>Cooke, Rebecca</t>
+  </si>
+  <si>
+    <t>Little, Matt</t>
+  </si>
+  <si>
+    <t>Swanson, Tina</t>
+  </si>
+  <si>
+    <t>Johnson, Jake</t>
+  </si>
+  <si>
+    <t>Chapin, Doug</t>
+  </si>
+  <si>
+    <t>Pratt, Eric</t>
+  </si>
+  <si>
+    <t>Mercer, Maurice</t>
+  </si>
+  <si>
+    <t>Osberg, Erik</t>
+  </si>
+  <si>
+    <t>Steil, Bryan</t>
+  </si>
+  <si>
+    <t>Van Orden, Jeff</t>
+  </si>
+  <si>
+    <t>Beck, Andrew</t>
+  </si>
+  <si>
+    <t>Nagel, John</t>
+  </si>
+  <si>
+    <t>Bass, Tyler</t>
+  </si>
+  <si>
+    <t>Clark, Fred</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crosson, Rick </t>
+  </si>
+  <si>
+    <t>Wikstrom, Paul</t>
+  </si>
+  <si>
+    <t>Sneed, Andrew</t>
   </si>
 </sst>
 </file>
@@ -3504,6 +3603,12 @@
         <f>E2+6.5+1.5</f>
         <v>-28.299999999999997</v>
       </c>
+      <c r="H2" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>972</v>
+      </c>
       <c r="K2" t="s">
         <v>673</v>
       </c>
@@ -3514,7 +3619,7 @@
         <v>699</v>
       </c>
       <c r="T2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
@@ -3542,6 +3647,12 @@
         <f t="shared" ref="G3:G66" si="0">E3+6.5+1.5</f>
         <v>-9.3000000000000043</v>
       </c>
+      <c r="H3" t="s">
+        <v>965</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>966</v>
+      </c>
       <c r="K3" t="s">
         <v>673</v>
       </c>
@@ -3552,7 +3663,7 @@
         <v>699</v>
       </c>
       <c r="T3" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.2">
@@ -3668,6 +3779,12 @@
         <f t="shared" si="0"/>
         <v>-21</v>
       </c>
+      <c r="H6" s="4" t="s">
+        <v>995</v>
+      </c>
+      <c r="I6" t="s">
+        <v>14</v>
+      </c>
       <c r="K6" t="s">
         <v>673</v>
       </c>
@@ -3706,8 +3823,11 @@
         <f t="shared" si="0"/>
         <v>-26.999999999999993</v>
       </c>
+      <c r="H7" s="4" t="s">
+        <v>985</v>
+      </c>
       <c r="I7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K7" t="s">
         <v>673</v>
@@ -3747,6 +3867,12 @@
         <f t="shared" si="0"/>
         <v>32.799999999999997</v>
       </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>976</v>
+      </c>
       <c r="K8" t="s">
         <v>673</v>
       </c>
@@ -3757,7 +3883,7 @@
         <v>699</v>
       </c>
       <c r="T8" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.2">
@@ -7855,6 +7981,12 @@
         <f t="shared" si="1"/>
         <v>30.9</v>
       </c>
+      <c r="H83" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="I83" s="4" t="s">
+        <v>967</v>
+      </c>
       <c r="K83" t="s">
         <v>662</v>
       </c>
@@ -7877,7 +8009,7 @@
         <v>699</v>
       </c>
       <c r="T83" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.2">
@@ -7904,6 +8036,12 @@
         <f t="shared" si="1"/>
         <v>15.7</v>
       </c>
+      <c r="H84" t="s">
+        <v>94</v>
+      </c>
+      <c r="I84" s="4" t="s">
+        <v>968</v>
+      </c>
       <c r="K84" t="s">
         <v>662</v>
       </c>
@@ -7926,7 +8064,7 @@
         <v>699</v>
       </c>
       <c r="T84" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.2">
@@ -7953,6 +8091,12 @@
         <f t="shared" si="1"/>
         <v>22.1</v>
       </c>
+      <c r="H85" t="s">
+        <v>95</v>
+      </c>
+      <c r="I85" s="4" t="s">
+        <v>969</v>
+      </c>
       <c r="K85" t="s">
         <v>662</v>
       </c>
@@ -7975,7 +8119,7 @@
         <v>699</v>
       </c>
       <c r="T85" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.2">
@@ -8002,6 +8146,12 @@
         <f t="shared" si="1"/>
         <v>31.4</v>
       </c>
+      <c r="H86" t="s">
+        <v>96</v>
+      </c>
+      <c r="I86" s="4" t="s">
+        <v>973</v>
+      </c>
       <c r="K86" t="s">
         <v>662</v>
       </c>
@@ -8024,7 +8174,7 @@
         <v>699</v>
       </c>
       <c r="T86" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.2">
@@ -8051,6 +8201,12 @@
         <f t="shared" si="1"/>
         <v>13.6</v>
       </c>
+      <c r="H87" t="s">
+        <v>97</v>
+      </c>
+      <c r="I87" s="4" t="s">
+        <v>971</v>
+      </c>
       <c r="K87" t="s">
         <v>662</v>
       </c>
@@ -8073,7 +8229,7 @@
         <v>699</v>
       </c>
       <c r="T87" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.2">
@@ -14713,6 +14869,12 @@
         <f t="shared" si="3"/>
         <v>-4</v>
       </c>
+      <c r="H213" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="I213" s="6" t="s">
+        <v>272</v>
+      </c>
       <c r="K213" t="s">
         <v>663</v>
       </c>
@@ -14762,6 +14924,12 @@
         <f t="shared" si="3"/>
         <v>13.8</v>
       </c>
+      <c r="H214" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="I214" s="4" t="s">
+        <v>984</v>
+      </c>
       <c r="K214" t="s">
         <v>663</v>
       </c>
@@ -14811,6 +14979,12 @@
         <f t="shared" si="3"/>
         <v>29.3</v>
       </c>
+      <c r="H215" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="I215" s="4" t="s">
+        <v>991</v>
+      </c>
       <c r="K215" t="s">
         <v>663</v>
       </c>
@@ -14860,6 +15034,12 @@
         <f t="shared" si="3"/>
         <v>43.7</v>
       </c>
+      <c r="H216" t="s">
+        <v>275</v>
+      </c>
+      <c r="I216" s="4" t="s">
+        <v>994</v>
+      </c>
       <c r="K216" t="s">
         <v>663</v>
       </c>
@@ -14909,6 +15089,12 @@
         <f t="shared" si="3"/>
         <v>69.900000000000006</v>
       </c>
+      <c r="H217" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="I217" s="4" t="s">
+        <v>990</v>
+      </c>
       <c r="K217" t="s">
         <v>663</v>
       </c>
@@ -14958,6 +15144,12 @@
         <f t="shared" si="3"/>
         <v>-11.7</v>
       </c>
+      <c r="H218" s="4" t="s">
+        <v>983</v>
+      </c>
+      <c r="I218" t="s">
+        <v>277</v>
+      </c>
       <c r="K218" t="s">
         <v>663</v>
       </c>
@@ -15007,6 +15199,12 @@
         <f t="shared" si="3"/>
         <v>-28.5</v>
       </c>
+      <c r="H219" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="I219" t="s">
+        <v>278</v>
+      </c>
       <c r="K219" t="s">
         <v>663</v>
       </c>
@@ -15056,6 +15254,12 @@
         <f t="shared" si="3"/>
         <v>-6.3000000000000007</v>
       </c>
+      <c r="H220" t="s">
+        <v>981</v>
+      </c>
+      <c r="I220" t="s">
+        <v>279</v>
+      </c>
       <c r="K220" t="s">
         <v>663</v>
       </c>
@@ -25192,6 +25396,12 @@
         <f t="shared" si="6"/>
         <v>42.8</v>
       </c>
+      <c r="H404" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="I404" s="4" t="s">
+        <v>970</v>
+      </c>
       <c r="K404" t="s">
         <v>662</v>
       </c>
@@ -25214,7 +25424,7 @@
         <v>699</v>
       </c>
       <c r="T404" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="405" spans="1:20" x14ac:dyDescent="0.2">
@@ -26077,6 +26287,9 @@
         <f t="shared" si="6"/>
         <v>-2.6999999999999993</v>
       </c>
+      <c r="H420" s="4" t="s">
+        <v>963</v>
+      </c>
       <c r="I420" t="s">
         <v>926</v>
       </c>
@@ -26102,7 +26315,7 @@
         <v>698</v>
       </c>
       <c r="T420" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="421" spans="1:20" x14ac:dyDescent="0.2">
@@ -26511,6 +26724,12 @@
         <f t="shared" si="6"/>
         <v>3.5</v>
       </c>
+      <c r="H428" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="I428" t="s">
+        <v>987</v>
+      </c>
       <c r="K428" t="s">
         <v>663</v>
       </c>
@@ -26533,7 +26752,7 @@
         <v>699</v>
       </c>
       <c r="T428" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="429" spans="1:20" x14ac:dyDescent="0.2">
@@ -26560,6 +26779,9 @@
         <f t="shared" si="6"/>
         <v>48</v>
       </c>
+      <c r="H429" t="s">
+        <v>601</v>
+      </c>
       <c r="K429" t="s">
         <v>663</v>
       </c>
@@ -26582,7 +26804,7 @@
         <v>699</v>
       </c>
       <c r="T429" t="s">
-        <v>702</v>
+        <v>770</v>
       </c>
     </row>
     <row r="430" spans="1:20" x14ac:dyDescent="0.2">
@@ -26609,6 +26831,12 @@
         <f t="shared" si="6"/>
         <v>0.59999999999999964</v>
       </c>
+      <c r="H430" s="4" t="s">
+        <v>979</v>
+      </c>
+      <c r="I430" t="s">
+        <v>988</v>
+      </c>
       <c r="K430" t="s">
         <v>663</v>
       </c>
@@ -26631,7 +26859,7 @@
         <v>699</v>
       </c>
       <c r="T430" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="431" spans="1:20" x14ac:dyDescent="0.2">
@@ -26658,6 +26886,12 @@
         <f t="shared" si="6"/>
         <v>59.4</v>
       </c>
+      <c r="H431" t="s">
+        <v>603</v>
+      </c>
+      <c r="I431" s="4" t="s">
+        <v>977</v>
+      </c>
       <c r="K431" t="s">
         <v>663</v>
       </c>
@@ -26680,7 +26914,7 @@
         <v>699</v>
       </c>
       <c r="T431" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="432" spans="1:20" x14ac:dyDescent="0.2">
@@ -26707,6 +26941,12 @@
         <f t="shared" si="6"/>
         <v>-14.100000000000001</v>
       </c>
+      <c r="H432" s="4" t="s">
+        <v>989</v>
+      </c>
+      <c r="I432" t="s">
+        <v>604</v>
+      </c>
       <c r="K432" t="s">
         <v>663</v>
       </c>
@@ -26729,7 +26969,7 @@
         <v>699</v>
       </c>
       <c r="T432" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="433" spans="1:20" x14ac:dyDescent="0.2">
@@ -26756,6 +26996,9 @@
         <f t="shared" si="6"/>
         <v>-8.3999999999999986</v>
       </c>
+      <c r="I433" t="s">
+        <v>605</v>
+      </c>
       <c r="K433" t="s">
         <v>663</v>
       </c>
@@ -26778,7 +27021,7 @@
         <v>699</v>
       </c>
       <c r="T433" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="434" spans="1:20" x14ac:dyDescent="0.2">
@@ -26805,6 +27048,12 @@
         <f t="shared" si="6"/>
         <v>-14.5</v>
       </c>
+      <c r="H434" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="I434" s="4" t="s">
+        <v>978</v>
+      </c>
       <c r="K434" t="s">
         <v>663</v>
       </c>
@@ -26827,7 +27076,7 @@
         <v>699</v>
       </c>
       <c r="T434" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="435" spans="1:20" x14ac:dyDescent="0.2">
@@ -26854,6 +27103,12 @@
         <f t="shared" si="6"/>
         <v>-8.1999999999999993</v>
       </c>
+      <c r="H435" s="4" t="s">
+        <v>993</v>
+      </c>
+      <c r="I435" t="s">
+        <v>607</v>
+      </c>
       <c r="K435" t="s">
         <v>663</v>
       </c>
@@ -26876,7 +27131,7 @@
         <v>699</v>
       </c>
       <c r="T435" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="436" spans="1:20" x14ac:dyDescent="0.2">

--- a/inputs/House Model Data.xlsx
+++ b/inputs/House Model Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Developer/house_model_python/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB9F942-EA02-774C-BC57-F1738C67CFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE3E6C7E-31B9-654D-A258-96AF159447AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -3600,8 +3600,8 @@
         <v>-30.199999999999996</v>
       </c>
       <c r="G2" s="3">
-        <f>E2+6.5+1.5</f>
-        <v>-28.299999999999997</v>
+        <f>E2+6.7+1.5</f>
+        <v>-28.099999999999998</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>964</v>
@@ -3644,8 +3644,8 @@
         <v>-11.799999999999997</v>
       </c>
       <c r="G3" s="3">
-        <f t="shared" ref="G3:G66" si="0">E3+6.5+1.5</f>
-        <v>-9.3000000000000043</v>
+        <f t="shared" ref="G3:G66" si="0">E3+6.7+1.5</f>
+        <v>-9.100000000000005</v>
       </c>
       <c r="H3" t="s">
         <v>965</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="G4" s="3">
         <f t="shared" si="0"/>
-        <v>-37.900000000000006</v>
+        <v>-37.700000000000003</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>11</v>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="G5" s="3">
         <f t="shared" si="0"/>
-        <v>-59.800000000000011</v>
+        <v>-59.600000000000009</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>13</v>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G6" s="3">
         <f t="shared" si="0"/>
-        <v>-21</v>
+        <v>-20.8</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>995</v>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G7" s="3">
         <f t="shared" si="0"/>
-        <v>-26.999999999999993</v>
+        <v>-26.799999999999994</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>985</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="G8" s="3">
         <f t="shared" si="0"/>
-        <v>32.799999999999997</v>
+        <v>33</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="G9" s="3">
         <f t="shared" si="0"/>
-        <v>-5.0999999999999996</v>
+        <v>-4.8999999999999995</v>
       </c>
       <c r="K9" t="s">
         <v>672</v>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="G10" s="3">
         <f t="shared" si="0"/>
-        <v>4.9000000000000004</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>895</v>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="G11" s="3">
         <f t="shared" si="0"/>
-        <v>-6.9</v>
+        <v>-6.6999999999999993</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>812</v>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="G12" s="3">
         <f t="shared" si="0"/>
-        <v>47.6</v>
+        <v>47.800000000000004</v>
       </c>
       <c r="H12" t="s">
         <v>21</v>
@@ -4119,7 +4119,7 @@
       </c>
       <c r="G13" s="3">
         <f t="shared" si="0"/>
-        <v>15.3</v>
+        <v>15.5</v>
       </c>
       <c r="H13" t="s">
         <v>22</v>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="G14" s="3">
         <f t="shared" si="0"/>
-        <v>-11.899999999999999</v>
+        <v>-11.7</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>883</v>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="G15" s="3">
         <f t="shared" si="0"/>
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>814</v>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="G16" s="3">
         <f t="shared" si="0"/>
-        <v>30.1</v>
+        <v>30.3</v>
       </c>
       <c r="H16" t="s">
         <v>25</v>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="G17" s="3">
         <f t="shared" si="0"/>
-        <v>-8.3000000000000007</v>
+        <v>-8.1000000000000014</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>884</v>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="G18" s="3">
         <f t="shared" si="0"/>
-        <v>-23</v>
+        <v>-22.8</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>817</v>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G19" s="3">
         <f t="shared" si="0"/>
-        <v>-37.299999999999997</v>
+        <v>-37.099999999999994</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>29</v>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="G20" s="3">
         <f t="shared" si="0"/>
-        <v>-7.6</v>
+        <v>-7.3999999999999986</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>31</v>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="G21" s="3">
         <f t="shared" si="0"/>
-        <v>-16.899999999999999</v>
+        <v>-16.7</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>33</v>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="G22" s="3">
         <f t="shared" si="0"/>
-        <v>-31.9</v>
+        <v>-31.699999999999996</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>35</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="G23" s="3">
         <f t="shared" si="0"/>
-        <v>20.2</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>740</v>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="G24" s="3">
         <f t="shared" si="0"/>
-        <v>32.6</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>37</v>
@@ -4780,7 +4780,7 @@
       </c>
       <c r="G25" s="3">
         <f t="shared" si="0"/>
-        <v>18.100000000000001</v>
+        <v>18.3</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>742</v>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G26" s="3">
         <f t="shared" si="0"/>
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>38</v>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="G27" s="3">
         <f t="shared" si="0"/>
-        <v>-12.600000000000001</v>
+        <v>-12.400000000000002</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>744</v>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="G28" s="3">
         <f t="shared" si="0"/>
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>791</v>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="G29" s="3">
         <f t="shared" si="0"/>
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="H29" t="s">
         <v>40</v>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="G30" s="3">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="H30" t="s">
         <v>41</v>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="G31" s="3">
         <f t="shared" si="0"/>
-        <v>19.399999999999999</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="H31" t="s">
         <v>42</v>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="G32" s="3">
         <f t="shared" si="0"/>
-        <v>41.5</v>
+        <v>41.7</v>
       </c>
       <c r="H32" t="s">
         <v>43</v>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="G33" s="3">
         <f t="shared" si="0"/>
-        <v>75.7</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>737</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="G34" s="3">
         <f t="shared" si="0"/>
-        <v>81.8</v>
+        <v>82</v>
       </c>
       <c r="H34" t="s">
         <v>45</v>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="G35" s="3">
         <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>8.6000000000000014</v>
       </c>
       <c r="H35" t="s">
         <v>46</v>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="G36" s="3">
         <f t="shared" si="0"/>
-        <v>42.7</v>
+        <v>42.900000000000006</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>749</v>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="G37" s="3">
         <f t="shared" si="0"/>
-        <v>55.8</v>
+        <v>56</v>
       </c>
       <c r="H37" t="s">
         <v>48</v>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="G38" s="3">
         <f t="shared" si="0"/>
-        <v>56.1</v>
+        <v>56.300000000000004</v>
       </c>
       <c r="H38" t="s">
         <v>49</v>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="G39" s="3">
         <f t="shared" si="0"/>
-        <v>46.9</v>
+        <v>47.1</v>
       </c>
       <c r="H39" t="s">
         <v>50</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G40" s="3">
         <f t="shared" si="0"/>
-        <v>36.4</v>
+        <v>36.6</v>
       </c>
       <c r="H40" t="s">
         <v>51</v>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="G41" s="3">
         <f t="shared" si="0"/>
-        <v>42.3</v>
+        <v>42.5</v>
       </c>
       <c r="H41" t="s">
         <v>52</v>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="G42" s="3">
         <f t="shared" si="0"/>
-        <v>-24.200000000000003</v>
+        <v>-24.000000000000004</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>753</v>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="G43" s="3">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="H43" t="s">
         <v>54</v>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="G44" s="3">
         <f t="shared" si="0"/>
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>794</v>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="G45" s="3">
         <f t="shared" si="0"/>
-        <v>-11.3</v>
+        <v>-11.100000000000001</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>773</v>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="G46" s="3">
         <f t="shared" si="0"/>
-        <v>32.9</v>
+        <v>33.099999999999994</v>
       </c>
       <c r="H46" t="s">
         <v>57</v>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="G47" s="3">
         <f t="shared" si="0"/>
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="H47" t="s">
         <v>58</v>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="G48" s="3">
         <f t="shared" si="0"/>
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="H48" s="4" t="s">
         <v>735</v>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="G49" s="3">
         <f t="shared" si="0"/>
-        <v>17.7</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="H49" t="s">
         <v>60</v>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="G50" s="3">
         <f t="shared" si="0"/>
-        <v>33.200000000000003</v>
+        <v>33.4</v>
       </c>
       <c r="H50" t="s">
         <v>61</v>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="G51" s="3">
         <f t="shared" si="0"/>
-        <v>41.6</v>
+        <v>41.800000000000004</v>
       </c>
       <c r="H51" t="s">
         <v>62</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="G52" s="3">
         <f t="shared" si="0"/>
-        <v>47.9</v>
+        <v>48.1</v>
       </c>
       <c r="H52" t="s">
         <v>63</v>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="G53" s="3">
         <f t="shared" si="0"/>
-        <v>20.2</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="H53" t="s">
         <v>64</v>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="G54" s="3">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="H54" t="s">
         <v>65</v>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="G55" s="3">
         <f t="shared" si="0"/>
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="H55" t="s">
         <v>66</v>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="G56" s="3">
         <f t="shared" si="0"/>
-        <v>58.6</v>
+        <v>58.800000000000004</v>
       </c>
       <c r="H56" t="s">
         <v>67</v>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="G57" s="3">
         <f t="shared" si="0"/>
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="H57" t="s">
         <v>68</v>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="G58" s="3">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>47.2</v>
       </c>
       <c r="H58" t="s">
         <v>69</v>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="G59" s="3">
         <f t="shared" si="0"/>
-        <v>68.400000000000006</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="H59" t="s">
         <v>70</v>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="G60" s="3">
         <f t="shared" si="0"/>
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="H60" s="4" t="s">
         <v>732</v>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="G61" s="3">
         <f t="shared" si="0"/>
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="H61" t="s">
         <v>71</v>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="G62" s="3">
         <f t="shared" si="0"/>
-        <v>-4.1999999999999993</v>
+        <v>-3.9999999999999991</v>
       </c>
       <c r="I62" s="6" t="s">
         <v>757</v>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="G63" s="3">
         <f t="shared" si="0"/>
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="H63" t="s">
         <v>73</v>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="G64" s="3">
         <f t="shared" si="0"/>
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="H64" t="s">
         <v>74</v>
@@ -6987,7 +6987,7 @@
       </c>
       <c r="G65" s="3">
         <f t="shared" si="0"/>
-        <v>56.9</v>
+        <v>57.1</v>
       </c>
       <c r="H65" t="s">
         <v>75</v>
@@ -7042,7 +7042,7 @@
       </c>
       <c r="G66" s="3">
         <f t="shared" si="0"/>
-        <v>43.1</v>
+        <v>43.300000000000004</v>
       </c>
       <c r="H66" t="s">
         <v>76</v>
@@ -7097,8 +7097,8 @@
         <v>10.100000000000001</v>
       </c>
       <c r="G67" s="3">
-        <f t="shared" ref="G67:G130" si="1">E67+6.5+1.5</f>
-        <v>11.9</v>
+        <f t="shared" ref="G67:G130" si="1">E67+6.7+1.5</f>
+        <v>12.1</v>
       </c>
       <c r="H67" t="s">
         <v>77</v>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="G68" s="3">
         <f t="shared" si="1"/>
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="H68" t="s">
         <v>78</v>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="G69" s="3">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="H69" t="s">
         <v>79</v>
@@ -7263,7 +7263,7 @@
       </c>
       <c r="G70" s="3">
         <f t="shared" si="1"/>
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="H70" s="4" t="s">
         <v>761</v>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="G71" s="3">
         <f t="shared" si="1"/>
-        <v>20.100000000000001</v>
+        <v>20.3</v>
       </c>
       <c r="H71" t="s">
         <v>81</v>
@@ -7374,7 +7374,7 @@
       </c>
       <c r="G72" s="3">
         <f t="shared" si="1"/>
-        <v>26.2</v>
+        <v>26.4</v>
       </c>
       <c r="H72" t="s">
         <v>82</v>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="G73" s="3">
         <f t="shared" si="1"/>
-        <v>26.2</v>
+        <v>26.4</v>
       </c>
       <c r="H73" t="s">
         <v>83</v>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="G74" s="3">
         <f t="shared" si="1"/>
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
       <c r="H74" t="s">
         <v>84</v>
@@ -7539,7 +7539,7 @@
       </c>
       <c r="G75" s="3">
         <f t="shared" si="1"/>
-        <v>63.9</v>
+        <v>64.099999999999994</v>
       </c>
       <c r="H75" s="4" t="s">
         <v>886</v>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="G76" s="3">
         <f t="shared" si="1"/>
-        <v>47.8</v>
+        <v>48</v>
       </c>
       <c r="H76" t="s">
         <v>86</v>
@@ -7649,7 +7649,7 @@
       </c>
       <c r="G77" s="3">
         <f t="shared" si="1"/>
-        <v>-1.6999999999999993</v>
+        <v>-1.4999999999999991</v>
       </c>
       <c r="H77" s="4" t="s">
         <v>889</v>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="G78" s="3">
         <f t="shared" si="1"/>
-        <v>-10.3</v>
+        <v>-10.100000000000001</v>
       </c>
       <c r="H78" s="4" t="s">
         <v>890</v>
@@ -7759,7 +7759,7 @@
       </c>
       <c r="G79" s="3">
         <f t="shared" si="1"/>
-        <v>-1.0999999999999996</v>
+        <v>-0.89999999999999947</v>
       </c>
       <c r="H79" s="4" t="s">
         <v>891</v>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="G80" s="3">
         <f t="shared" si="1"/>
-        <v>27.8</v>
+        <v>28</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>90</v>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="G81" s="3">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>91</v>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="G82" s="3">
         <f t="shared" si="1"/>
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H82" s="4" t="s">
         <v>894</v>
@@ -7979,7 +7979,7 @@
       </c>
       <c r="G83" s="3">
         <f t="shared" si="1"/>
-        <v>30.9</v>
+        <v>31.099999999999998</v>
       </c>
       <c r="H83" s="4" t="s">
         <v>974</v>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="G84" s="3">
         <f t="shared" si="1"/>
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="H84" t="s">
         <v>94</v>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="G85" s="3">
         <f t="shared" si="1"/>
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="H85" t="s">
         <v>95</v>
@@ -8144,7 +8144,7 @@
       </c>
       <c r="G86" s="3">
         <f t="shared" si="1"/>
-        <v>31.4</v>
+        <v>31.599999999999998</v>
       </c>
       <c r="H86" t="s">
         <v>96</v>
@@ -8199,7 +8199,7 @@
       </c>
       <c r="G87" s="3">
         <f t="shared" si="1"/>
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="H87" t="s">
         <v>97</v>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="G88" s="3">
         <f t="shared" si="1"/>
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="K88" t="s">
         <v>675</v>
@@ -8304,7 +8304,7 @@
       </c>
       <c r="G89" s="3">
         <f t="shared" si="1"/>
-        <v>-28.900000000000006</v>
+        <v>-28.700000000000006</v>
       </c>
       <c r="K89" t="s">
         <v>673</v>
@@ -8354,7 +8354,7 @@
       </c>
       <c r="G90" s="3">
         <f t="shared" si="1"/>
-        <v>-10</v>
+        <v>-9.8000000000000007</v>
       </c>
       <c r="K90" t="s">
         <v>673</v>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="G91" s="3">
         <f t="shared" si="1"/>
-        <v>-12.899999999999999</v>
+        <v>-12.7</v>
       </c>
       <c r="K91" t="s">
         <v>676</v>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="G92" s="3">
         <f t="shared" si="1"/>
-        <v>-3.8000000000000043</v>
+        <v>-3.6000000000000041</v>
       </c>
       <c r="K92" t="s">
         <v>676</v>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="G93" s="3">
         <f t="shared" si="1"/>
-        <v>-13.399999999999999</v>
+        <v>-13.2</v>
       </c>
       <c r="K93" t="s">
         <v>676</v>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="G94" s="3">
         <f t="shared" si="1"/>
-        <v>-22</v>
+        <v>-21.8</v>
       </c>
       <c r="K94" t="s">
         <v>676</v>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="G95" s="3">
         <f t="shared" si="1"/>
-        <v>-4.3999999999999986</v>
+        <v>-4.1999999999999984</v>
       </c>
       <c r="K95" t="s">
         <v>676</v>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="G96" s="3">
         <f t="shared" si="1"/>
-        <v>-8.0999999999999943</v>
+        <v>-7.899999999999995</v>
       </c>
       <c r="K96" t="s">
         <v>676</v>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="G97" s="3">
         <f t="shared" si="1"/>
-        <v>-9.7000000000000028</v>
+        <v>-9.5000000000000036</v>
       </c>
       <c r="K97" t="s">
         <v>676</v>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="G98" s="3">
         <f t="shared" si="1"/>
-        <v>31.9</v>
+        <v>32.099999999999994</v>
       </c>
       <c r="K98" t="s">
         <v>676</v>
@@ -8804,7 +8804,7 @@
       </c>
       <c r="G99" s="3">
         <f t="shared" si="1"/>
-        <v>-7.7000000000000028</v>
+        <v>-7.5000000000000036</v>
       </c>
       <c r="K99" t="s">
         <v>676</v>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="G100" s="3">
         <f t="shared" si="1"/>
-        <v>-7.2999999999999972</v>
+        <v>-7.0999999999999979</v>
       </c>
       <c r="K100" t="s">
         <v>676</v>
@@ -8904,7 +8904,7 @@
       </c>
       <c r="G101" s="3">
         <f t="shared" si="1"/>
-        <v>-5.7999999999999972</v>
+        <v>-5.599999999999997</v>
       </c>
       <c r="K101" t="s">
         <v>676</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="G102" s="3">
         <f t="shared" si="1"/>
-        <v>-2.5</v>
+        <v>-2.2999999999999998</v>
       </c>
       <c r="K102" t="s">
         <v>676</v>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="G103" s="3">
         <f t="shared" si="1"/>
-        <v>-11.800000000000004</v>
+        <v>-11.600000000000005</v>
       </c>
       <c r="K103" t="s">
         <v>676</v>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="G104" s="3">
         <f t="shared" si="1"/>
-        <v>-5.6000000000000014</v>
+        <v>-5.4000000000000012</v>
       </c>
       <c r="K104" t="s">
         <v>676</v>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="G105" s="3">
         <f t="shared" si="1"/>
-        <v>-14</v>
+        <v>-13.8</v>
       </c>
       <c r="K105" t="s">
         <v>676</v>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="G106" s="3">
         <f t="shared" si="1"/>
-        <v>-8.8999999999999986</v>
+        <v>-8.6999999999999993</v>
       </c>
       <c r="K106" t="s">
         <v>676</v>
@@ -9204,7 +9204,7 @@
       </c>
       <c r="G107" s="3">
         <f t="shared" si="1"/>
-        <v>-23.000000000000007</v>
+        <v>-22.800000000000008</v>
       </c>
       <c r="K107" t="s">
         <v>676</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="G108" s="3">
         <f t="shared" si="1"/>
-        <v>45.000000000000007</v>
+        <v>45.20000000000001</v>
       </c>
       <c r="K108" t="s">
         <v>676</v>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="G109" s="3">
         <f t="shared" si="1"/>
-        <v>-8.2000000000000028</v>
+        <v>-8.0000000000000036</v>
       </c>
       <c r="K109" t="s">
         <v>676</v>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="G110" s="3">
         <f t="shared" si="1"/>
-        <v>-2.5</v>
+        <v>-2.2999999999999998</v>
       </c>
       <c r="K110" t="s">
         <v>676</v>
@@ -9404,7 +9404,7 @@
       </c>
       <c r="G111" s="3">
         <f t="shared" si="1"/>
-        <v>21.799999999999997</v>
+        <v>21.999999999999996</v>
       </c>
       <c r="K111" t="s">
         <v>676</v>
@@ -9454,7 +9454,7 @@
       </c>
       <c r="G112" s="3">
         <f t="shared" si="1"/>
-        <v>46.6</v>
+        <v>46.800000000000004</v>
       </c>
       <c r="K112" t="s">
         <v>676</v>
@@ -9504,7 +9504,7 @@
       </c>
       <c r="G113" s="3">
         <f t="shared" si="1"/>
-        <v>-1.2000000000000028</v>
+        <v>-1.0000000000000027</v>
       </c>
       <c r="K113" t="s">
         <v>676</v>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="G114" s="3">
         <f t="shared" si="1"/>
-        <v>-10.300000000000004</v>
+        <v>-10.100000000000005</v>
       </c>
       <c r="K114" t="s">
         <v>676</v>
@@ -9604,7 +9604,7 @@
       </c>
       <c r="G115" s="3">
         <f t="shared" si="1"/>
-        <v>-6.5</v>
+        <v>-6.3</v>
       </c>
       <c r="K115" t="s">
         <v>676</v>
@@ -9654,7 +9654,7 @@
       </c>
       <c r="G116" s="3">
         <f t="shared" si="1"/>
-        <v>-17.400000000000006</v>
+        <v>-17.200000000000006</v>
       </c>
       <c r="K116" t="s">
         <v>676</v>
@@ -9703,7 +9703,7 @@
       </c>
       <c r="G117" s="3">
         <f t="shared" si="1"/>
-        <v>-7.6999999999999993</v>
+        <v>-7.5</v>
       </c>
       <c r="H117" s="4" t="s">
         <v>823</v>
@@ -9758,7 +9758,7 @@
       </c>
       <c r="G118" s="3">
         <f t="shared" si="1"/>
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="H118" t="s">
         <v>127</v>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="G119" s="3">
         <f t="shared" si="1"/>
-        <v>-23</v>
+        <v>-22.8</v>
       </c>
       <c r="H119" s="4" t="s">
         <v>130</v>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="G120" s="3">
         <f t="shared" si="1"/>
-        <v>60.2</v>
+        <v>60.400000000000006</v>
       </c>
       <c r="H120" t="s">
         <v>131</v>
@@ -9925,7 +9925,7 @@
       </c>
       <c r="G121" s="3">
         <f t="shared" si="1"/>
-        <v>80.099999999999994</v>
+        <v>80.3</v>
       </c>
       <c r="H121" t="s">
         <v>133</v>
@@ -9981,7 +9981,7 @@
       </c>
       <c r="G122" s="3">
         <f t="shared" si="1"/>
-        <v>58</v>
+        <v>58.2</v>
       </c>
       <c r="H122" t="s">
         <v>135</v>
@@ -10036,7 +10036,7 @@
       </c>
       <c r="G123" s="3">
         <f t="shared" si="1"/>
-        <v>-13.100000000000001</v>
+        <v>-12.900000000000002</v>
       </c>
       <c r="H123" s="4" t="s">
         <v>826</v>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="G124" s="3">
         <f t="shared" si="1"/>
-        <v>-23.3</v>
+        <v>-23.1</v>
       </c>
       <c r="H124" s="4" t="s">
         <v>138</v>
@@ -10148,7 +10148,7 @@
       </c>
       <c r="G125" s="3">
         <f t="shared" si="1"/>
-        <v>-26.9</v>
+        <v>-26.7</v>
       </c>
       <c r="H125" s="4" t="s">
         <v>140</v>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="G126" s="3">
         <f t="shared" si="1"/>
-        <v>-13.899999999999999</v>
+        <v>-13.7</v>
       </c>
       <c r="H126" s="4" t="s">
         <v>827</v>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="G127" s="3">
         <f t="shared" si="1"/>
-        <v>-15.7</v>
+        <v>-15.5</v>
       </c>
       <c r="H127" s="4" t="s">
         <v>144</v>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="G128" s="3">
         <f t="shared" si="1"/>
-        <v>-6.1</v>
+        <v>-5.8999999999999995</v>
       </c>
       <c r="H128" s="4" t="s">
         <v>829</v>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="G129" s="3">
         <f t="shared" si="1"/>
-        <v>50.4</v>
+        <v>50.6</v>
       </c>
       <c r="H129" s="4" t="s">
         <v>146</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="G130" s="3">
         <f t="shared" si="1"/>
-        <v>-29.4</v>
+        <v>-29.2</v>
       </c>
       <c r="H130" s="4" t="s">
         <v>149</v>
@@ -10480,8 +10480,8 @@
         <v>29.4</v>
       </c>
       <c r="G131" s="3">
-        <f t="shared" ref="G131:G194" si="2">E131+6.5+1.5</f>
-        <v>32.700000000000003</v>
+        <f t="shared" ref="G131:G194" si="2">E131+6.7+1.5</f>
+        <v>32.9</v>
       </c>
       <c r="H131" s="6" t="s">
         <v>150</v>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="G132" s="3">
         <f t="shared" si="2"/>
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="H132" s="6" t="s">
         <v>151</v>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="G133" s="3">
         <f t="shared" si="2"/>
-        <v>-37.1</v>
+        <v>-36.9</v>
       </c>
       <c r="H133" s="4" t="s">
         <v>153</v>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="G134" s="3">
         <f t="shared" si="2"/>
-        <v>-18.7</v>
+        <v>-18.5</v>
       </c>
       <c r="H134" s="4" t="s">
         <v>155</v>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="G135" s="3">
         <f t="shared" si="2"/>
-        <v>40</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="H135" s="6" t="s">
         <v>156</v>
@@ -10757,7 +10757,7 @@
       </c>
       <c r="G136" s="3">
         <f t="shared" si="2"/>
-        <v>41.1</v>
+        <v>41.300000000000004</v>
       </c>
       <c r="H136" s="4" t="s">
         <v>159</v>
@@ -10813,7 +10813,7 @@
       </c>
       <c r="G137" s="3">
         <f t="shared" si="2"/>
-        <v>39.200000000000003</v>
+        <v>39.4</v>
       </c>
       <c r="H137" s="6" t="s">
         <v>161</v>
@@ -10869,7 +10869,7 @@
       </c>
       <c r="G138" s="3">
         <f t="shared" si="2"/>
-        <v>36.299999999999997</v>
+        <v>36.5</v>
       </c>
       <c r="H138" s="4" t="s">
         <v>164</v>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="G139" s="3">
         <f t="shared" si="2"/>
-        <v>45.2</v>
+        <v>45.400000000000006</v>
       </c>
       <c r="H139" s="6" t="s">
         <v>166</v>
@@ -10981,7 +10981,7 @@
       </c>
       <c r="G140" s="3">
         <f t="shared" si="2"/>
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="H140" s="6" t="s">
         <v>168</v>
@@ -11037,7 +11037,7 @@
       </c>
       <c r="G141" s="3">
         <f t="shared" si="2"/>
-        <v>73.5</v>
+        <v>73.7</v>
       </c>
       <c r="H141" s="4" t="s">
         <v>171</v>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="G142" s="3">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="H142" s="4" t="s">
         <v>174</v>
@@ -11149,7 +11149,7 @@
       </c>
       <c r="G143" s="3">
         <f t="shared" si="2"/>
-        <v>44.5</v>
+        <v>44.7</v>
       </c>
       <c r="H143" s="4" t="s">
         <v>177</v>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="G144" s="3">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>30.2</v>
       </c>
       <c r="H144" s="6" t="s">
         <v>179</v>
@@ -11261,7 +11261,7 @@
       </c>
       <c r="G145" s="3">
         <f t="shared" si="2"/>
-        <v>19.399999999999999</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="H145" s="6" t="s">
         <v>181</v>
@@ -11317,7 +11317,7 @@
       </c>
       <c r="G146" s="3">
         <f t="shared" si="2"/>
-        <v>-35.5</v>
+        <v>-35.299999999999997</v>
       </c>
       <c r="H146" s="4" t="s">
         <v>184</v>
@@ -11372,7 +11372,7 @@
       </c>
       <c r="G147" s="3">
         <f t="shared" si="2"/>
-        <v>18.7</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="H147" s="6" t="s">
         <v>185</v>
@@ -11428,7 +11428,7 @@
       </c>
       <c r="G148" s="3">
         <f t="shared" si="2"/>
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
       <c r="H148" s="6" t="s">
         <v>187</v>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="G149" s="3">
         <f t="shared" si="2"/>
-        <v>-31.9</v>
+        <v>-31.699999999999996</v>
       </c>
       <c r="H149" s="4" t="s">
         <v>190</v>
@@ -11540,7 +11540,7 @@
       </c>
       <c r="G150" s="3">
         <f t="shared" si="2"/>
-        <v>-14.7</v>
+        <v>-14.5</v>
       </c>
       <c r="H150" s="4" t="s">
         <v>192</v>
@@ -11596,7 +11596,7 @@
       </c>
       <c r="G151" s="3">
         <f t="shared" si="2"/>
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="H151" t="s">
         <v>193</v>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="G152" s="3">
         <f t="shared" si="2"/>
-        <v>8.3000000000000007</v>
+        <v>8.5</v>
       </c>
       <c r="H152" t="s">
         <v>195</v>
@@ -11708,7 +11708,7 @@
       </c>
       <c r="G153" s="3">
         <f t="shared" si="2"/>
-        <v>-18.399999999999999</v>
+        <v>-18.2</v>
       </c>
       <c r="H153" s="4" t="s">
         <v>198</v>
@@ -11764,7 +11764,7 @@
       </c>
       <c r="G154" s="3">
         <f t="shared" si="2"/>
-        <v>-23.6</v>
+        <v>-23.400000000000002</v>
       </c>
       <c r="H154" s="4" t="s">
         <v>200</v>
@@ -11820,7 +11820,7 @@
       </c>
       <c r="G155" s="3">
         <f t="shared" si="2"/>
-        <v>-21.7</v>
+        <v>-21.5</v>
       </c>
       <c r="H155" s="4" t="s">
         <v>202</v>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="G156" s="3">
         <f t="shared" si="2"/>
-        <v>-8.6999999999999993</v>
+        <v>-8.5</v>
       </c>
       <c r="H156" s="4" t="s">
         <v>204</v>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="G157" s="3">
         <f t="shared" si="2"/>
-        <v>-25.1</v>
+        <v>-24.900000000000002</v>
       </c>
       <c r="H157" s="4" t="s">
         <v>206</v>
@@ -11988,7 +11988,7 @@
       </c>
       <c r="G158" s="3">
         <f t="shared" si="2"/>
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
       <c r="H158" s="6" t="s">
         <v>207</v>
@@ -12044,7 +12044,7 @@
       </c>
       <c r="G159" s="3">
         <f t="shared" si="2"/>
-        <v>-28.5</v>
+        <v>-28.3</v>
       </c>
       <c r="H159" s="4" t="s">
         <v>210</v>
@@ -12100,7 +12100,7 @@
       </c>
       <c r="G160" s="3">
         <f t="shared" si="2"/>
-        <v>-22.4</v>
+        <v>-22.2</v>
       </c>
       <c r="H160" s="4" t="s">
         <v>212</v>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="G161" s="3">
         <f t="shared" si="2"/>
-        <v>-0.5</v>
+        <v>-0.29999999999999982</v>
       </c>
       <c r="H161" s="4" t="s">
         <v>718</v>
@@ -12212,7 +12212,7 @@
       </c>
       <c r="G162" s="3">
         <f t="shared" si="2"/>
-        <v>-2</v>
+        <v>-1.7999999999999998</v>
       </c>
       <c r="H162" s="4" t="s">
         <v>720</v>
@@ -12268,7 +12268,7 @@
       </c>
       <c r="G163" s="3">
         <f t="shared" si="2"/>
-        <v>3.5999999999999996</v>
+        <v>3.8</v>
       </c>
       <c r="H163" s="4" t="s">
         <v>722</v>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="G164" s="3">
         <f t="shared" si="2"/>
-        <v>-23.5</v>
+        <v>-23.3</v>
       </c>
       <c r="H164" s="4" t="s">
         <v>731</v>
@@ -12380,7 +12380,7 @@
       </c>
       <c r="G165" s="3">
         <f t="shared" si="2"/>
-        <v>-23.3</v>
+        <v>-23.1</v>
       </c>
       <c r="H165" s="4" t="s">
         <v>944</v>
@@ -12435,7 +12435,7 @@
       </c>
       <c r="G166" s="3">
         <f t="shared" si="2"/>
-        <v>-11.7</v>
+        <v>-11.5</v>
       </c>
       <c r="H166" s="4" t="s">
         <v>914</v>
@@ -12490,7 +12490,7 @@
       </c>
       <c r="G167" s="3">
         <f t="shared" si="2"/>
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="H167" s="6" t="s">
         <v>219</v>
@@ -12545,7 +12545,7 @@
       </c>
       <c r="G168" s="3">
         <f t="shared" si="2"/>
-        <v>-15.3</v>
+        <v>-15.100000000000001</v>
       </c>
       <c r="H168" s="4" t="s">
         <v>945</v>
@@ -12600,7 +12600,7 @@
       </c>
       <c r="G169" s="3">
         <f t="shared" si="2"/>
-        <v>-39.299999999999997</v>
+        <v>-39.099999999999994</v>
       </c>
       <c r="H169" s="4" t="s">
         <v>222</v>
@@ -12655,7 +12655,7 @@
       </c>
       <c r="G170" s="3">
         <f t="shared" si="2"/>
-        <v>-33.299999999999997</v>
+        <v>-33.099999999999994</v>
       </c>
       <c r="H170" s="4" t="s">
         <v>224</v>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="G171" s="3">
         <f t="shared" si="2"/>
-        <v>26.9</v>
+        <v>27.099999999999998</v>
       </c>
       <c r="H171" t="s">
         <v>225</v>
@@ -12766,7 +12766,7 @@
       </c>
       <c r="G172" s="3">
         <f t="shared" si="2"/>
-        <v>-27.5</v>
+        <v>-27.3</v>
       </c>
       <c r="H172" s="4" t="s">
         <v>228</v>
@@ -12822,7 +12822,7 @@
       </c>
       <c r="G173" s="3">
         <f t="shared" si="2"/>
-        <v>-55.9</v>
+        <v>-55.699999999999996</v>
       </c>
       <c r="H173" s="4" t="s">
         <v>231</v>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="G174" s="3">
         <f t="shared" si="2"/>
-        <v>-7</v>
+        <v>-6.8000000000000007</v>
       </c>
       <c r="H174" s="4" t="s">
         <v>233</v>
@@ -12934,7 +12934,7 @@
       </c>
       <c r="G175" s="3">
         <f t="shared" si="2"/>
-        <v>-30.4</v>
+        <v>-30.2</v>
       </c>
       <c r="K175" t="s">
         <v>673</v>
@@ -12972,7 +12972,7 @@
       </c>
       <c r="G176" s="3">
         <f t="shared" si="2"/>
-        <v>55.699999999999996</v>
+        <v>55.9</v>
       </c>
       <c r="K176" t="s">
         <v>673</v>
@@ -13010,7 +13010,7 @@
       </c>
       <c r="G177" s="3">
         <f t="shared" si="2"/>
-        <v>-28.200000000000003</v>
+        <v>-28.000000000000004</v>
       </c>
       <c r="K177" t="s">
         <v>673</v>
@@ -13048,7 +13048,7 @@
       </c>
       <c r="G178" s="3">
         <f t="shared" si="2"/>
-        <v>-26.200000000000003</v>
+        <v>-26.000000000000004</v>
       </c>
       <c r="K178" t="s">
         <v>673</v>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="G179" s="3">
         <f t="shared" si="2"/>
-        <v>-26.000000000000007</v>
+        <v>-25.800000000000008</v>
       </c>
       <c r="K179" t="s">
         <v>673</v>
@@ -13124,7 +13124,7 @@
       </c>
       <c r="G180" s="3">
         <f t="shared" si="2"/>
-        <v>-23.799999999999997</v>
+        <v>-23.599999999999998</v>
       </c>
       <c r="K180" t="s">
         <v>673</v>
@@ -13161,7 +13161,7 @@
       </c>
       <c r="G181" s="3">
         <f t="shared" si="2"/>
-        <v>29.8</v>
+        <v>30</v>
       </c>
       <c r="H181" t="s">
         <v>241</v>
@@ -13216,7 +13216,7 @@
       </c>
       <c r="G182" s="3">
         <f t="shared" si="2"/>
-        <v>-1.5</v>
+        <v>-1.2999999999999998</v>
       </c>
       <c r="H182" s="4" t="s">
         <v>830</v>
@@ -13271,7 +13271,7 @@
       </c>
       <c r="G183" s="3">
         <f t="shared" si="2"/>
-        <v>-8.8000000000000007</v>
+        <v>-8.6000000000000014</v>
       </c>
       <c r="H183" s="4" t="s">
         <v>864</v>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="G184" s="3">
         <f t="shared" si="2"/>
-        <v>26.3</v>
+        <v>26.5</v>
       </c>
       <c r="H184" t="s">
         <v>244</v>
@@ -13381,7 +13381,7 @@
       </c>
       <c r="G185" s="3">
         <f t="shared" si="2"/>
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="H185" t="s">
         <v>245</v>
@@ -13436,7 +13436,7 @@
       </c>
       <c r="G186" s="3">
         <f t="shared" si="2"/>
-        <v>81.2</v>
+        <v>81.400000000000006</v>
       </c>
       <c r="H186" t="s">
         <v>246</v>
@@ -13491,7 +13491,7 @@
       </c>
       <c r="G187" s="3">
         <f t="shared" si="2"/>
-        <v>41.1</v>
+        <v>41.300000000000004</v>
       </c>
       <c r="H187" s="4" t="s">
         <v>865</v>
@@ -13546,7 +13546,7 @@
       </c>
       <c r="G188" s="3">
         <f t="shared" si="2"/>
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="H188" t="s">
         <v>248</v>
@@ -13601,7 +13601,7 @@
       </c>
       <c r="G189" s="3">
         <f t="shared" si="2"/>
-        <v>66.599999999999994</v>
+        <v>66.8</v>
       </c>
       <c r="H189" t="s">
         <v>249</v>
@@ -13656,7 +13656,7 @@
       </c>
       <c r="G190" s="3">
         <f t="shared" si="2"/>
-        <v>63.8</v>
+        <v>64</v>
       </c>
       <c r="H190" t="s">
         <v>250</v>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="G191" s="3">
         <f t="shared" si="2"/>
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="K191" t="s">
         <v>662</v>
@@ -13760,7 +13760,7 @@
       </c>
       <c r="G192" s="3">
         <f t="shared" si="2"/>
-        <v>31.6</v>
+        <v>31.8</v>
       </c>
       <c r="K192" t="s">
         <v>662</v>
@@ -13809,7 +13809,7 @@
       </c>
       <c r="G193" s="3">
         <f t="shared" si="2"/>
-        <v>26.8</v>
+        <v>27</v>
       </c>
       <c r="K193" t="s">
         <v>662</v>
@@ -13858,7 +13858,7 @@
       </c>
       <c r="G194" s="3">
         <f t="shared" si="2"/>
-        <v>27.6</v>
+        <v>27.8</v>
       </c>
       <c r="K194" t="s">
         <v>662</v>
@@ -13906,8 +13906,8 @@
         <v>50.900000000000006</v>
       </c>
       <c r="G195" s="3">
-        <f t="shared" ref="G195:G258" si="3">E195+6.5+1.5</f>
-        <v>52.9</v>
+        <f t="shared" ref="G195:G258" si="3">E195+6.7+1.5</f>
+        <v>53.1</v>
       </c>
       <c r="K195" t="s">
         <v>662</v>
@@ -13956,7 +13956,7 @@
       </c>
       <c r="G196" s="3">
         <f t="shared" si="3"/>
-        <v>28.6</v>
+        <v>28.8</v>
       </c>
       <c r="K196" t="s">
         <v>662</v>
@@ -14005,7 +14005,7 @@
       </c>
       <c r="G197" s="3">
         <f t="shared" si="3"/>
-        <v>70.7</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="K197" t="s">
         <v>662</v>
@@ -14054,7 +14054,7 @@
       </c>
       <c r="G198" s="3">
         <f t="shared" si="3"/>
-        <v>34.200000000000003</v>
+        <v>34.4</v>
       </c>
       <c r="K198" t="s">
         <v>662</v>
@@ -14103,7 +14103,7 @@
       </c>
       <c r="G199" s="3">
         <f t="shared" si="3"/>
-        <v>18.7</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="K199" t="s">
         <v>662</v>
@@ -14152,7 +14152,7 @@
       </c>
       <c r="G200" s="3">
         <f t="shared" si="3"/>
-        <v>-13.2</v>
+        <v>-13</v>
       </c>
       <c r="H200" s="4" t="s">
         <v>943</v>
@@ -14207,7 +14207,7 @@
       </c>
       <c r="G201" s="3">
         <f t="shared" si="3"/>
-        <v>-21.9</v>
+        <v>-21.7</v>
       </c>
       <c r="H201" s="4" t="s">
         <v>961</v>
@@ -14262,7 +14262,7 @@
       </c>
       <c r="G202" s="3">
         <f t="shared" si="3"/>
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="H202" t="s">
         <v>261</v>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="G203" s="3">
         <f t="shared" si="3"/>
-        <v>2.2999999999999998</v>
+        <v>2.5</v>
       </c>
       <c r="H203" s="4" t="s">
         <v>935</v>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="G204" s="3">
         <f t="shared" si="3"/>
-        <v>-19.100000000000001</v>
+        <v>-18.900000000000002</v>
       </c>
       <c r="H204" s="4" t="s">
         <v>908</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="G205" s="3">
         <f t="shared" si="3"/>
-        <v>31.2</v>
+        <v>31.4</v>
       </c>
       <c r="H205" t="s">
         <v>264</v>
@@ -14482,7 +14482,7 @@
       </c>
       <c r="G206" s="3">
         <f t="shared" si="3"/>
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="H206" s="4" t="s">
         <v>929</v>
@@ -14537,7 +14537,7 @@
       </c>
       <c r="G207" s="3">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H207" t="s">
         <v>266</v>
@@ -14592,7 +14592,7 @@
       </c>
       <c r="G208" s="3">
         <f t="shared" si="3"/>
-        <v>-24.299999999999997</v>
+        <v>-24.099999999999998</v>
       </c>
       <c r="H208" s="4" t="s">
         <v>910</v>
@@ -14647,7 +14647,7 @@
       </c>
       <c r="G209" s="3">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>1.7000000000000002</v>
       </c>
       <c r="H209" s="4" t="s">
         <v>940</v>
@@ -14702,7 +14702,7 @@
       </c>
       <c r="G210" s="3">
         <f t="shared" si="3"/>
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="H210" s="4" t="s">
         <v>920</v>
@@ -14757,7 +14757,7 @@
       </c>
       <c r="G211" s="3">
         <f t="shared" si="3"/>
-        <v>45.7</v>
+        <v>45.900000000000006</v>
       </c>
       <c r="H211" t="s">
         <v>270</v>
@@ -14812,7 +14812,7 @@
       </c>
       <c r="G212" s="3">
         <f t="shared" si="3"/>
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
       <c r="H212" s="4" t="s">
         <v>946</v>
@@ -14867,7 +14867,7 @@
       </c>
       <c r="G213" s="3">
         <f t="shared" si="3"/>
-        <v>-4</v>
+        <v>-3.8</v>
       </c>
       <c r="H213" s="4" t="s">
         <v>982</v>
@@ -14922,7 +14922,7 @@
       </c>
       <c r="G214" s="3">
         <f t="shared" si="3"/>
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="H214" s="4" t="s">
         <v>980</v>
@@ -14977,7 +14977,7 @@
       </c>
       <c r="G215" s="3">
         <f t="shared" si="3"/>
-        <v>29.3</v>
+        <v>29.5</v>
       </c>
       <c r="H215" s="6" t="s">
         <v>274</v>
@@ -15032,7 +15032,7 @@
       </c>
       <c r="G216" s="3">
         <f t="shared" si="3"/>
-        <v>43.7</v>
+        <v>43.900000000000006</v>
       </c>
       <c r="H216" t="s">
         <v>275</v>
@@ -15087,7 +15087,7 @@
       </c>
       <c r="G217" s="3">
         <f t="shared" si="3"/>
-        <v>69.900000000000006</v>
+        <v>70.099999999999994</v>
       </c>
       <c r="H217" s="6" t="s">
         <v>276</v>
@@ -15142,7 +15142,7 @@
       </c>
       <c r="G218" s="3">
         <f t="shared" si="3"/>
-        <v>-11.7</v>
+        <v>-11.5</v>
       </c>
       <c r="H218" s="4" t="s">
         <v>983</v>
@@ -15197,7 +15197,7 @@
       </c>
       <c r="G219" s="3">
         <f t="shared" si="3"/>
-        <v>-28.5</v>
+        <v>-28.3</v>
       </c>
       <c r="H219" s="4" t="s">
         <v>986</v>
@@ -15252,7 +15252,7 @@
       </c>
       <c r="G220" s="3">
         <f t="shared" si="3"/>
-        <v>-6.3000000000000007</v>
+        <v>-6.1000000000000005</v>
       </c>
       <c r="H220" t="s">
         <v>981</v>
@@ -15307,7 +15307,7 @@
       </c>
       <c r="G221" s="3">
         <f t="shared" si="3"/>
-        <v>-29</v>
+        <v>-28.8</v>
       </c>
       <c r="H221" s="4" t="s">
         <v>281</v>
@@ -15362,7 +15362,7 @@
       </c>
       <c r="G222" s="3">
         <f t="shared" si="3"/>
-        <v>28.4</v>
+        <v>28.599999999999998</v>
       </c>
       <c r="H222" t="s">
         <v>282</v>
@@ -15418,7 +15418,7 @@
       </c>
       <c r="G223" s="3">
         <f t="shared" si="3"/>
-        <v>-21.2</v>
+        <v>-21</v>
       </c>
       <c r="H223" s="4" t="s">
         <v>285</v>
@@ -15473,7 +15473,7 @@
       </c>
       <c r="G224" s="3">
         <f t="shared" si="3"/>
-        <v>-34.5</v>
+        <v>-34.299999999999997</v>
       </c>
       <c r="H224" s="4" t="s">
         <v>287</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="G225" s="3">
         <f t="shared" si="3"/>
-        <v>65.5</v>
+        <v>65.7</v>
       </c>
       <c r="H225" s="6" t="s">
         <v>288</v>
@@ -15583,7 +15583,7 @@
       </c>
       <c r="G226" s="3">
         <f t="shared" si="3"/>
-        <v>-3.3000000000000007</v>
+        <v>-3.1000000000000005</v>
       </c>
       <c r="H226" s="4" t="s">
         <v>941</v>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="G227" s="3">
         <f t="shared" si="3"/>
-        <v>-11.899999999999999</v>
+        <v>-11.7</v>
       </c>
       <c r="H227" s="4" t="s">
         <v>919</v>
@@ -15693,7 +15693,7 @@
       </c>
       <c r="G228" s="3">
         <f t="shared" si="3"/>
-        <v>-13</v>
+        <v>-12.8</v>
       </c>
       <c r="H228" s="4" t="s">
         <v>938</v>
@@ -15748,7 +15748,7 @@
       </c>
       <c r="G229" s="3">
         <f t="shared" si="3"/>
-        <v>-10.3</v>
+        <v>-10.100000000000001</v>
       </c>
       <c r="H229" t="s">
         <v>916</v>
@@ -15803,7 +15803,7 @@
       </c>
       <c r="G230" s="3">
         <f t="shared" si="3"/>
-        <v>-18.600000000000001</v>
+        <v>-18.400000000000002</v>
       </c>
       <c r="H230" s="4" t="s">
         <v>924</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="G231" s="3">
         <f t="shared" si="3"/>
-        <v>-34.6</v>
+        <v>-34.4</v>
       </c>
       <c r="H231" s="4" t="s">
         <v>917</v>
@@ -15913,7 +15913,7 @@
       </c>
       <c r="G232" s="3">
         <f t="shared" si="3"/>
-        <v>-45.8</v>
+        <v>-45.599999999999994</v>
       </c>
       <c r="H232" s="4" t="s">
         <v>939</v>
@@ -15968,7 +15968,7 @@
       </c>
       <c r="G233" s="3">
         <f t="shared" si="3"/>
-        <v>-3.5</v>
+        <v>-3.3</v>
       </c>
       <c r="H233" s="4" t="s">
         <v>765</v>
@@ -16024,7 +16024,7 @@
       </c>
       <c r="G234" s="3">
         <f t="shared" si="3"/>
-        <v>-21.5</v>
+        <v>-21.3</v>
       </c>
       <c r="H234" s="4" t="s">
         <v>764</v>
@@ -16080,7 +16080,7 @@
       </c>
       <c r="G235" s="3">
         <f t="shared" si="3"/>
-        <v>-5.0999999999999996</v>
+        <v>-4.8999999999999995</v>
       </c>
       <c r="H235" s="4" t="s">
         <v>299</v>
@@ -16135,7 +16135,7 @@
       </c>
       <c r="G236" s="3">
         <f t="shared" si="3"/>
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="H236" s="4" t="s">
         <v>301</v>
@@ -16191,7 +16191,7 @@
       </c>
       <c r="G237" s="3">
         <f t="shared" si="3"/>
-        <v>-45.8</v>
+        <v>-45.599999999999994</v>
       </c>
       <c r="H237" s="4" t="s">
         <v>304</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="G238" s="3">
         <f t="shared" si="3"/>
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="H238" s="6" t="s">
         <v>305</v>
@@ -16301,7 +16301,7 @@
       </c>
       <c r="G239" s="3">
         <f t="shared" si="3"/>
-        <v>-6</v>
+        <v>-5.8</v>
       </c>
       <c r="H239" s="4" t="s">
         <v>802</v>
@@ -16356,7 +16356,7 @@
       </c>
       <c r="G240" s="3">
         <f t="shared" si="3"/>
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="H240" s="6" t="s">
         <v>307</v>
@@ -16411,7 +16411,7 @@
       </c>
       <c r="G241" s="3">
         <f t="shared" si="3"/>
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="H241" t="s">
         <v>800</v>
@@ -16466,7 +16466,7 @@
       </c>
       <c r="G242" s="3">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="K242" t="s">
         <v>662</v>
@@ -16515,7 +16515,7 @@
       </c>
       <c r="G243" s="3">
         <f t="shared" si="3"/>
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="K243" t="s">
         <v>662</v>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="G244" s="3">
         <f t="shared" si="3"/>
-        <v>26.7</v>
+        <v>26.9</v>
       </c>
       <c r="H244" t="s">
         <v>311</v>
@@ -16620,7 +16620,7 @@
       </c>
       <c r="G245" s="3">
         <f t="shared" si="3"/>
-        <v>-4.5999999999999996</v>
+        <v>-4.3999999999999995</v>
       </c>
       <c r="H245" s="4" t="s">
         <v>707</v>
@@ -16675,7 +16675,7 @@
       </c>
       <c r="G246" s="3">
         <f t="shared" si="3"/>
-        <v>16.399999999999999</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="H246" t="s">
         <v>313</v>
@@ -16731,7 +16731,7 @@
       </c>
       <c r="G247" s="3">
         <f t="shared" si="3"/>
-        <v>-22.1</v>
+        <v>-21.900000000000002</v>
       </c>
       <c r="H247" s="4" t="s">
         <v>709</v>
@@ -16786,7 +16786,7 @@
       </c>
       <c r="G248" s="3">
         <f t="shared" si="3"/>
-        <v>9.8000000000000007</v>
+        <v>10</v>
       </c>
       <c r="H248" t="s">
         <v>315</v>
@@ -16842,7 +16842,7 @@
       </c>
       <c r="G249" s="3">
         <f t="shared" si="3"/>
-        <v>14.4</v>
+        <v>14.600000000000001</v>
       </c>
       <c r="H249" s="6" t="s">
         <v>316</v>
@@ -16898,7 +16898,7 @@
       </c>
       <c r="G250" s="3">
         <f t="shared" si="3"/>
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H250" s="4" t="s">
         <v>712</v>
@@ -16953,7 +16953,7 @@
       </c>
       <c r="G251" s="3">
         <f t="shared" si="3"/>
-        <v>32.200000000000003</v>
+        <v>32.4</v>
       </c>
       <c r="H251" t="s">
         <v>318</v>
@@ -17005,7 +17005,7 @@
       </c>
       <c r="G252" s="3">
         <f t="shared" si="3"/>
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="H252" t="s">
         <v>319</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="G253" s="3">
         <f t="shared" si="3"/>
-        <v>58.8</v>
+        <v>59</v>
       </c>
       <c r="H253" t="s">
         <v>320</v>
@@ -17116,7 +17116,7 @@
       </c>
       <c r="G254" s="3">
         <f t="shared" si="3"/>
-        <v>16.7</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="H254" t="s">
         <v>714</v>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="G255" s="3">
         <f t="shared" si="3"/>
-        <v>31.9</v>
+        <v>32.099999999999994</v>
       </c>
       <c r="H255" s="4" t="s">
         <v>716</v>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="G256" s="3">
         <f t="shared" si="3"/>
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="H256" t="s">
         <v>323</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="G257" s="3">
         <f t="shared" si="3"/>
-        <v>6.1</v>
+        <v>6.3000000000000007</v>
       </c>
       <c r="H257" t="s">
         <v>777</v>
@@ -17338,7 +17338,7 @@
       </c>
       <c r="G258" s="3">
         <f t="shared" si="3"/>
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="H258" t="s">
         <v>325</v>
@@ -17392,8 +17392,8 @@
         <v>-1.8000000000000043</v>
       </c>
       <c r="G259" s="3">
-        <f t="shared" ref="G259:G322" si="4">E259+6.5+1.5</f>
-        <v>-2.0999999999999996</v>
+        <f t="shared" ref="G259:G322" si="4">E259+6.7+1.5</f>
+        <v>-1.8999999999999995</v>
       </c>
       <c r="H259" s="4" t="s">
         <v>832</v>
@@ -17448,7 +17448,7 @@
       </c>
       <c r="G260" s="3">
         <f t="shared" si="4"/>
-        <v>-5.9</v>
+        <v>-5.7</v>
       </c>
       <c r="H260" s="4" t="s">
         <v>833</v>
@@ -17503,7 +17503,7 @@
       </c>
       <c r="G261" s="3">
         <f t="shared" si="4"/>
-        <v>3.7</v>
+        <v>3.9000000000000004</v>
       </c>
       <c r="H261" t="s">
         <v>328</v>
@@ -17558,7 +17558,7 @@
       </c>
       <c r="G262" s="3">
         <f t="shared" si="4"/>
-        <v>9.3000000000000007</v>
+        <v>9.5</v>
       </c>
       <c r="H262" t="s">
         <v>329</v>
@@ -17613,7 +17613,7 @@
       </c>
       <c r="G263" s="3">
         <f t="shared" si="4"/>
-        <v>50.2</v>
+        <v>50.400000000000006</v>
       </c>
       <c r="H263" t="s">
         <v>330</v>
@@ -17668,7 +17668,7 @@
       </c>
       <c r="G264" s="3">
         <f t="shared" si="4"/>
-        <v>14.4</v>
+        <v>14.600000000000001</v>
       </c>
       <c r="H264" t="s">
         <v>331</v>
@@ -17723,7 +17723,7 @@
       </c>
       <c r="G265" s="3">
         <f t="shared" si="4"/>
-        <v>53.9</v>
+        <v>54.1</v>
       </c>
       <c r="H265" s="4" t="s">
         <v>838</v>
@@ -17778,7 +17778,7 @@
       </c>
       <c r="G266" s="3">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>52.2</v>
       </c>
       <c r="H266" t="s">
         <v>333</v>
@@ -17833,7 +17833,7 @@
       </c>
       <c r="G267" s="3">
         <f t="shared" si="4"/>
-        <v>48.6</v>
+        <v>48.800000000000004</v>
       </c>
       <c r="H267" t="s">
         <v>334</v>
@@ -17888,7 +17888,7 @@
       </c>
       <c r="G268" s="3">
         <f t="shared" si="4"/>
-        <v>68.400000000000006</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="H268" s="4" t="s">
         <v>842</v>
@@ -17943,7 +17943,7 @@
       </c>
       <c r="G269" s="3">
         <f t="shared" si="4"/>
-        <v>-16.399999999999999</v>
+        <v>-16.2</v>
       </c>
       <c r="H269" s="4" t="s">
         <v>844</v>
@@ -17998,7 +17998,7 @@
       </c>
       <c r="G270" s="3">
         <f t="shared" si="4"/>
-        <v>71.599999999999994</v>
+        <v>71.8</v>
       </c>
       <c r="H270" s="4" t="s">
         <v>845</v>
@@ -18053,7 +18053,7 @@
       </c>
       <c r="G271" s="3">
         <f t="shared" si="4"/>
-        <v>67.3</v>
+        <v>67.5</v>
       </c>
       <c r="H271" s="4" t="s">
         <v>847</v>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="G272" s="3">
         <f t="shared" si="4"/>
-        <v>39.799999999999997</v>
+        <v>40</v>
       </c>
       <c r="H272" s="6" t="s">
         <v>339</v>
@@ -18163,7 +18163,7 @@
       </c>
       <c r="G273" s="3">
         <f t="shared" si="4"/>
-        <v>56.3</v>
+        <v>56.5</v>
       </c>
       <c r="H273" s="6" t="s">
         <v>340</v>
@@ -18218,7 +18218,7 @@
       </c>
       <c r="G274" s="3">
         <f t="shared" si="4"/>
-        <v>41.1</v>
+        <v>41.300000000000004</v>
       </c>
       <c r="H274" s="6" t="s">
         <v>341</v>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="G275" s="3">
         <f t="shared" si="4"/>
-        <v>8.6</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="H275" s="4" t="s">
         <v>852</v>
@@ -18328,7 +18328,7 @@
       </c>
       <c r="G276" s="3">
         <f t="shared" si="4"/>
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="H276" s="6" t="s">
         <v>343</v>
@@ -18383,7 +18383,7 @@
       </c>
       <c r="G277" s="3">
         <f t="shared" si="4"/>
-        <v>9.8000000000000007</v>
+        <v>10</v>
       </c>
       <c r="H277" s="6" t="s">
         <v>344</v>
@@ -18439,7 +18439,7 @@
       </c>
       <c r="G278" s="3">
         <f t="shared" si="4"/>
-        <v>22.200000000000003</v>
+        <v>22.400000000000002</v>
       </c>
       <c r="H278" s="6" t="s">
         <v>345</v>
@@ -18494,7 +18494,7 @@
       </c>
       <c r="G279" s="3">
         <f t="shared" si="4"/>
-        <v>-12.7</v>
+        <v>-12.5</v>
       </c>
       <c r="H279" s="4" t="s">
         <v>856</v>
@@ -18549,7 +18549,7 @@
       </c>
       <c r="G280" s="3">
         <f t="shared" si="4"/>
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="H280" s="6" t="s">
         <v>347</v>
@@ -18604,7 +18604,7 @@
       </c>
       <c r="G281" s="3">
         <f t="shared" si="4"/>
-        <v>-13</v>
+        <v>-12.8</v>
       </c>
       <c r="H281" s="4" t="s">
         <v>859</v>
@@ -18659,7 +18659,7 @@
       </c>
       <c r="G282" s="3">
         <f t="shared" si="4"/>
-        <v>-15.100000000000001</v>
+        <v>-14.900000000000002</v>
       </c>
       <c r="H282" s="4" t="s">
         <v>860</v>
@@ -18714,7 +18714,7 @@
       </c>
       <c r="G283" s="3">
         <f t="shared" si="4"/>
-        <v>26.4</v>
+        <v>26.599999999999998</v>
       </c>
       <c r="H283" s="6" t="s">
         <v>861</v>
@@ -18769,7 +18769,7 @@
       </c>
       <c r="G284" s="3">
         <f t="shared" si="4"/>
-        <v>27.3</v>
+        <v>27.5</v>
       </c>
       <c r="H284" s="6" t="s">
         <v>351</v>
@@ -18824,7 +18824,7 @@
       </c>
       <c r="G285" s="3">
         <f t="shared" si="4"/>
-        <v>-3.5999999999999996</v>
+        <v>-3.3999999999999995</v>
       </c>
       <c r="H285" t="s">
         <v>352</v>
@@ -18880,7 +18880,7 @@
       </c>
       <c r="G286" s="3">
         <f t="shared" si="4"/>
-        <v>42.3</v>
+        <v>42.5</v>
       </c>
       <c r="H286" t="s">
         <v>354</v>
@@ -18936,7 +18936,7 @@
       </c>
       <c r="G287" s="3">
         <f t="shared" si="4"/>
-        <v>-5.6</v>
+        <v>-5.3999999999999995</v>
       </c>
       <c r="H287" s="4" t="s">
         <v>357</v>
@@ -18991,7 +18991,7 @@
       </c>
       <c r="G288" s="3">
         <f t="shared" si="4"/>
-        <v>53.3</v>
+        <v>53.5</v>
       </c>
       <c r="H288" s="6" t="s">
         <v>358</v>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="G289" s="3">
         <f t="shared" si="4"/>
-        <v>-9.8000000000000007</v>
+        <v>-9.6000000000000014</v>
       </c>
       <c r="H289" s="4" t="s">
         <v>361</v>
@@ -19102,7 +19102,7 @@
       </c>
       <c r="G290" s="3">
         <f t="shared" si="4"/>
-        <v>-9</v>
+        <v>-8.8000000000000007</v>
       </c>
       <c r="H290" s="4" t="s">
         <v>363</v>
@@ -19157,7 +19157,7 @@
       </c>
       <c r="G291" s="3">
         <f t="shared" si="4"/>
-        <v>-5.8000000000000007</v>
+        <v>-5.6000000000000005</v>
       </c>
       <c r="H291" s="4" t="s">
         <v>365</v>
@@ -19212,7 +19212,7 @@
       </c>
       <c r="G292" s="3">
         <f t="shared" si="4"/>
-        <v>-11.600000000000001</v>
+        <v>-11.400000000000002</v>
       </c>
       <c r="H292" s="4" t="s">
         <v>368</v>
@@ -19267,7 +19267,7 @@
       </c>
       <c r="G293" s="3">
         <f t="shared" si="4"/>
-        <v>-7.8000000000000007</v>
+        <v>-7.6000000000000014</v>
       </c>
       <c r="H293" s="4" t="s">
         <v>370</v>
@@ -19322,7 +19322,7 @@
       </c>
       <c r="G294" s="3">
         <f t="shared" si="4"/>
-        <v>-9.6999999999999993</v>
+        <v>-9.5</v>
       </c>
       <c r="H294" s="4" t="s">
         <v>372</v>
@@ -19377,7 +19377,7 @@
       </c>
       <c r="G295" s="3">
         <f t="shared" si="4"/>
-        <v>-1.5</v>
+        <v>-1.2999999999999998</v>
       </c>
       <c r="H295" s="4" t="s">
         <v>374</v>
@@ -19432,7 +19432,7 @@
       </c>
       <c r="G296" s="3">
         <f t="shared" si="4"/>
-        <v>54.2</v>
+        <v>54.400000000000006</v>
       </c>
       <c r="H296" s="6" t="s">
         <v>375</v>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="G297" s="3">
         <f t="shared" si="4"/>
-        <v>-8.8000000000000007</v>
+        <v>-8.6000000000000014</v>
       </c>
       <c r="H297" s="4" t="s">
         <v>378</v>
@@ -19543,7 +19543,7 @@
       </c>
       <c r="G298" s="3">
         <f t="shared" si="4"/>
-        <v>-7.1</v>
+        <v>-6.8999999999999986</v>
       </c>
       <c r="H298" s="4" t="s">
         <v>380</v>
@@ -19598,7 +19598,7 @@
       </c>
       <c r="G299" s="3">
         <f t="shared" si="4"/>
-        <v>-28.799999999999997</v>
+        <v>-28.599999999999998</v>
       </c>
       <c r="H299" s="4" t="s">
         <v>896</v>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="G300" s="3">
         <f t="shared" si="4"/>
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="H300" s="6" t="s">
         <v>382</v>
@@ -19709,7 +19709,7 @@
       </c>
       <c r="G301" s="3">
         <f t="shared" si="4"/>
-        <v>-34.1</v>
+        <v>-33.9</v>
       </c>
       <c r="H301" s="4" t="s">
         <v>385</v>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="G302" s="3">
         <f t="shared" si="4"/>
-        <v>48.2</v>
+        <v>48.400000000000006</v>
       </c>
       <c r="H302" t="s">
         <v>386</v>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="G303" s="3">
         <f t="shared" si="4"/>
-        <v>-34.6</v>
+        <v>-34.4</v>
       </c>
       <c r="H303" s="4" t="s">
         <v>389</v>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="G304" s="3">
         <f t="shared" si="4"/>
-        <v>-15.7</v>
+        <v>-15.5</v>
       </c>
       <c r="H304" s="4" t="s">
         <v>391</v>
@@ -19933,7 +19933,7 @@
       </c>
       <c r="G305" s="3">
         <f t="shared" si="4"/>
-        <v>-26.6</v>
+        <v>-26.400000000000002</v>
       </c>
       <c r="H305" s="4" t="s">
         <v>393</v>
@@ -19989,7 +19989,7 @@
       </c>
       <c r="G306" s="3">
         <f t="shared" si="4"/>
-        <v>-3</v>
+        <v>-2.8</v>
       </c>
       <c r="H306" s="4" t="s">
         <v>395</v>
@@ -20045,7 +20045,7 @@
       </c>
       <c r="G307" s="3">
         <f t="shared" si="4"/>
-        <v>-7.6</v>
+        <v>-7.3999999999999986</v>
       </c>
       <c r="H307" s="4" t="s">
         <v>397</v>
@@ -20101,7 +20101,7 @@
       </c>
       <c r="G308" s="3">
         <f t="shared" si="4"/>
-        <v>-2.5</v>
+        <v>-2.2999999999999998</v>
       </c>
       <c r="H308" t="s">
         <v>398</v>
@@ -20157,7 +20157,7 @@
       </c>
       <c r="G309" s="3">
         <f t="shared" si="4"/>
-        <v>0.29999999999999982</v>
+        <v>0.5</v>
       </c>
       <c r="H309" s="4" t="s">
         <v>401</v>
@@ -20213,7 +20213,7 @@
       </c>
       <c r="G310" s="3">
         <f t="shared" si="4"/>
-        <v>63</v>
+        <v>63.2</v>
       </c>
       <c r="H310" t="s">
         <v>402</v>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="G311" s="3">
         <f t="shared" si="4"/>
-        <v>-22</v>
+        <v>-21.8</v>
       </c>
       <c r="H311" s="4" t="s">
         <v>405</v>
@@ -20324,7 +20324,7 @@
       </c>
       <c r="G312" s="3">
         <f t="shared" si="4"/>
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="H312" t="s">
         <v>406</v>
@@ -20380,7 +20380,7 @@
       </c>
       <c r="G313" s="3">
         <f t="shared" si="4"/>
-        <v>-12.3</v>
+        <v>-12.100000000000001</v>
       </c>
       <c r="H313" s="4" t="s">
         <v>409</v>
@@ -20435,7 +20435,7 @@
       </c>
       <c r="G314" s="3">
         <f t="shared" si="4"/>
-        <v>-2</v>
+        <v>-1.7999999999999998</v>
       </c>
       <c r="H314" s="4" t="s">
         <v>411</v>
@@ -20490,7 +20490,7 @@
       </c>
       <c r="G315" s="3">
         <f t="shared" si="4"/>
-        <v>-13.5</v>
+        <v>-13.3</v>
       </c>
       <c r="K315" t="s">
         <v>678</v>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="G316" s="3">
         <f t="shared" si="4"/>
-        <v>-47.6</v>
+        <v>-47.4</v>
       </c>
       <c r="K316" t="s">
         <v>678</v>
@@ -20588,7 +20588,7 @@
       </c>
       <c r="G317" s="3">
         <f t="shared" si="4"/>
-        <v>-36.799999999999997</v>
+        <v>-36.599999999999994</v>
       </c>
       <c r="K317" t="s">
         <v>678</v>
@@ -20637,7 +20637,7 @@
       </c>
       <c r="G318" s="3">
         <f t="shared" si="4"/>
-        <v>-24.9</v>
+        <v>-24.7</v>
       </c>
       <c r="K318" t="s">
         <v>678</v>
@@ -20686,7 +20686,7 @@
       </c>
       <c r="G319" s="3">
         <f t="shared" si="4"/>
-        <v>-10.199999999999999</v>
+        <v>-10</v>
       </c>
       <c r="K319" t="s">
         <v>678</v>
@@ -20735,7 +20735,7 @@
       </c>
       <c r="G320" s="3">
         <f t="shared" si="4"/>
-        <v>45.6</v>
+        <v>45.800000000000004</v>
       </c>
       <c r="H320" s="6" t="s">
         <v>417</v>
@@ -20791,7 +20791,7 @@
       </c>
       <c r="G321" s="3">
         <f t="shared" si="4"/>
-        <v>-19.100000000000001</v>
+        <v>-18.900000000000002</v>
       </c>
       <c r="H321" s="4" t="s">
         <v>420</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="G322" s="3">
         <f t="shared" si="4"/>
-        <v>53.6</v>
+        <v>53.800000000000004</v>
       </c>
       <c r="H322" s="6" t="s">
         <v>421</v>
@@ -20902,8 +20902,8 @@
         <v>12.700000000000003</v>
       </c>
       <c r="G323" s="3">
-        <f t="shared" ref="G323:G386" si="5">E323+6.5+1.5</f>
-        <v>20</v>
+        <f t="shared" ref="G323:G386" si="5">E323+6.7+1.5</f>
+        <v>20.2</v>
       </c>
       <c r="H323" s="6" t="s">
         <v>423</v>
@@ -20959,7 +20959,7 @@
       </c>
       <c r="G324" s="3">
         <f t="shared" si="5"/>
-        <v>16.600000000000001</v>
+        <v>16.8</v>
       </c>
       <c r="H324" s="6" t="s">
         <v>425</v>
@@ -21015,7 +21015,7 @@
       </c>
       <c r="G325" s="3">
         <f t="shared" si="5"/>
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="H325" s="6" t="s">
         <v>427</v>
@@ -21071,7 +21071,7 @@
       </c>
       <c r="G326" s="3">
         <f t="shared" si="5"/>
-        <v>8.3000000000000007</v>
+        <v>8.5</v>
       </c>
       <c r="H326" s="4" t="s">
         <v>430</v>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="G327" s="3">
         <f t="shared" si="5"/>
-        <v>43.7</v>
+        <v>43.900000000000006</v>
       </c>
       <c r="H327" t="s">
         <v>431</v>
@@ -21182,7 +21182,7 @@
       </c>
       <c r="G328" s="3">
         <f t="shared" si="5"/>
-        <v>85.3</v>
+        <v>85.5</v>
       </c>
       <c r="H328" s="6" t="s">
         <v>434</v>
@@ -21235,7 +21235,7 @@
       </c>
       <c r="G329" s="3">
         <f t="shared" si="5"/>
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="H329" t="s">
         <v>435</v>
@@ -21291,7 +21291,7 @@
       </c>
       <c r="G330" s="3">
         <f t="shared" si="5"/>
-        <v>36.6</v>
+        <v>36.800000000000004</v>
       </c>
       <c r="H330" s="6" t="s">
         <v>437</v>
@@ -21347,7 +21347,7 @@
       </c>
       <c r="G331" s="3">
         <f t="shared" si="5"/>
-        <v>19.399999999999999</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="H331" t="s">
         <v>439</v>
@@ -21403,7 +21403,7 @@
       </c>
       <c r="G332" s="3">
         <f t="shared" si="5"/>
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H332" s="4" t="s">
         <v>442</v>
@@ -21459,7 +21459,7 @@
       </c>
       <c r="G333" s="3">
         <f t="shared" si="5"/>
-        <v>-0.5</v>
+        <v>-0.29999999999999982</v>
       </c>
       <c r="H333" s="4" t="s">
         <v>444</v>
@@ -21515,7 +21515,7 @@
       </c>
       <c r="G334" s="3">
         <f t="shared" si="5"/>
-        <v>-29.9</v>
+        <v>-29.7</v>
       </c>
       <c r="H334" s="4" t="s">
         <v>446</v>
@@ -21571,7 +21571,7 @@
       </c>
       <c r="G335" s="3">
         <f t="shared" si="5"/>
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="H335" s="4" t="s">
         <v>448</v>
@@ -21627,7 +21627,7 @@
       </c>
       <c r="G336" s="3">
         <f t="shared" si="5"/>
-        <v>-13.399999999999999</v>
+        <v>-13.2</v>
       </c>
       <c r="H336" s="4" t="s">
         <v>450</v>
@@ -21683,7 +21683,7 @@
       </c>
       <c r="G337" s="3">
         <f t="shared" si="5"/>
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="H337" s="6" t="s">
         <v>451</v>
@@ -21739,7 +21739,7 @@
       </c>
       <c r="G338" s="3">
         <f t="shared" si="5"/>
-        <v>-37.5</v>
+        <v>-37.299999999999997</v>
       </c>
       <c r="H338" s="4" t="s">
         <v>454</v>
@@ -21795,7 +21795,7 @@
       </c>
       <c r="G339" s="3">
         <f t="shared" si="5"/>
-        <v>-25.4</v>
+        <v>-25.2</v>
       </c>
       <c r="H339" s="4" t="s">
         <v>456</v>
@@ -21851,7 +21851,7 @@
       </c>
       <c r="G340" s="3">
         <f t="shared" si="5"/>
-        <v>-30</v>
+        <v>-29.8</v>
       </c>
       <c r="H340" s="4" t="s">
         <v>458</v>
@@ -21907,7 +21907,7 @@
       </c>
       <c r="G341" s="3">
         <f t="shared" si="5"/>
-        <v>-14.8</v>
+        <v>-14.600000000000001</v>
       </c>
       <c r="H341" s="4" t="s">
         <v>460</v>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="G342" s="3">
         <f t="shared" si="5"/>
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="H342" t="s">
         <v>461</v>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="G343" s="3">
         <f t="shared" si="5"/>
-        <v>30</v>
+        <v>30.2</v>
       </c>
       <c r="K343" t="s">
         <v>662</v>
@@ -22068,7 +22068,7 @@
       </c>
       <c r="G344" s="3">
         <f t="shared" si="5"/>
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="K344" t="s">
         <v>662</v>
@@ -22117,7 +22117,7 @@
       </c>
       <c r="G345" s="3">
         <f t="shared" si="5"/>
-        <v>-5.0999999999999996</v>
+        <v>-4.8999999999999995</v>
       </c>
       <c r="H345" s="4" t="s">
         <v>873</v>
@@ -22172,7 +22172,7 @@
       </c>
       <c r="G346" s="3">
         <f t="shared" si="5"/>
-        <v>-6</v>
+        <v>-5.8</v>
       </c>
       <c r="H346" s="4" t="s">
         <v>875</v>
@@ -22227,7 +22227,7 @@
       </c>
       <c r="G347" s="3">
         <f t="shared" si="5"/>
-        <v>-35</v>
+        <v>-34.799999999999997</v>
       </c>
       <c r="H347" s="4" t="s">
         <v>799</v>
@@ -22282,7 +22282,7 @@
       </c>
       <c r="G348" s="3">
         <f t="shared" si="5"/>
-        <v>-15.600000000000001</v>
+        <v>-15.400000000000002</v>
       </c>
       <c r="H348" s="4" t="s">
         <v>786</v>
@@ -22337,7 +22337,7 @@
       </c>
       <c r="G349" s="3">
         <f t="shared" si="5"/>
-        <v>-14.8</v>
+        <v>-14.600000000000001</v>
       </c>
       <c r="H349" s="4" t="s">
         <v>798</v>
@@ -22392,7 +22392,7 @@
       </c>
       <c r="G350" s="3">
         <f t="shared" si="5"/>
-        <v>30.8</v>
+        <v>31</v>
       </c>
       <c r="H350" t="s">
         <v>784</v>
@@ -22447,7 +22447,7 @@
       </c>
       <c r="G351" s="3">
         <f t="shared" si="5"/>
-        <v>-18.399999999999999</v>
+        <v>-18.2</v>
       </c>
       <c r="H351" s="4" t="s">
         <v>788</v>
@@ -22502,7 +22502,7 @@
       </c>
       <c r="G352" s="3">
         <f t="shared" si="5"/>
-        <v>-21.2</v>
+        <v>-21</v>
       </c>
       <c r="H352" s="4" t="s">
         <v>725</v>
@@ -22559,7 +22559,7 @@
       </c>
       <c r="G353" s="3">
         <f t="shared" si="5"/>
-        <v>-49.800000000000004</v>
+        <v>-49.6</v>
       </c>
       <c r="H353" s="4" t="s">
         <v>947</v>
@@ -22615,7 +22615,7 @@
       </c>
       <c r="G354" s="3">
         <f t="shared" si="5"/>
-        <v>-25.800000000000004</v>
+        <v>-25.600000000000005</v>
       </c>
       <c r="H354" s="4" t="s">
         <v>948</v>
@@ -22671,7 +22671,7 @@
       </c>
       <c r="G355" s="3">
         <f t="shared" si="5"/>
-        <v>-27.700000000000003</v>
+        <v>-27.500000000000004</v>
       </c>
       <c r="H355" s="4" t="s">
         <v>949</v>
@@ -22727,7 +22727,7 @@
       </c>
       <c r="G356" s="3">
         <f t="shared" si="5"/>
-        <v>-15.900000000000006</v>
+        <v>-15.700000000000006</v>
       </c>
       <c r="H356" s="4" t="s">
         <v>955</v>
@@ -22783,7 +22783,7 @@
       </c>
       <c r="G357" s="3">
         <f t="shared" si="5"/>
-        <v>-15.100000000000001</v>
+        <v>-14.900000000000002</v>
       </c>
       <c r="H357" s="4" t="s">
         <v>958</v>
@@ -22839,7 +22839,7 @@
       </c>
       <c r="G358" s="3">
         <f t="shared" si="5"/>
-        <v>-18.5</v>
+        <v>-18.3</v>
       </c>
       <c r="H358" s="4" t="s">
         <v>956</v>
@@ -22895,7 +22895,7 @@
       </c>
       <c r="G359" s="3">
         <f t="shared" si="5"/>
-        <v>-14.399999999999999</v>
+        <v>-14.2</v>
       </c>
       <c r="H359" s="4" t="s">
         <v>954</v>
@@ -22951,7 +22951,7 @@
       </c>
       <c r="G360" s="3">
         <f t="shared" si="5"/>
-        <v>-12.199999999999996</v>
+        <v>-11.999999999999996</v>
       </c>
       <c r="H360" s="4" t="s">
         <v>952</v>
@@ -23007,7 +23007,7 @@
       </c>
       <c r="G361" s="3">
         <f t="shared" si="5"/>
-        <v>-13.100000000000001</v>
+        <v>-12.900000000000002</v>
       </c>
       <c r="H361" s="4" t="s">
         <v>950</v>
@@ -23062,7 +23062,7 @@
       </c>
       <c r="G362" s="3">
         <f t="shared" si="5"/>
-        <v>-41.4</v>
+        <v>-41.199999999999996</v>
       </c>
       <c r="H362" s="4" t="s">
         <v>483</v>
@@ -23117,7 +23117,7 @@
       </c>
       <c r="G363" s="3">
         <f t="shared" si="5"/>
-        <v>-14.8</v>
+        <v>-14.600000000000001</v>
       </c>
       <c r="H363" s="4" t="s">
         <v>485</v>
@@ -23173,7 +23173,7 @@
       </c>
       <c r="G364" s="3">
         <f t="shared" si="5"/>
-        <v>-15.3</v>
+        <v>-15.100000000000001</v>
       </c>
       <c r="H364" s="4" t="s">
         <v>488</v>
@@ -23228,7 +23228,7 @@
       </c>
       <c r="G365" s="3">
         <f t="shared" si="5"/>
-        <v>-16.600000000000001</v>
+        <v>-16.400000000000002</v>
       </c>
       <c r="H365" s="4" t="s">
         <v>490</v>
@@ -23283,7 +23283,7 @@
       </c>
       <c r="G366" s="3">
         <f t="shared" si="5"/>
-        <v>-13.5</v>
+        <v>-13.3</v>
       </c>
       <c r="H366" s="4" t="s">
         <v>492</v>
@@ -23338,7 +23338,7 @@
       </c>
       <c r="G367" s="3">
         <f t="shared" si="5"/>
-        <v>-14.8</v>
+        <v>-14.600000000000001</v>
       </c>
       <c r="H367" s="4" t="s">
         <v>494</v>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="G368" s="3">
         <f t="shared" si="5"/>
-        <v>31.4</v>
+        <v>31.599999999999998</v>
       </c>
       <c r="H368" t="s">
         <v>495</v>
@@ -23449,7 +23449,7 @@
       </c>
       <c r="G369" s="3">
         <f t="shared" si="5"/>
-        <v>-19.600000000000001</v>
+        <v>-19.400000000000002</v>
       </c>
       <c r="H369" s="4" t="s">
         <v>498</v>
@@ -23505,7 +23505,7 @@
       </c>
       <c r="G370" s="3">
         <f t="shared" si="5"/>
-        <v>-11.8</v>
+        <v>-11.600000000000001</v>
       </c>
       <c r="H370" s="4" t="s">
         <v>500</v>
@@ -23561,7 +23561,7 @@
       </c>
       <c r="G371" s="3">
         <f t="shared" si="5"/>
-        <v>-14.5</v>
+        <v>-14.3</v>
       </c>
       <c r="H371" s="4" t="s">
         <v>503</v>
@@ -23617,7 +23617,7 @@
       </c>
       <c r="G372" s="3">
         <f t="shared" si="5"/>
-        <v>-26.299999999999997</v>
+        <v>-26.099999999999998</v>
       </c>
       <c r="H372" s="4" t="s">
         <v>506</v>
@@ -23672,7 +23672,7 @@
       </c>
       <c r="G373" s="3">
         <f t="shared" si="5"/>
-        <v>-15.8</v>
+        <v>-15.600000000000001</v>
       </c>
       <c r="H373" s="4" t="s">
         <v>509</v>
@@ -23727,7 +23727,7 @@
       </c>
       <c r="G374" s="3">
         <f t="shared" si="5"/>
-        <v>-38.1</v>
+        <v>-37.9</v>
       </c>
       <c r="H374" s="4" t="s">
         <v>511</v>
@@ -23782,7 +23782,7 @@
       </c>
       <c r="G375" s="3">
         <f t="shared" si="5"/>
-        <v>-16.2</v>
+        <v>-16</v>
       </c>
       <c r="H375" s="4" t="s">
         <v>811</v>
@@ -23837,7 +23837,7 @@
       </c>
       <c r="G376" s="3">
         <f t="shared" si="5"/>
-        <v>-9.8000000000000007</v>
+        <v>-9.6000000000000014</v>
       </c>
       <c r="H376" s="4" t="s">
         <v>514</v>
@@ -23892,7 +23892,7 @@
       </c>
       <c r="G377" s="3">
         <f t="shared" si="5"/>
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="H377" t="s">
         <v>515</v>
@@ -23949,7 +23949,7 @@
       </c>
       <c r="G378" s="3">
         <f t="shared" si="5"/>
-        <v>-10</v>
+        <v>-9.8000000000000007</v>
       </c>
       <c r="H378" s="4" t="s">
         <v>518</v>
@@ -24004,7 +24004,7 @@
       </c>
       <c r="G379" s="3">
         <f t="shared" si="5"/>
-        <v>62.8</v>
+        <v>63</v>
       </c>
       <c r="H379" t="s">
         <v>520</v>
@@ -24060,7 +24060,7 @@
       </c>
       <c r="G380" s="3">
         <f t="shared" si="5"/>
-        <v>-43.6</v>
+        <v>-43.4</v>
       </c>
       <c r="H380" s="4" t="s">
         <v>523</v>
@@ -24116,7 +24116,7 @@
       </c>
       <c r="G381" s="3">
         <f t="shared" si="5"/>
-        <v>36.4</v>
+        <v>36.6</v>
       </c>
       <c r="H381" t="s">
         <v>525</v>
@@ -24172,7 +24172,7 @@
       </c>
       <c r="G382" s="3">
         <f t="shared" si="5"/>
-        <v>-13.8</v>
+        <v>-13.600000000000001</v>
       </c>
       <c r="H382" s="4" t="s">
         <v>528</v>
@@ -24228,7 +24228,7 @@
       </c>
       <c r="G383" s="3">
         <f t="shared" si="5"/>
-        <v>-14.100000000000001</v>
+        <v>-13.900000000000002</v>
       </c>
       <c r="H383" s="4" t="s">
         <v>531</v>
@@ -24284,7 +24284,7 @@
       </c>
       <c r="G384" s="3">
         <f t="shared" si="5"/>
-        <v>-6.6999999999999993</v>
+        <v>-6.4999999999999991</v>
       </c>
       <c r="H384" s="4" t="s">
         <v>534</v>
@@ -24340,7 +24340,7 @@
       </c>
       <c r="G385" s="3">
         <f t="shared" si="5"/>
-        <v>-8</v>
+        <v>-7.8000000000000007</v>
       </c>
       <c r="H385" s="4" t="s">
         <v>537</v>
@@ -24395,7 +24395,7 @@
       </c>
       <c r="G386" s="3">
         <f t="shared" si="5"/>
-        <v>-16</v>
+        <v>-15.8</v>
       </c>
       <c r="H386" s="4" t="s">
         <v>539</v>
@@ -24449,8 +24449,8 @@
         <v>-18.5</v>
       </c>
       <c r="G387" s="3">
-        <f t="shared" ref="G387:G436" si="6">E387+6.5+1.5</f>
-        <v>-15.7</v>
+        <f t="shared" ref="G387:G436" si="6">E387+6.7+1.5</f>
+        <v>-15.5</v>
       </c>
       <c r="H387" s="4" t="s">
         <v>541</v>
@@ -24505,7 +24505,7 @@
       </c>
       <c r="G388" s="3">
         <f t="shared" si="6"/>
-        <v>-13.100000000000001</v>
+        <v>-12.900000000000002</v>
       </c>
       <c r="H388" s="4" t="s">
         <v>543</v>
@@ -24560,7 +24560,7 @@
       </c>
       <c r="G389" s="3">
         <f t="shared" si="6"/>
-        <v>-2.3000000000000007</v>
+        <v>-2.1000000000000005</v>
       </c>
       <c r="H389" t="s">
         <v>544</v>
@@ -24616,7 +24616,7 @@
       </c>
       <c r="G390" s="3">
         <f t="shared" si="6"/>
-        <v>38.4</v>
+        <v>38.6</v>
       </c>
       <c r="H390" s="6" t="s">
         <v>546</v>
@@ -24672,7 +24672,7 @@
       </c>
       <c r="G391" s="3">
         <f t="shared" si="6"/>
-        <v>48.7</v>
+        <v>48.900000000000006</v>
       </c>
       <c r="H391" s="4" t="s">
         <v>549</v>
@@ -24728,7 +24728,7 @@
       </c>
       <c r="G392" s="3">
         <f t="shared" si="6"/>
-        <v>-13.8</v>
+        <v>-13.600000000000001</v>
       </c>
       <c r="H392" s="4" t="s">
         <v>552</v>
@@ -24783,7 +24783,7 @@
       </c>
       <c r="G393" s="3">
         <f t="shared" si="6"/>
-        <v>-9.6999999999999993</v>
+        <v>-9.5</v>
       </c>
       <c r="H393" s="4" t="s">
         <v>553</v>
@@ -24839,7 +24839,7 @@
       </c>
       <c r="G394" s="3">
         <f t="shared" si="6"/>
-        <v>40.5</v>
+        <v>40.700000000000003</v>
       </c>
       <c r="H394" s="4" t="s">
         <v>556</v>
@@ -24895,7 +24895,7 @@
       </c>
       <c r="G395" s="3">
         <f t="shared" si="6"/>
-        <v>-2.0999999999999996</v>
+        <v>-1.8999999999999995</v>
       </c>
       <c r="H395" t="s">
         <v>558</v>
@@ -24951,7 +24951,7 @@
       </c>
       <c r="G396" s="3">
         <f t="shared" si="6"/>
-        <v>-2.4000000000000004</v>
+        <v>-2.2000000000000002</v>
       </c>
       <c r="H396" s="4" t="s">
         <v>560</v>
@@ -25007,7 +25007,7 @@
       </c>
       <c r="G397" s="3">
         <f t="shared" si="6"/>
-        <v>-16.899999999999999</v>
+        <v>-16.7</v>
       </c>
       <c r="H397" s="4" t="s">
         <v>563</v>
@@ -25062,7 +25062,7 @@
       </c>
       <c r="G398" s="3">
         <f t="shared" si="6"/>
-        <v>64.2</v>
+        <v>64.400000000000006</v>
       </c>
       <c r="H398" t="s">
         <v>564</v>
@@ -25118,7 +25118,7 @@
       </c>
       <c r="G399" s="3">
         <f t="shared" si="6"/>
-        <v>-12.899999999999999</v>
+        <v>-12.7</v>
       </c>
       <c r="H399" s="4" t="s">
         <v>567</v>
@@ -25174,7 +25174,7 @@
       </c>
       <c r="G400" s="3">
         <f t="shared" si="6"/>
-        <v>31.6</v>
+        <v>31.8</v>
       </c>
       <c r="H400" s="4" t="s">
         <v>876</v>
@@ -25229,7 +25229,7 @@
       </c>
       <c r="G401" s="3">
         <f t="shared" si="6"/>
-        <v>-20.9</v>
+        <v>-20.7</v>
       </c>
       <c r="H401" s="4" t="s">
         <v>878</v>
@@ -25284,7 +25284,7 @@
       </c>
       <c r="G402" s="3">
         <f t="shared" si="6"/>
-        <v>-33.299999999999997</v>
+        <v>-33.099999999999994</v>
       </c>
       <c r="H402" s="4" t="s">
         <v>879</v>
@@ -25339,7 +25339,7 @@
       </c>
       <c r="G403" s="3">
         <f t="shared" si="6"/>
-        <v>-24.4</v>
+        <v>-24.2</v>
       </c>
       <c r="H403" s="4" t="s">
         <v>880</v>
@@ -25394,7 +25394,7 @@
       </c>
       <c r="G404" s="3">
         <f t="shared" si="6"/>
-        <v>42.8</v>
+        <v>43</v>
       </c>
       <c r="H404" s="4" t="s">
         <v>573</v>
@@ -25450,7 +25450,7 @@
       </c>
       <c r="G405" s="3">
         <f t="shared" si="6"/>
-        <v>3.1000000000000014</v>
+        <v>3.3000000000000016</v>
       </c>
       <c r="H405" s="4" t="s">
         <v>906</v>
@@ -25506,7 +25506,7 @@
       </c>
       <c r="G406" s="3">
         <f t="shared" si="6"/>
-        <v>7.8000000000000043</v>
+        <v>8.0000000000000036</v>
       </c>
       <c r="H406" s="4" t="s">
         <v>903</v>
@@ -25562,7 +25562,7 @@
       </c>
       <c r="G407" s="3">
         <f t="shared" si="6"/>
-        <v>42.600000000000009</v>
+        <v>42.800000000000011</v>
       </c>
       <c r="H407" t="s">
         <v>576</v>
@@ -25618,7 +25618,7 @@
       </c>
       <c r="G408" s="3">
         <f t="shared" si="6"/>
-        <v>40.600000000000009</v>
+        <v>40.800000000000011</v>
       </c>
       <c r="H408" t="s">
         <v>577</v>
@@ -25674,7 +25674,7 @@
       </c>
       <c r="G409" s="3">
         <f t="shared" si="6"/>
-        <v>-4.1999999999999957</v>
+        <v>-3.9999999999999956</v>
       </c>
       <c r="H409" s="4" t="s">
         <v>905</v>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="G410" s="3">
         <f t="shared" si="6"/>
-        <v>-16</v>
+        <v>-15.8</v>
       </c>
       <c r="H410" s="4" t="s">
         <v>899</v>
@@ -25786,7 +25786,7 @@
       </c>
       <c r="G411" s="3">
         <f t="shared" si="6"/>
-        <v>10.899999999999999</v>
+        <v>11.099999999999998</v>
       </c>
       <c r="H411" t="s">
         <v>580</v>
@@ -25842,7 +25842,7 @@
       </c>
       <c r="G412" s="3">
         <f t="shared" si="6"/>
-        <v>57.2</v>
+        <v>57.400000000000006</v>
       </c>
       <c r="H412" t="s">
         <v>581</v>
@@ -25898,7 +25898,7 @@
       </c>
       <c r="G413" s="3">
         <f t="shared" si="6"/>
-        <v>-35.900000000000006</v>
+        <v>-35.700000000000003</v>
       </c>
       <c r="H413" s="4" t="s">
         <v>907</v>
@@ -25954,7 +25954,7 @@
       </c>
       <c r="G414" s="3">
         <f t="shared" si="6"/>
-        <v>16.300000000000004</v>
+        <v>16.500000000000004</v>
       </c>
       <c r="H414" t="s">
         <v>583</v>
@@ -26010,7 +26010,7 @@
       </c>
       <c r="G415" s="3">
         <f t="shared" si="6"/>
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="H415" t="s">
         <v>584</v>
@@ -26065,7 +26065,7 @@
       </c>
       <c r="G416" s="3">
         <f t="shared" si="6"/>
-        <v>36.5</v>
+        <v>36.700000000000003</v>
       </c>
       <c r="H416" t="s">
         <v>585</v>
@@ -26120,7 +26120,7 @@
       </c>
       <c r="G417" s="3">
         <f t="shared" si="6"/>
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="H417" t="s">
         <v>586</v>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="G418" s="3">
         <f t="shared" si="6"/>
-        <v>4.7</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H418" t="s">
         <v>587</v>
@@ -26230,7 +26230,7 @@
       </c>
       <c r="G419" s="3">
         <f t="shared" si="6"/>
-        <v>-12.600000000000001</v>
+        <v>-12.400000000000002</v>
       </c>
       <c r="H419" s="4" t="s">
         <v>932</v>
@@ -26285,7 +26285,7 @@
       </c>
       <c r="G420" s="3">
         <f t="shared" si="6"/>
-        <v>-2.6999999999999993</v>
+        <v>-2.4999999999999991</v>
       </c>
       <c r="H420" s="4" t="s">
         <v>963</v>
@@ -26340,7 +26340,7 @@
       </c>
       <c r="G421" s="3">
         <f t="shared" si="6"/>
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="H421" t="s">
         <v>590</v>
@@ -26395,7 +26395,7 @@
       </c>
       <c r="G422" s="3">
         <f t="shared" si="6"/>
-        <v>82.5</v>
+        <v>82.7</v>
       </c>
       <c r="H422" t="s">
         <v>591</v>
@@ -26450,7 +26450,7 @@
       </c>
       <c r="G423" s="3">
         <f t="shared" si="6"/>
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="H423" t="s">
         <v>592</v>
@@ -26502,7 +26502,7 @@
       </c>
       <c r="G424" s="3">
         <f t="shared" si="6"/>
-        <v>49</v>
+        <v>49.2</v>
       </c>
       <c r="H424" t="s">
         <v>593</v>
@@ -26557,7 +26557,7 @@
       </c>
       <c r="G425" s="3">
         <f t="shared" si="6"/>
-        <v>25.9</v>
+        <v>26.099999999999998</v>
       </c>
       <c r="H425" t="s">
         <v>594</v>
@@ -26612,7 +26612,7 @@
       </c>
       <c r="G426" s="3">
         <f t="shared" si="6"/>
-        <v>-36.4</v>
+        <v>-36.199999999999996</v>
       </c>
       <c r="H426" s="4" t="s">
         <v>596</v>
@@ -26667,7 +26667,7 @@
       </c>
       <c r="G427" s="3">
         <f t="shared" si="6"/>
-        <v>-31.6</v>
+        <v>-31.4</v>
       </c>
       <c r="H427" s="4" t="s">
         <v>598</v>
@@ -26722,7 +26722,7 @@
       </c>
       <c r="G428" s="3">
         <f t="shared" si="6"/>
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="H428" s="4" t="s">
         <v>975</v>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="G429" s="3">
         <f t="shared" si="6"/>
-        <v>48</v>
+        <v>48.2</v>
       </c>
       <c r="H429" t="s">
         <v>601</v>
@@ -26829,7 +26829,7 @@
       </c>
       <c r="G430" s="3">
         <f t="shared" si="6"/>
-        <v>0.59999999999999964</v>
+        <v>0.79999999999999982</v>
       </c>
       <c r="H430" s="4" t="s">
         <v>979</v>
@@ -26884,7 +26884,7 @@
       </c>
       <c r="G431" s="3">
         <f t="shared" si="6"/>
-        <v>59.4</v>
+        <v>59.6</v>
       </c>
       <c r="H431" t="s">
         <v>603</v>
@@ -26939,7 +26939,7 @@
       </c>
       <c r="G432" s="3">
         <f t="shared" si="6"/>
-        <v>-14.100000000000001</v>
+        <v>-13.900000000000002</v>
       </c>
       <c r="H432" s="4" t="s">
         <v>989</v>
@@ -26994,7 +26994,7 @@
       </c>
       <c r="G433" s="3">
         <f t="shared" si="6"/>
-        <v>-8.3999999999999986</v>
+        <v>-8.1999999999999993</v>
       </c>
       <c r="I433" t="s">
         <v>605</v>
@@ -27046,7 +27046,7 @@
       </c>
       <c r="G434" s="3">
         <f t="shared" si="6"/>
-        <v>-14.5</v>
+        <v>-14.3</v>
       </c>
       <c r="H434" s="4" t="s">
         <v>992</v>
@@ -27101,7 +27101,7 @@
       </c>
       <c r="G435" s="3">
         <f t="shared" si="6"/>
-        <v>-8.1999999999999993</v>
+        <v>-8</v>
       </c>
       <c r="H435" s="4" t="s">
         <v>993</v>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="G436" s="3">
         <f t="shared" si="6"/>
-        <v>-38.200000000000003</v>
+        <v>-38</v>
       </c>
       <c r="K436" t="s">
         <v>678</v>

--- a/inputs/House Model Data.xlsx
+++ b/inputs/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Developer/house_model_python/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE3E6C7E-31B9-654D-A258-96AF159447AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D7FFD67-6D83-DA46-A7A6-7D4224C1BC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5526" uniqueCount="996">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5582" uniqueCount="1032">
   <si>
     <t>State</t>
   </si>
@@ -3061,6 +3061,114 @@
   </si>
   <si>
     <t>Sneed, Andrew</t>
+  </si>
+  <si>
+    <t>Grage, Rachel</t>
+  </si>
+  <si>
+    <t>Jenkins, Jennifer</t>
+  </si>
+  <si>
+    <t>Haridopolous, Mike</t>
+  </si>
+  <si>
+    <t>Gray, Leela</t>
+  </si>
+  <si>
+    <t>Franklin, C. Scott,</t>
+  </si>
+  <si>
+    <t>Dandiya, Pia</t>
+  </si>
+  <si>
+    <t>Brown, Te Mayonna</t>
+  </si>
+  <si>
+    <t>Locklin, Nicole</t>
+  </si>
+  <si>
+    <t>Ehr, Phil</t>
+  </si>
+  <si>
+    <t>Holloway, LaShonda</t>
+  </si>
+  <si>
+    <t>Beltran, Mike</t>
+  </si>
+  <si>
+    <t>Anderson, Brent</t>
+  </si>
+  <si>
+    <t>Pericola, James</t>
+  </si>
+  <si>
+    <t>Adeimy, Deborah</t>
+  </si>
+  <si>
+    <t>Gruters, Sydney</t>
+  </si>
+  <si>
+    <t>Askar, Casey</t>
+  </si>
+  <si>
+    <t>Dalton, Bale</t>
+  </si>
+  <si>
+    <t>Schwartzel, Jim</t>
+  </si>
+  <si>
+    <t>Montavon, Matthew</t>
+  </si>
+  <si>
+    <t>Valimont, Gay</t>
+  </si>
+  <si>
+    <t>Elijah, Ryan</t>
+  </si>
+  <si>
+    <t>Arias, Victor</t>
+  </si>
+  <si>
+    <t>Rogers, Austin</t>
+  </si>
+  <si>
+    <t>Harp, Seth</t>
+  </si>
+  <si>
+    <t>Overman,  Kimberly</t>
+  </si>
+  <si>
+    <t>People, Robert</t>
+  </si>
+  <si>
+    <t>Singer, Scott</t>
+  </si>
+  <si>
+    <t>Kirschner, Kelly</t>
+  </si>
+  <si>
+    <t>Yonce, Eric</t>
+  </si>
+  <si>
+    <t>Gibson, Curtis</t>
+  </si>
+  <si>
+    <t>Rodriguez, Eliott</t>
+  </si>
+  <si>
+    <t>Gilbert, Oliver</t>
+  </si>
+  <si>
+    <t>Green, Amanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kinney, Lisa </t>
+  </si>
+  <si>
+    <t>Hill, Bill (I)</t>
+  </si>
+  <si>
+    <t>Gray, Chuck</t>
   </si>
 </sst>
 </file>
@@ -3600,8 +3708,8 @@
         <v>-30.199999999999996</v>
       </c>
       <c r="G2" s="3">
-        <f>E2+6.7+1.5</f>
-        <v>-28.099999999999998</v>
+        <f>E2+6.8+1.5</f>
+        <v>-27.999999999999996</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>964</v>
@@ -3644,8 +3752,8 @@
         <v>-11.799999999999997</v>
       </c>
       <c r="G3" s="3">
-        <f t="shared" ref="G3:G66" si="0">E3+6.7+1.5</f>
-        <v>-9.100000000000005</v>
+        <f t="shared" ref="G3:G66" si="0">E3+6.8+1.5</f>
+        <v>-9.0000000000000036</v>
       </c>
       <c r="H3" t="s">
         <v>965</v>
@@ -3689,7 +3797,7 @@
       </c>
       <c r="G4" s="3">
         <f t="shared" si="0"/>
-        <v>-37.700000000000003</v>
+        <v>-37.600000000000009</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>11</v>
@@ -3733,7 +3841,7 @@
       </c>
       <c r="G5" s="3">
         <f t="shared" si="0"/>
-        <v>-59.600000000000009</v>
+        <v>-59.500000000000014</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>13</v>
@@ -3777,7 +3885,7 @@
       </c>
       <c r="G6" s="3">
         <f t="shared" si="0"/>
-        <v>-20.8</v>
+        <v>-20.7</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>995</v>
@@ -3795,7 +3903,7 @@
         <v>699</v>
       </c>
       <c r="T6" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.2">
@@ -3821,7 +3929,7 @@
       </c>
       <c r="G7" s="3">
         <f t="shared" si="0"/>
-        <v>-26.799999999999994</v>
+        <v>-26.699999999999992</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>985</v>
@@ -3839,7 +3947,7 @@
         <v>699</v>
       </c>
       <c r="T7" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
@@ -3865,7 +3973,7 @@
       </c>
       <c r="G8" s="3">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>33.099999999999994</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
@@ -3908,7 +4016,13 @@
       </c>
       <c r="G9" s="3">
         <f t="shared" si="0"/>
-        <v>-4.8999999999999995</v>
+        <v>-4.8</v>
+      </c>
+      <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>1030</v>
       </c>
       <c r="K9" t="s">
         <v>672</v>
@@ -3954,7 +4068,7 @@
       </c>
       <c r="G10" s="3">
         <f t="shared" si="0"/>
-        <v>5.0999999999999996</v>
+        <v>5.1999999999999993</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>895</v>
@@ -4009,7 +4123,7 @@
       </c>
       <c r="G11" s="3">
         <f t="shared" si="0"/>
-        <v>-6.6999999999999993</v>
+        <v>-6.6000000000000014</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>812</v>
@@ -4064,7 +4178,7 @@
       </c>
       <c r="G12" s="3">
         <f t="shared" si="0"/>
-        <v>47.800000000000004</v>
+        <v>47.9</v>
       </c>
       <c r="H12" t="s">
         <v>21</v>
@@ -4119,7 +4233,7 @@
       </c>
       <c r="G13" s="3">
         <f t="shared" si="0"/>
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="H13" t="s">
         <v>22</v>
@@ -4174,7 +4288,7 @@
       </c>
       <c r="G14" s="3">
         <f t="shared" si="0"/>
-        <v>-11.7</v>
+        <v>-11.599999999999998</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>883</v>
@@ -4229,7 +4343,7 @@
       </c>
       <c r="G15" s="3">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>814</v>
@@ -4284,7 +4398,7 @@
       </c>
       <c r="G16" s="3">
         <f t="shared" si="0"/>
-        <v>30.3</v>
+        <v>30.400000000000002</v>
       </c>
       <c r="H16" t="s">
         <v>25</v>
@@ -4339,7 +4453,7 @@
       </c>
       <c r="G17" s="3">
         <f t="shared" si="0"/>
-        <v>-8.1000000000000014</v>
+        <v>-8</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>884</v>
@@ -4394,7 +4508,7 @@
       </c>
       <c r="G18" s="3">
         <f t="shared" si="0"/>
-        <v>-22.8</v>
+        <v>-22.7</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>817</v>
@@ -4449,7 +4563,7 @@
       </c>
       <c r="G19" s="3">
         <f t="shared" si="0"/>
-        <v>-37.099999999999994</v>
+        <v>-37</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>29</v>
@@ -4504,7 +4618,7 @@
       </c>
       <c r="G20" s="3">
         <f t="shared" si="0"/>
-        <v>-7.3999999999999986</v>
+        <v>-7.3000000000000007</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>31</v>
@@ -4559,7 +4673,7 @@
       </c>
       <c r="G21" s="3">
         <f t="shared" si="0"/>
-        <v>-16.7</v>
+        <v>-16.599999999999998</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>33</v>
@@ -4614,7 +4728,7 @@
       </c>
       <c r="G22" s="3">
         <f t="shared" si="0"/>
-        <v>-31.699999999999996</v>
+        <v>-31.6</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>35</v>
@@ -4669,7 +4783,7 @@
       </c>
       <c r="G23" s="3">
         <f t="shared" si="0"/>
-        <v>20.399999999999999</v>
+        <v>20.5</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>740</v>
@@ -4725,7 +4839,7 @@
       </c>
       <c r="G24" s="3">
         <f t="shared" si="0"/>
-        <v>32.799999999999997</v>
+        <v>32.900000000000006</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>37</v>
@@ -4780,7 +4894,7 @@
       </c>
       <c r="G25" s="3">
         <f t="shared" si="0"/>
-        <v>18.3</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>742</v>
@@ -4836,7 +4950,7 @@
       </c>
       <c r="G26" s="3">
         <f t="shared" si="0"/>
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>38</v>
@@ -4891,7 +5005,7 @@
       </c>
       <c r="G27" s="3">
         <f t="shared" si="0"/>
-        <v>-12.400000000000002</v>
+        <v>-12.3</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>744</v>
@@ -4946,7 +5060,7 @@
       </c>
       <c r="G28" s="3">
         <f t="shared" si="0"/>
-        <v>16.5</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>791</v>
@@ -5001,7 +5115,7 @@
       </c>
       <c r="G29" s="3">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="H29" t="s">
         <v>40</v>
@@ -5056,7 +5170,7 @@
       </c>
       <c r="G30" s="3">
         <f t="shared" si="0"/>
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="H30" t="s">
         <v>41</v>
@@ -5111,7 +5225,7 @@
       </c>
       <c r="G31" s="3">
         <f t="shared" si="0"/>
-        <v>19.600000000000001</v>
+        <v>19.7</v>
       </c>
       <c r="H31" t="s">
         <v>42</v>
@@ -5167,7 +5281,7 @@
       </c>
       <c r="G32" s="3">
         <f t="shared" si="0"/>
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="H32" t="s">
         <v>43</v>
@@ -5222,7 +5336,7 @@
       </c>
       <c r="G33" s="3">
         <f t="shared" si="0"/>
-        <v>75.900000000000006</v>
+        <v>76</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>737</v>
@@ -5277,7 +5391,7 @@
       </c>
       <c r="G34" s="3">
         <f t="shared" si="0"/>
-        <v>82</v>
+        <v>82.1</v>
       </c>
       <c r="H34" t="s">
         <v>45</v>
@@ -5332,7 +5446,7 @@
       </c>
       <c r="G35" s="3">
         <f t="shared" si="0"/>
-        <v>8.6000000000000014</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="H35" t="s">
         <v>46</v>
@@ -5387,7 +5501,7 @@
       </c>
       <c r="G36" s="3">
         <f t="shared" si="0"/>
-        <v>42.900000000000006</v>
+        <v>43</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>749</v>
@@ -5442,7 +5556,7 @@
       </c>
       <c r="G37" s="3">
         <f t="shared" si="0"/>
-        <v>56</v>
+        <v>56.099999999999994</v>
       </c>
       <c r="H37" t="s">
         <v>48</v>
@@ -5497,7 +5611,7 @@
       </c>
       <c r="G38" s="3">
         <f t="shared" si="0"/>
-        <v>56.300000000000004</v>
+        <v>56.4</v>
       </c>
       <c r="H38" t="s">
         <v>49</v>
@@ -5552,7 +5666,7 @@
       </c>
       <c r="G39" s="3">
         <f t="shared" si="0"/>
-        <v>47.1</v>
+        <v>47.199999999999996</v>
       </c>
       <c r="H39" t="s">
         <v>50</v>
@@ -5607,7 +5721,7 @@
       </c>
       <c r="G40" s="3">
         <f t="shared" si="0"/>
-        <v>36.6</v>
+        <v>36.699999999999996</v>
       </c>
       <c r="H40" t="s">
         <v>51</v>
@@ -5662,7 +5776,7 @@
       </c>
       <c r="G41" s="3">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>42.599999999999994</v>
       </c>
       <c r="H41" t="s">
         <v>52</v>
@@ -5717,7 +5831,7 @@
       </c>
       <c r="G42" s="3">
         <f t="shared" si="0"/>
-        <v>-24.000000000000004</v>
+        <v>-23.900000000000002</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>753</v>
@@ -5772,7 +5886,7 @@
       </c>
       <c r="G43" s="3">
         <f t="shared" si="0"/>
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="H43" t="s">
         <v>54</v>
@@ -5827,7 +5941,7 @@
       </c>
       <c r="G44" s="3">
         <f t="shared" si="0"/>
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>794</v>
@@ -5882,7 +5996,7 @@
       </c>
       <c r="G45" s="3">
         <f t="shared" si="0"/>
-        <v>-11.100000000000001</v>
+        <v>-11</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>773</v>
@@ -5937,7 +6051,7 @@
       </c>
       <c r="G46" s="3">
         <f t="shared" si="0"/>
-        <v>33.099999999999994</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="H46" t="s">
         <v>57</v>
@@ -5993,7 +6107,7 @@
       </c>
       <c r="G47" s="3">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="H47" t="s">
         <v>58</v>
@@ -6048,7 +6162,7 @@
       </c>
       <c r="G48" s="3">
         <f t="shared" si="0"/>
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="H48" s="4" t="s">
         <v>735</v>
@@ -6103,7 +6217,7 @@
       </c>
       <c r="G49" s="3">
         <f t="shared" si="0"/>
-        <v>17.899999999999999</v>
+        <v>18</v>
       </c>
       <c r="H49" t="s">
         <v>60</v>
@@ -6159,7 +6273,7 @@
       </c>
       <c r="G50" s="3">
         <f t="shared" si="0"/>
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="H50" t="s">
         <v>61</v>
@@ -6214,7 +6328,7 @@
       </c>
       <c r="G51" s="3">
         <f t="shared" si="0"/>
-        <v>41.800000000000004</v>
+        <v>41.9</v>
       </c>
       <c r="H51" t="s">
         <v>62</v>
@@ -6269,7 +6383,7 @@
       </c>
       <c r="G52" s="3">
         <f t="shared" si="0"/>
-        <v>48.1</v>
+        <v>48.199999999999996</v>
       </c>
       <c r="H52" t="s">
         <v>63</v>
@@ -6324,7 +6438,7 @@
       </c>
       <c r="G53" s="3">
         <f t="shared" si="0"/>
-        <v>20.399999999999999</v>
+        <v>20.5</v>
       </c>
       <c r="H53" t="s">
         <v>64</v>
@@ -6379,7 +6493,7 @@
       </c>
       <c r="G54" s="3">
         <f t="shared" si="0"/>
-        <v>33.200000000000003</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="H54" t="s">
         <v>65</v>
@@ -6434,7 +6548,7 @@
       </c>
       <c r="G55" s="3">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="H55" t="s">
         <v>66</v>
@@ -6489,7 +6603,7 @@
       </c>
       <c r="G56" s="3">
         <f t="shared" si="0"/>
-        <v>58.800000000000004</v>
+        <v>58.9</v>
       </c>
       <c r="H56" t="s">
         <v>67</v>
@@ -6544,7 +6658,7 @@
       </c>
       <c r="G57" s="3">
         <f t="shared" si="0"/>
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="H57" t="s">
         <v>68</v>
@@ -6600,7 +6714,7 @@
       </c>
       <c r="G58" s="3">
         <f t="shared" si="0"/>
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
       <c r="H58" t="s">
         <v>69</v>
@@ -6655,7 +6769,7 @@
       </c>
       <c r="G59" s="3">
         <f t="shared" si="0"/>
-        <v>68.599999999999994</v>
+        <v>68.7</v>
       </c>
       <c r="H59" t="s">
         <v>70</v>
@@ -6710,7 +6824,7 @@
       </c>
       <c r="G60" s="3">
         <f t="shared" si="0"/>
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="H60" s="4" t="s">
         <v>732</v>
@@ -6766,7 +6880,7 @@
       </c>
       <c r="G61" s="3">
         <f t="shared" si="0"/>
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="H61" t="s">
         <v>71</v>
@@ -6822,7 +6936,7 @@
       </c>
       <c r="G62" s="3">
         <f t="shared" si="0"/>
-        <v>-3.9999999999999991</v>
+        <v>-3.8999999999999995</v>
       </c>
       <c r="I62" s="6" t="s">
         <v>757</v>
@@ -6877,7 +6991,7 @@
       </c>
       <c r="G63" s="3">
         <f t="shared" si="0"/>
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="H63" t="s">
         <v>73</v>
@@ -6932,7 +7046,7 @@
       </c>
       <c r="G64" s="3">
         <f t="shared" si="0"/>
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="H64" t="s">
         <v>74</v>
@@ -6987,7 +7101,7 @@
       </c>
       <c r="G65" s="3">
         <f t="shared" si="0"/>
-        <v>57.1</v>
+        <v>57.199999999999996</v>
       </c>
       <c r="H65" t="s">
         <v>75</v>
@@ -7042,7 +7156,7 @@
       </c>
       <c r="G66" s="3">
         <f t="shared" si="0"/>
-        <v>43.300000000000004</v>
+        <v>43.4</v>
       </c>
       <c r="H66" t="s">
         <v>76</v>
@@ -7097,8 +7211,8 @@
         <v>10.100000000000001</v>
       </c>
       <c r="G67" s="3">
-        <f t="shared" ref="G67:G130" si="1">E67+6.7+1.5</f>
-        <v>12.1</v>
+        <f t="shared" ref="G67:G130" si="1">E67+6.8+1.5</f>
+        <v>12.2</v>
       </c>
       <c r="H67" t="s">
         <v>77</v>
@@ -7153,7 +7267,7 @@
       </c>
       <c r="G68" s="3">
         <f t="shared" si="1"/>
-        <v>24.3</v>
+        <v>24.400000000000002</v>
       </c>
       <c r="H68" t="s">
         <v>78</v>
@@ -7208,7 +7322,7 @@
       </c>
       <c r="G69" s="3">
         <f t="shared" si="1"/>
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="H69" t="s">
         <v>79</v>
@@ -7263,7 +7377,7 @@
       </c>
       <c r="G70" s="3">
         <f t="shared" si="1"/>
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="H70" s="4" t="s">
         <v>761</v>
@@ -7319,7 +7433,7 @@
       </c>
       <c r="G71" s="3">
         <f t="shared" si="1"/>
-        <v>20.3</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="H71" t="s">
         <v>81</v>
@@ -7374,7 +7488,7 @@
       </c>
       <c r="G72" s="3">
         <f t="shared" si="1"/>
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="H72" t="s">
         <v>82</v>
@@ -7429,7 +7543,7 @@
       </c>
       <c r="G73" s="3">
         <f t="shared" si="1"/>
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="H73" t="s">
         <v>83</v>
@@ -7484,7 +7598,7 @@
       </c>
       <c r="G74" s="3">
         <f t="shared" si="1"/>
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="H74" t="s">
         <v>84</v>
@@ -7539,7 +7653,7 @@
       </c>
       <c r="G75" s="3">
         <f t="shared" si="1"/>
-        <v>64.099999999999994</v>
+        <v>64.199999999999989</v>
       </c>
       <c r="H75" s="4" t="s">
         <v>886</v>
@@ -7594,7 +7708,7 @@
       </c>
       <c r="G76" s="3">
         <f t="shared" si="1"/>
-        <v>48</v>
+        <v>48.099999999999994</v>
       </c>
       <c r="H76" t="s">
         <v>86</v>
@@ -7649,7 +7763,7 @@
       </c>
       <c r="G77" s="3">
         <f t="shared" si="1"/>
-        <v>-1.4999999999999991</v>
+        <v>-1.3999999999999995</v>
       </c>
       <c r="H77" s="4" t="s">
         <v>889</v>
@@ -7704,7 +7818,7 @@
       </c>
       <c r="G78" s="3">
         <f t="shared" si="1"/>
-        <v>-10.100000000000001</v>
+        <v>-10</v>
       </c>
       <c r="H78" s="4" t="s">
         <v>890</v>
@@ -7759,7 +7873,7 @@
       </c>
       <c r="G79" s="3">
         <f t="shared" si="1"/>
-        <v>-0.89999999999999947</v>
+        <v>-0.79999999999999982</v>
       </c>
       <c r="H79" s="4" t="s">
         <v>891</v>
@@ -7814,7 +7928,7 @@
       </c>
       <c r="G80" s="3">
         <f t="shared" si="1"/>
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>90</v>
@@ -7869,7 +7983,7 @@
       </c>
       <c r="G81" s="3">
         <f t="shared" si="1"/>
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>91</v>
@@ -7924,7 +8038,7 @@
       </c>
       <c r="G82" s="3">
         <f t="shared" si="1"/>
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H82" s="4" t="s">
         <v>894</v>
@@ -7979,7 +8093,7 @@
       </c>
       <c r="G83" s="3">
         <f t="shared" si="1"/>
-        <v>31.099999999999998</v>
+        <v>31.2</v>
       </c>
       <c r="H83" s="4" t="s">
         <v>974</v>
@@ -8034,7 +8148,7 @@
       </c>
       <c r="G84" s="3">
         <f t="shared" si="1"/>
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="H84" t="s">
         <v>94</v>
@@ -8089,7 +8203,7 @@
       </c>
       <c r="G85" s="3">
         <f t="shared" si="1"/>
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="H85" t="s">
         <v>95</v>
@@ -8144,7 +8258,7 @@
       </c>
       <c r="G86" s="3">
         <f t="shared" si="1"/>
-        <v>31.599999999999998</v>
+        <v>31.7</v>
       </c>
       <c r="H86" t="s">
         <v>96</v>
@@ -8199,7 +8313,7 @@
       </c>
       <c r="G87" s="3">
         <f t="shared" si="1"/>
-        <v>13.8</v>
+        <v>13.899999999999999</v>
       </c>
       <c r="H87" t="s">
         <v>97</v>
@@ -8254,7 +8368,7 @@
       </c>
       <c r="G88" s="3">
         <f t="shared" si="1"/>
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="K88" t="s">
         <v>675</v>
@@ -8304,7 +8418,13 @@
       </c>
       <c r="G89" s="3">
         <f t="shared" si="1"/>
-        <v>-28.700000000000006</v>
+        <v>-28.600000000000005</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="K89" t="s">
         <v>673</v>
@@ -8328,7 +8448,7 @@
         <v>699</v>
       </c>
       <c r="T89" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.2">
@@ -8354,7 +8474,13 @@
       </c>
       <c r="G90" s="3">
         <f t="shared" si="1"/>
-        <v>-9.8000000000000007</v>
+        <v>-9.6999999999999993</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I90" s="4" t="s">
+        <v>1018</v>
       </c>
       <c r="K90" t="s">
         <v>673</v>
@@ -8378,7 +8504,7 @@
         <v>699</v>
       </c>
       <c r="T90" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.2">
@@ -8404,7 +8530,13 @@
       </c>
       <c r="G91" s="3">
         <f t="shared" si="1"/>
-        <v>-12.7</v>
+        <v>-12.599999999999998</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>1019</v>
+      </c>
+      <c r="I91" t="s">
+        <v>101</v>
       </c>
       <c r="K91" t="s">
         <v>676</v>
@@ -8428,7 +8560,7 @@
         <v>699</v>
       </c>
       <c r="T91" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.2">
@@ -8454,7 +8586,13 @@
       </c>
       <c r="G92" s="3">
         <f t="shared" si="1"/>
-        <v>-3.6000000000000041</v>
+        <v>-3.5000000000000044</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I92" t="s">
+        <v>102</v>
       </c>
       <c r="K92" t="s">
         <v>676</v>
@@ -8478,7 +8616,7 @@
         <v>699</v>
       </c>
       <c r="T92" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.2">
@@ -8504,7 +8642,13 @@
       </c>
       <c r="G93" s="3">
         <f t="shared" si="1"/>
-        <v>-13.2</v>
+        <v>-13.099999999999998</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="I93" t="s">
+        <v>103</v>
       </c>
       <c r="K93" t="s">
         <v>676</v>
@@ -8528,7 +8672,7 @@
         <v>699</v>
       </c>
       <c r="T93" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.2">
@@ -8554,7 +8698,13 @@
       </c>
       <c r="G94" s="3">
         <f t="shared" si="1"/>
-        <v>-21.8</v>
+        <v>-21.7</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>1024</v>
+      </c>
+      <c r="I94" t="s">
+        <v>104</v>
       </c>
       <c r="K94" t="s">
         <v>676</v>
@@ -8578,7 +8728,7 @@
         <v>699</v>
       </c>
       <c r="T94" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.2">
@@ -8604,7 +8754,13 @@
       </c>
       <c r="G95" s="3">
         <f t="shared" si="1"/>
-        <v>-4.1999999999999984</v>
+        <v>-4.0999999999999988</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="I95" s="4" t="s">
+        <v>1016</v>
       </c>
       <c r="K95" t="s">
         <v>676</v>
@@ -8628,7 +8784,7 @@
         <v>699</v>
       </c>
       <c r="T95" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.2">
@@ -8654,7 +8810,13 @@
       </c>
       <c r="G96" s="3">
         <f t="shared" si="1"/>
-        <v>-7.899999999999995</v>
+        <v>-7.7999999999999936</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>997</v>
+      </c>
+      <c r="I96" t="s">
+        <v>998</v>
       </c>
       <c r="K96" t="s">
         <v>676</v>
@@ -8678,7 +8840,7 @@
         <v>699</v>
       </c>
       <c r="T96" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.2">
@@ -8704,7 +8866,10 @@
       </c>
       <c r="G97" s="3">
         <f t="shared" si="1"/>
-        <v>-9.5000000000000036</v>
+        <v>-9.4000000000000021</v>
+      </c>
+      <c r="H97" t="s">
+        <v>107</v>
       </c>
       <c r="K97" t="s">
         <v>676</v>
@@ -8728,7 +8893,7 @@
         <v>699</v>
       </c>
       <c r="T97" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="98" spans="1:20" x14ac:dyDescent="0.2">
@@ -8754,7 +8919,10 @@
       </c>
       <c r="G98" s="3">
         <f t="shared" si="1"/>
-        <v>32.099999999999994</v>
+        <v>32.200000000000003</v>
+      </c>
+      <c r="H98" t="s">
+        <v>108</v>
       </c>
       <c r="K98" t="s">
         <v>676</v>
@@ -8778,7 +8946,7 @@
         <v>699</v>
       </c>
       <c r="T98" t="s">
-        <v>702</v>
+        <v>770</v>
       </c>
     </row>
     <row r="99" spans="1:20" x14ac:dyDescent="0.2">
@@ -8804,7 +8972,10 @@
       </c>
       <c r="G99" s="3">
         <f t="shared" si="1"/>
-        <v>-7.5000000000000036</v>
+        <v>-7.4000000000000021</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>1008</v>
       </c>
       <c r="K99" t="s">
         <v>676</v>
@@ -8828,7 +8999,7 @@
         <v>699</v>
       </c>
       <c r="T99" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="100" spans="1:20" x14ac:dyDescent="0.2">
@@ -8854,7 +9025,13 @@
       </c>
       <c r="G100" s="3">
         <f t="shared" si="1"/>
-        <v>-7.0999999999999979</v>
+        <v>-6.9999999999999964</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I100" t="s">
+        <v>110</v>
       </c>
       <c r="K100" t="s">
         <v>676</v>
@@ -8878,7 +9055,7 @@
         <v>699</v>
       </c>
       <c r="T100" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="101" spans="1:20" x14ac:dyDescent="0.2">
@@ -8904,7 +9081,13 @@
       </c>
       <c r="G101" s="3">
         <f t="shared" si="1"/>
-        <v>-5.599999999999997</v>
+        <v>-5.4999999999999973</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>999</v>
+      </c>
+      <c r="I101" t="s">
+        <v>111</v>
       </c>
       <c r="K101" t="s">
         <v>676</v>
@@ -8928,7 +9111,7 @@
         <v>699</v>
       </c>
       <c r="T101" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="102" spans="1:20" x14ac:dyDescent="0.2">
@@ -8954,7 +9137,13 @@
       </c>
       <c r="G102" s="3">
         <f t="shared" si="1"/>
-        <v>-2.2999999999999998</v>
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="H102" t="s">
+        <v>112</v>
+      </c>
+      <c r="I102" s="4" t="s">
+        <v>1006</v>
       </c>
       <c r="K102" t="s">
         <v>676</v>
@@ -8978,7 +9167,7 @@
         <v>699</v>
       </c>
       <c r="T102" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="103" spans="1:20" x14ac:dyDescent="0.2">
@@ -9004,7 +9193,13 @@
       </c>
       <c r="G103" s="3">
         <f t="shared" si="1"/>
-        <v>-11.600000000000005</v>
+        <v>-11.500000000000004</v>
+      </c>
+      <c r="H103" s="4" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I103" t="s">
+        <v>113</v>
       </c>
       <c r="K103" t="s">
         <v>676</v>
@@ -9028,7 +9223,7 @@
         <v>699</v>
       </c>
       <c r="T103" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="104" spans="1:20" x14ac:dyDescent="0.2">
@@ -9054,7 +9249,13 @@
       </c>
       <c r="G104" s="3">
         <f t="shared" si="1"/>
-        <v>-5.4000000000000012</v>
+        <v>-5.3000000000000016</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I104" s="4" t="s">
+        <v>1010</v>
       </c>
       <c r="K104" t="s">
         <v>676</v>
@@ -9078,7 +9279,7 @@
         <v>699</v>
       </c>
       <c r="T104" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.2">
@@ -9104,7 +9305,13 @@
       </c>
       <c r="G105" s="3">
         <f t="shared" si="1"/>
-        <v>-13.8</v>
+        <v>-13.7</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="I105" t="s">
+        <v>115</v>
       </c>
       <c r="K105" t="s">
         <v>676</v>
@@ -9128,7 +9335,7 @@
         <v>699</v>
       </c>
       <c r="T105" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="106" spans="1:20" x14ac:dyDescent="0.2">
@@ -9154,7 +9361,13 @@
       </c>
       <c r="G106" s="3">
         <f t="shared" si="1"/>
-        <v>-8.6999999999999993</v>
+        <v>-8.5999999999999979</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>1025</v>
+      </c>
+      <c r="I106" t="s">
+        <v>1000</v>
       </c>
       <c r="K106" t="s">
         <v>676</v>
@@ -9178,7 +9391,7 @@
         <v>699</v>
       </c>
       <c r="T106" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="107" spans="1:20" x14ac:dyDescent="0.2">
@@ -9204,7 +9417,13 @@
       </c>
       <c r="G107" s="3">
         <f t="shared" si="1"/>
-        <v>-22.800000000000008</v>
+        <v>-22.700000000000006</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I107" s="4" t="s">
+        <v>1013</v>
       </c>
       <c r="K107" t="s">
         <v>676</v>
@@ -9228,7 +9447,7 @@
         <v>699</v>
       </c>
       <c r="T107" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="108" spans="1:20" x14ac:dyDescent="0.2">
@@ -9254,7 +9473,13 @@
       </c>
       <c r="G108" s="3">
         <f t="shared" si="1"/>
-        <v>45.20000000000001</v>
+        <v>45.300000000000004</v>
+      </c>
+      <c r="H108" t="s">
+        <v>122</v>
+      </c>
+      <c r="I108" s="4" t="s">
+        <v>1007</v>
       </c>
       <c r="K108" t="s">
         <v>676</v>
@@ -9278,7 +9503,7 @@
         <v>699</v>
       </c>
       <c r="T108" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="109" spans="1:20" x14ac:dyDescent="0.2">
@@ -9304,7 +9529,10 @@
       </c>
       <c r="G109" s="3">
         <f t="shared" si="1"/>
-        <v>-8.0000000000000036</v>
+        <v>-7.9000000000000021</v>
+      </c>
+      <c r="I109" t="s">
+        <v>118</v>
       </c>
       <c r="K109" t="s">
         <v>676</v>
@@ -9328,7 +9556,7 @@
         <v>699</v>
       </c>
       <c r="T109" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="110" spans="1:20" x14ac:dyDescent="0.2">
@@ -9354,7 +9582,13 @@
       </c>
       <c r="G110" s="3">
         <f t="shared" si="1"/>
-        <v>-2.2999999999999998</v>
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="H110" s="4" t="s">
+        <v>1001</v>
+      </c>
+      <c r="I110" s="4" t="s">
+        <v>1011</v>
       </c>
       <c r="K110" t="s">
         <v>676</v>
@@ -9378,7 +9612,7 @@
         <v>699</v>
       </c>
       <c r="T110" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="111" spans="1:20" x14ac:dyDescent="0.2">
@@ -9404,7 +9638,13 @@
       </c>
       <c r="G111" s="3">
         <f t="shared" si="1"/>
-        <v>21.999999999999996</v>
+        <v>22.099999999999998</v>
+      </c>
+      <c r="H111" t="s">
+        <v>119</v>
+      </c>
+      <c r="I111" s="4" t="s">
+        <v>1009</v>
       </c>
       <c r="K111" t="s">
         <v>676</v>
@@ -9428,7 +9668,7 @@
         <v>699</v>
       </c>
       <c r="T111" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="112" spans="1:20" x14ac:dyDescent="0.2">
@@ -9454,7 +9694,13 @@
       </c>
       <c r="G112" s="3">
         <f t="shared" si="1"/>
-        <v>46.800000000000004</v>
+        <v>46.9</v>
+      </c>
+      <c r="H112" s="4" t="s">
+        <v>1027</v>
+      </c>
+      <c r="I112" s="4" t="s">
+        <v>1002</v>
       </c>
       <c r="K112" t="s">
         <v>676</v>
@@ -9478,7 +9724,7 @@
         <v>699</v>
       </c>
       <c r="T112" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="113" spans="1:20" x14ac:dyDescent="0.2">
@@ -9504,7 +9750,13 @@
       </c>
       <c r="G113" s="3">
         <f t="shared" si="1"/>
-        <v>-1.0000000000000027</v>
+        <v>-0.90000000000000302</v>
+      </c>
+      <c r="H113" t="s">
+        <v>120</v>
+      </c>
+      <c r="I113" s="4" t="s">
+        <v>1022</v>
       </c>
       <c r="K113" t="s">
         <v>676</v>
@@ -9528,7 +9780,7 @@
         <v>699</v>
       </c>
       <c r="T113" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="114" spans="1:20" x14ac:dyDescent="0.2">
@@ -9554,7 +9806,13 @@
       </c>
       <c r="G114" s="3">
         <f t="shared" si="1"/>
-        <v>-10.100000000000005</v>
+        <v>-10.000000000000004</v>
+      </c>
+      <c r="H114" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I114" t="s">
+        <v>123</v>
       </c>
       <c r="K114" t="s">
         <v>676</v>
@@ -9578,7 +9836,7 @@
         <v>699</v>
       </c>
       <c r="T114" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="115" spans="1:20" x14ac:dyDescent="0.2">
@@ -9604,7 +9862,13 @@
       </c>
       <c r="G115" s="3">
         <f t="shared" si="1"/>
-        <v>-6.3</v>
+        <v>-6.2</v>
+      </c>
+      <c r="H115" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I115" t="s">
+        <v>124</v>
       </c>
       <c r="K115" t="s">
         <v>676</v>
@@ -9628,7 +9892,7 @@
         <v>699</v>
       </c>
       <c r="T115" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="116" spans="1:20" x14ac:dyDescent="0.2">
@@ -9654,7 +9918,13 @@
       </c>
       <c r="G116" s="3">
         <f t="shared" si="1"/>
-        <v>-17.200000000000006</v>
+        <v>-17.100000000000005</v>
+      </c>
+      <c r="H116" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="I116" s="6" t="s">
+        <v>125</v>
       </c>
       <c r="K116" t="s">
         <v>676</v>
@@ -9678,7 +9948,7 @@
         <v>699</v>
       </c>
       <c r="T116" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="117" spans="1:20" x14ac:dyDescent="0.2">
@@ -9703,7 +9973,7 @@
       </c>
       <c r="G117" s="3">
         <f t="shared" si="1"/>
-        <v>-7.5</v>
+        <v>-7.3999999999999986</v>
       </c>
       <c r="H117" s="4" t="s">
         <v>823</v>
@@ -9758,7 +10028,7 @@
       </c>
       <c r="G118" s="3">
         <f t="shared" si="1"/>
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="H118" t="s">
         <v>127</v>
@@ -9814,7 +10084,7 @@
       </c>
       <c r="G119" s="3">
         <f t="shared" si="1"/>
-        <v>-22.8</v>
+        <v>-22.7</v>
       </c>
       <c r="H119" s="4" t="s">
         <v>130</v>
@@ -9869,7 +10139,7 @@
       </c>
       <c r="G120" s="3">
         <f t="shared" si="1"/>
-        <v>60.400000000000006</v>
+        <v>60.5</v>
       </c>
       <c r="H120" t="s">
         <v>131</v>
@@ -9925,7 +10195,7 @@
       </c>
       <c r="G121" s="3">
         <f t="shared" si="1"/>
-        <v>80.3</v>
+        <v>80.399999999999991</v>
       </c>
       <c r="H121" t="s">
         <v>133</v>
@@ -9981,7 +10251,7 @@
       </c>
       <c r="G122" s="3">
         <f t="shared" si="1"/>
-        <v>58.2</v>
+        <v>58.3</v>
       </c>
       <c r="H122" t="s">
         <v>135</v>
@@ -10036,7 +10306,7 @@
       </c>
       <c r="G123" s="3">
         <f t="shared" si="1"/>
-        <v>-12.900000000000002</v>
+        <v>-12.8</v>
       </c>
       <c r="H123" s="4" t="s">
         <v>826</v>
@@ -10092,7 +10362,7 @@
       </c>
       <c r="G124" s="3">
         <f t="shared" si="1"/>
-        <v>-23.1</v>
+        <v>-23</v>
       </c>
       <c r="H124" s="4" t="s">
         <v>138</v>
@@ -10148,7 +10418,7 @@
       </c>
       <c r="G125" s="3">
         <f t="shared" si="1"/>
-        <v>-26.7</v>
+        <v>-26.599999999999998</v>
       </c>
       <c r="H125" s="4" t="s">
         <v>140</v>
@@ -10204,7 +10474,7 @@
       </c>
       <c r="G126" s="3">
         <f t="shared" si="1"/>
-        <v>-13.7</v>
+        <v>-13.599999999999998</v>
       </c>
       <c r="H126" s="4" t="s">
         <v>827</v>
@@ -10260,7 +10530,7 @@
       </c>
       <c r="G127" s="3">
         <f t="shared" si="1"/>
-        <v>-15.5</v>
+        <v>-15.399999999999999</v>
       </c>
       <c r="H127" s="4" t="s">
         <v>144</v>
@@ -10315,7 +10585,7 @@
       </c>
       <c r="G128" s="3">
         <f t="shared" si="1"/>
-        <v>-5.8999999999999995</v>
+        <v>-5.8</v>
       </c>
       <c r="H128" s="4" t="s">
         <v>829</v>
@@ -10370,7 +10640,7 @@
       </c>
       <c r="G129" s="3">
         <f t="shared" si="1"/>
-        <v>50.6</v>
+        <v>50.699999999999996</v>
       </c>
       <c r="H129" s="4" t="s">
         <v>146</v>
@@ -10426,7 +10696,7 @@
       </c>
       <c r="G130" s="3">
         <f t="shared" si="1"/>
-        <v>-29.2</v>
+        <v>-29.099999999999998</v>
       </c>
       <c r="H130" s="4" t="s">
         <v>149</v>
@@ -10480,8 +10750,8 @@
         <v>29.4</v>
       </c>
       <c r="G131" s="3">
-        <f t="shared" ref="G131:G194" si="2">E131+6.7+1.5</f>
-        <v>32.9</v>
+        <f t="shared" ref="G131:G194" si="2">E131+6.8+1.5</f>
+        <v>33</v>
       </c>
       <c r="H131" s="6" t="s">
         <v>150</v>
@@ -10536,7 +10806,7 @@
       </c>
       <c r="G132" s="3">
         <f t="shared" si="2"/>
-        <v>29.8</v>
+        <v>29.900000000000002</v>
       </c>
       <c r="H132" s="6" t="s">
         <v>151</v>
@@ -10591,7 +10861,7 @@
       </c>
       <c r="G133" s="3">
         <f t="shared" si="2"/>
-        <v>-36.9</v>
+        <v>-36.800000000000004</v>
       </c>
       <c r="H133" s="4" t="s">
         <v>153</v>
@@ -10646,7 +10916,7 @@
       </c>
       <c r="G134" s="3">
         <f t="shared" si="2"/>
-        <v>-18.5</v>
+        <v>-18.399999999999999</v>
       </c>
       <c r="H134" s="4" t="s">
         <v>155</v>
@@ -10701,7 +10971,7 @@
       </c>
       <c r="G135" s="3">
         <f t="shared" si="2"/>
-        <v>40.200000000000003</v>
+        <v>40.299999999999997</v>
       </c>
       <c r="H135" s="6" t="s">
         <v>156</v>
@@ -10757,7 +11027,7 @@
       </c>
       <c r="G136" s="3">
         <f t="shared" si="2"/>
-        <v>41.300000000000004</v>
+        <v>41.4</v>
       </c>
       <c r="H136" s="4" t="s">
         <v>159</v>
@@ -10813,7 +11083,7 @@
       </c>
       <c r="G137" s="3">
         <f t="shared" si="2"/>
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="H137" s="6" t="s">
         <v>161</v>
@@ -10869,7 +11139,7 @@
       </c>
       <c r="G138" s="3">
         <f t="shared" si="2"/>
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="H138" s="4" t="s">
         <v>164</v>
@@ -10925,7 +11195,7 @@
       </c>
       <c r="G139" s="3">
         <f t="shared" si="2"/>
-        <v>45.400000000000006</v>
+        <v>45.5</v>
       </c>
       <c r="H139" s="6" t="s">
         <v>166</v>
@@ -10981,7 +11251,7 @@
       </c>
       <c r="G140" s="3">
         <f t="shared" si="2"/>
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="H140" s="6" t="s">
         <v>168</v>
@@ -11037,7 +11307,7 @@
       </c>
       <c r="G141" s="3">
         <f t="shared" si="2"/>
-        <v>73.7</v>
+        <v>73.8</v>
       </c>
       <c r="H141" s="4" t="s">
         <v>171</v>
@@ -11093,7 +11363,7 @@
       </c>
       <c r="G142" s="3">
         <f t="shared" si="2"/>
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="H142" s="4" t="s">
         <v>174</v>
@@ -11149,7 +11419,7 @@
       </c>
       <c r="G143" s="3">
         <f t="shared" si="2"/>
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
       <c r="H143" s="4" t="s">
         <v>177</v>
@@ -11205,7 +11475,7 @@
       </c>
       <c r="G144" s="3">
         <f t="shared" si="2"/>
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="H144" s="6" t="s">
         <v>179</v>
@@ -11261,7 +11531,7 @@
       </c>
       <c r="G145" s="3">
         <f t="shared" si="2"/>
-        <v>19.600000000000001</v>
+        <v>19.7</v>
       </c>
       <c r="H145" s="6" t="s">
         <v>181</v>
@@ -11317,7 +11587,7 @@
       </c>
       <c r="G146" s="3">
         <f t="shared" si="2"/>
-        <v>-35.299999999999997</v>
+        <v>-35.200000000000003</v>
       </c>
       <c r="H146" s="4" t="s">
         <v>184</v>
@@ -11372,7 +11642,7 @@
       </c>
       <c r="G147" s="3">
         <f t="shared" si="2"/>
-        <v>18.899999999999999</v>
+        <v>19</v>
       </c>
       <c r="H147" s="6" t="s">
         <v>185</v>
@@ -11428,7 +11698,7 @@
       </c>
       <c r="G148" s="3">
         <f t="shared" si="2"/>
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="H148" s="6" t="s">
         <v>187</v>
@@ -11484,7 +11754,7 @@
       </c>
       <c r="G149" s="3">
         <f t="shared" si="2"/>
-        <v>-31.699999999999996</v>
+        <v>-31.6</v>
       </c>
       <c r="H149" s="4" t="s">
         <v>190</v>
@@ -11540,7 +11810,7 @@
       </c>
       <c r="G150" s="3">
         <f t="shared" si="2"/>
-        <v>-14.5</v>
+        <v>-14.399999999999999</v>
       </c>
       <c r="H150" s="4" t="s">
         <v>192</v>
@@ -11596,7 +11866,7 @@
       </c>
       <c r="G151" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="H151" t="s">
         <v>193</v>
@@ -11652,7 +11922,7 @@
       </c>
       <c r="G152" s="3">
         <f t="shared" si="2"/>
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="H152" t="s">
         <v>195</v>
@@ -11708,7 +11978,7 @@
       </c>
       <c r="G153" s="3">
         <f t="shared" si="2"/>
-        <v>-18.2</v>
+        <v>-18.099999999999998</v>
       </c>
       <c r="H153" s="4" t="s">
         <v>198</v>
@@ -11764,7 +12034,7 @@
       </c>
       <c r="G154" s="3">
         <f t="shared" si="2"/>
-        <v>-23.400000000000002</v>
+        <v>-23.3</v>
       </c>
       <c r="H154" s="4" t="s">
         <v>200</v>
@@ -11820,7 +12090,7 @@
       </c>
       <c r="G155" s="3">
         <f t="shared" si="2"/>
-        <v>-21.5</v>
+        <v>-21.4</v>
       </c>
       <c r="H155" s="4" t="s">
         <v>202</v>
@@ -11876,7 +12146,7 @@
       </c>
       <c r="G156" s="3">
         <f t="shared" si="2"/>
-        <v>-8.5</v>
+        <v>-8.3999999999999986</v>
       </c>
       <c r="H156" s="4" t="s">
         <v>204</v>
@@ -11932,7 +12202,7 @@
       </c>
       <c r="G157" s="3">
         <f t="shared" si="2"/>
-        <v>-24.900000000000002</v>
+        <v>-24.8</v>
       </c>
       <c r="H157" s="4" t="s">
         <v>206</v>
@@ -11988,7 +12258,7 @@
       </c>
       <c r="G158" s="3">
         <f t="shared" si="2"/>
-        <v>49.6</v>
+        <v>49.699999999999996</v>
       </c>
       <c r="H158" s="6" t="s">
         <v>207</v>
@@ -12044,7 +12314,7 @@
       </c>
       <c r="G159" s="3">
         <f t="shared" si="2"/>
-        <v>-28.3</v>
+        <v>-28.2</v>
       </c>
       <c r="H159" s="4" t="s">
         <v>210</v>
@@ -12100,7 +12370,7 @@
       </c>
       <c r="G160" s="3">
         <f t="shared" si="2"/>
-        <v>-22.2</v>
+        <v>-22.099999999999998</v>
       </c>
       <c r="H160" s="4" t="s">
         <v>212</v>
@@ -12156,7 +12426,7 @@
       </c>
       <c r="G161" s="3">
         <f t="shared" si="2"/>
-        <v>-0.29999999999999982</v>
+        <v>-0.20000000000000018</v>
       </c>
       <c r="H161" s="4" t="s">
         <v>718</v>
@@ -12212,7 +12482,7 @@
       </c>
       <c r="G162" s="3">
         <f t="shared" si="2"/>
-        <v>-1.7999999999999998</v>
+        <v>-1.7000000000000002</v>
       </c>
       <c r="H162" s="4" t="s">
         <v>720</v>
@@ -12268,7 +12538,7 @@
       </c>
       <c r="G163" s="3">
         <f t="shared" si="2"/>
-        <v>3.8</v>
+        <v>3.8999999999999995</v>
       </c>
       <c r="H163" s="4" t="s">
         <v>722</v>
@@ -12324,7 +12594,7 @@
       </c>
       <c r="G164" s="3">
         <f t="shared" si="2"/>
-        <v>-23.3</v>
+        <v>-23.2</v>
       </c>
       <c r="H164" s="4" t="s">
         <v>731</v>
@@ -12380,7 +12650,7 @@
       </c>
       <c r="G165" s="3">
         <f t="shared" si="2"/>
-        <v>-23.1</v>
+        <v>-23</v>
       </c>
       <c r="H165" s="4" t="s">
         <v>944</v>
@@ -12435,7 +12705,7 @@
       </c>
       <c r="G166" s="3">
         <f t="shared" si="2"/>
-        <v>-11.5</v>
+        <v>-11.399999999999999</v>
       </c>
       <c r="H166" s="4" t="s">
         <v>914</v>
@@ -12490,7 +12760,7 @@
       </c>
       <c r="G167" s="3">
         <f t="shared" si="2"/>
-        <v>12.3</v>
+        <v>12.399999999999999</v>
       </c>
       <c r="H167" s="6" t="s">
         <v>219</v>
@@ -12545,7 +12815,7 @@
       </c>
       <c r="G168" s="3">
         <f t="shared" si="2"/>
-        <v>-15.100000000000001</v>
+        <v>-15</v>
       </c>
       <c r="H168" s="4" t="s">
         <v>945</v>
@@ -12600,7 +12870,7 @@
       </c>
       <c r="G169" s="3">
         <f t="shared" si="2"/>
-        <v>-39.099999999999994</v>
+        <v>-39</v>
       </c>
       <c r="H169" s="4" t="s">
         <v>222</v>
@@ -12655,7 +12925,7 @@
       </c>
       <c r="G170" s="3">
         <f t="shared" si="2"/>
-        <v>-33.099999999999994</v>
+        <v>-33</v>
       </c>
       <c r="H170" s="4" t="s">
         <v>224</v>
@@ -12710,7 +12980,7 @@
       </c>
       <c r="G171" s="3">
         <f t="shared" si="2"/>
-        <v>27.099999999999998</v>
+        <v>27.2</v>
       </c>
       <c r="H171" t="s">
         <v>225</v>
@@ -12766,7 +13036,7 @@
       </c>
       <c r="G172" s="3">
         <f t="shared" si="2"/>
-        <v>-27.3</v>
+        <v>-27.2</v>
       </c>
       <c r="H172" s="4" t="s">
         <v>228</v>
@@ -12822,7 +13092,7 @@
       </c>
       <c r="G173" s="3">
         <f t="shared" si="2"/>
-        <v>-55.699999999999996</v>
+        <v>-55.6</v>
       </c>
       <c r="H173" s="4" t="s">
         <v>231</v>
@@ -12877,7 +13147,7 @@
       </c>
       <c r="G174" s="3">
         <f t="shared" si="2"/>
-        <v>-6.8000000000000007</v>
+        <v>-6.6999999999999993</v>
       </c>
       <c r="H174" s="4" t="s">
         <v>233</v>
@@ -12934,7 +13204,7 @@
       </c>
       <c r="G175" s="3">
         <f t="shared" si="2"/>
-        <v>-30.2</v>
+        <v>-30.099999999999998</v>
       </c>
       <c r="K175" t="s">
         <v>673</v>
@@ -12972,7 +13242,7 @@
       </c>
       <c r="G176" s="3">
         <f t="shared" si="2"/>
-        <v>55.9</v>
+        <v>55.999999999999993</v>
       </c>
       <c r="K176" t="s">
         <v>673</v>
@@ -13010,7 +13280,7 @@
       </c>
       <c r="G177" s="3">
         <f t="shared" si="2"/>
-        <v>-28.000000000000004</v>
+        <v>-27.900000000000002</v>
       </c>
       <c r="K177" t="s">
         <v>673</v>
@@ -13048,7 +13318,7 @@
       </c>
       <c r="G178" s="3">
         <f t="shared" si="2"/>
-        <v>-26.000000000000004</v>
+        <v>-25.900000000000002</v>
       </c>
       <c r="K178" t="s">
         <v>673</v>
@@ -13086,7 +13356,7 @@
       </c>
       <c r="G179" s="3">
         <f t="shared" si="2"/>
-        <v>-25.800000000000008</v>
+        <v>-25.700000000000006</v>
       </c>
       <c r="K179" t="s">
         <v>673</v>
@@ -13124,7 +13394,7 @@
       </c>
       <c r="G180" s="3">
         <f t="shared" si="2"/>
-        <v>-23.599999999999998</v>
+        <v>-23.499999999999996</v>
       </c>
       <c r="K180" t="s">
         <v>673</v>
@@ -13161,7 +13431,7 @@
       </c>
       <c r="G181" s="3">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="H181" t="s">
         <v>241</v>
@@ -13216,7 +13486,7 @@
       </c>
       <c r="G182" s="3">
         <f t="shared" si="2"/>
-        <v>-1.2999999999999998</v>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="H182" s="4" t="s">
         <v>830</v>
@@ -13271,7 +13541,7 @@
       </c>
       <c r="G183" s="3">
         <f t="shared" si="2"/>
-        <v>-8.6000000000000014</v>
+        <v>-8.5</v>
       </c>
       <c r="H183" s="4" t="s">
         <v>864</v>
@@ -13326,7 +13596,7 @@
       </c>
       <c r="G184" s="3">
         <f t="shared" si="2"/>
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="H184" t="s">
         <v>244</v>
@@ -13381,7 +13651,7 @@
       </c>
       <c r="G185" s="3">
         <f t="shared" si="2"/>
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="H185" t="s">
         <v>245</v>
@@ -13436,7 +13706,7 @@
       </c>
       <c r="G186" s="3">
         <f t="shared" si="2"/>
-        <v>81.400000000000006</v>
+        <v>81.5</v>
       </c>
       <c r="H186" t="s">
         <v>246</v>
@@ -13491,7 +13761,7 @@
       </c>
       <c r="G187" s="3">
         <f t="shared" si="2"/>
-        <v>41.300000000000004</v>
+        <v>41.4</v>
       </c>
       <c r="H187" s="4" t="s">
         <v>865</v>
@@ -13546,7 +13816,7 @@
       </c>
       <c r="G188" s="3">
         <f t="shared" si="2"/>
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="H188" t="s">
         <v>248</v>
@@ -13601,7 +13871,7 @@
       </c>
       <c r="G189" s="3">
         <f t="shared" si="2"/>
-        <v>66.8</v>
+        <v>66.900000000000006</v>
       </c>
       <c r="H189" t="s">
         <v>249</v>
@@ -13656,7 +13926,7 @@
       </c>
       <c r="G190" s="3">
         <f t="shared" si="2"/>
-        <v>64</v>
+        <v>64.099999999999994</v>
       </c>
       <c r="H190" t="s">
         <v>250</v>
@@ -13711,7 +13981,7 @@
       </c>
       <c r="G191" s="3">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="K191" t="s">
         <v>662</v>
@@ -13760,7 +14030,7 @@
       </c>
       <c r="G192" s="3">
         <f t="shared" si="2"/>
-        <v>31.8</v>
+        <v>31.900000000000002</v>
       </c>
       <c r="K192" t="s">
         <v>662</v>
@@ -13809,7 +14079,7 @@
       </c>
       <c r="G193" s="3">
         <f t="shared" si="2"/>
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="K193" t="s">
         <v>662</v>
@@ -13858,7 +14128,7 @@
       </c>
       <c r="G194" s="3">
         <f t="shared" si="2"/>
-        <v>27.8</v>
+        <v>27.900000000000002</v>
       </c>
       <c r="K194" t="s">
         <v>662</v>
@@ -13906,8 +14176,8 @@
         <v>50.900000000000006</v>
       </c>
       <c r="G195" s="3">
-        <f t="shared" ref="G195:G258" si="3">E195+6.7+1.5</f>
-        <v>53.1</v>
+        <f t="shared" ref="G195:G258" si="3">E195+6.8+1.5</f>
+        <v>53.199999999999996</v>
       </c>
       <c r="K195" t="s">
         <v>662</v>
@@ -13956,7 +14226,7 @@
       </c>
       <c r="G196" s="3">
         <f t="shared" si="3"/>
-        <v>28.8</v>
+        <v>28.900000000000002</v>
       </c>
       <c r="K196" t="s">
         <v>662</v>
@@ -14005,7 +14275,7 @@
       </c>
       <c r="G197" s="3">
         <f t="shared" si="3"/>
-        <v>70.900000000000006</v>
+        <v>71</v>
       </c>
       <c r="K197" t="s">
         <v>662</v>
@@ -14054,7 +14324,7 @@
       </c>
       <c r="G198" s="3">
         <f t="shared" si="3"/>
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="K198" t="s">
         <v>662</v>
@@ -14103,7 +14373,7 @@
       </c>
       <c r="G199" s="3">
         <f t="shared" si="3"/>
-        <v>18.899999999999999</v>
+        <v>19</v>
       </c>
       <c r="K199" t="s">
         <v>662</v>
@@ -14152,7 +14422,7 @@
       </c>
       <c r="G200" s="3">
         <f t="shared" si="3"/>
-        <v>-13</v>
+        <v>-12.899999999999999</v>
       </c>
       <c r="H200" s="4" t="s">
         <v>943</v>
@@ -14207,7 +14477,7 @@
       </c>
       <c r="G201" s="3">
         <f t="shared" si="3"/>
-        <v>-21.7</v>
+        <v>-21.599999999999998</v>
       </c>
       <c r="H201" s="4" t="s">
         <v>961</v>
@@ -14262,7 +14532,7 @@
       </c>
       <c r="G202" s="3">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="H202" t="s">
         <v>261</v>
@@ -14317,7 +14587,7 @@
       </c>
       <c r="G203" s="3">
         <f t="shared" si="3"/>
-        <v>2.5</v>
+        <v>2.5999999999999996</v>
       </c>
       <c r="H203" s="4" t="s">
         <v>935</v>
@@ -14372,7 +14642,7 @@
       </c>
       <c r="G204" s="3">
         <f t="shared" si="3"/>
-        <v>-18.900000000000002</v>
+        <v>-18.8</v>
       </c>
       <c r="H204" s="4" t="s">
         <v>908</v>
@@ -14427,7 +14697,7 @@
       </c>
       <c r="G205" s="3">
         <f t="shared" si="3"/>
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="H205" t="s">
         <v>264</v>
@@ -14482,7 +14752,7 @@
       </c>
       <c r="G206" s="3">
         <f t="shared" si="3"/>
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="H206" s="4" t="s">
         <v>929</v>
@@ -14537,7 +14807,7 @@
       </c>
       <c r="G207" s="3">
         <f t="shared" si="3"/>
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="H207" t="s">
         <v>266</v>
@@ -14592,7 +14862,7 @@
       </c>
       <c r="G208" s="3">
         <f t="shared" si="3"/>
-        <v>-24.099999999999998</v>
+        <v>-23.999999999999996</v>
       </c>
       <c r="H208" s="4" t="s">
         <v>910</v>
@@ -14647,7 +14917,7 @@
       </c>
       <c r="G209" s="3">
         <f t="shared" si="3"/>
-        <v>1.7000000000000002</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="H209" s="4" t="s">
         <v>940</v>
@@ -14702,7 +14972,7 @@
       </c>
       <c r="G210" s="3">
         <f t="shared" si="3"/>
-        <v>24.3</v>
+        <v>24.400000000000002</v>
       </c>
       <c r="H210" s="4" t="s">
         <v>920</v>
@@ -14757,7 +15027,7 @@
       </c>
       <c r="G211" s="3">
         <f t="shared" si="3"/>
-        <v>45.900000000000006</v>
+        <v>46</v>
       </c>
       <c r="H211" t="s">
         <v>270</v>
@@ -14812,7 +15082,7 @@
       </c>
       <c r="G212" s="3">
         <f t="shared" si="3"/>
-        <v>49.6</v>
+        <v>49.699999999999996</v>
       </c>
       <c r="H212" s="4" t="s">
         <v>946</v>
@@ -14867,7 +15137,7 @@
       </c>
       <c r="G213" s="3">
         <f t="shared" si="3"/>
-        <v>-3.8</v>
+        <v>-3.7</v>
       </c>
       <c r="H213" s="4" t="s">
         <v>982</v>
@@ -14922,7 +15192,7 @@
       </c>
       <c r="G214" s="3">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="H214" s="4" t="s">
         <v>980</v>
@@ -14977,7 +15247,7 @@
       </c>
       <c r="G215" s="3">
         <f t="shared" si="3"/>
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="H215" s="6" t="s">
         <v>274</v>
@@ -15032,7 +15302,7 @@
       </c>
       <c r="G216" s="3">
         <f t="shared" si="3"/>
-        <v>43.900000000000006</v>
+        <v>44</v>
       </c>
       <c r="H216" t="s">
         <v>275</v>
@@ -15087,7 +15357,7 @@
       </c>
       <c r="G217" s="3">
         <f t="shared" si="3"/>
-        <v>70.099999999999994</v>
+        <v>70.2</v>
       </c>
       <c r="H217" s="6" t="s">
         <v>276</v>
@@ -15142,7 +15412,7 @@
       </c>
       <c r="G218" s="3">
         <f t="shared" si="3"/>
-        <v>-11.5</v>
+        <v>-11.399999999999999</v>
       </c>
       <c r="H218" s="4" t="s">
         <v>983</v>
@@ -15197,7 +15467,7 @@
       </c>
       <c r="G219" s="3">
         <f t="shared" si="3"/>
-        <v>-28.3</v>
+        <v>-28.2</v>
       </c>
       <c r="H219" s="4" t="s">
         <v>986</v>
@@ -15252,7 +15522,7 @@
       </c>
       <c r="G220" s="3">
         <f t="shared" si="3"/>
-        <v>-6.1000000000000005</v>
+        <v>-6.0000000000000009</v>
       </c>
       <c r="H220" t="s">
         <v>981</v>
@@ -15307,7 +15577,7 @@
       </c>
       <c r="G221" s="3">
         <f t="shared" si="3"/>
-        <v>-28.8</v>
+        <v>-28.7</v>
       </c>
       <c r="H221" s="4" t="s">
         <v>281</v>
@@ -15362,7 +15632,7 @@
       </c>
       <c r="G222" s="3">
         <f t="shared" si="3"/>
-        <v>28.599999999999998</v>
+        <v>28.7</v>
       </c>
       <c r="H222" t="s">
         <v>282</v>
@@ -15418,7 +15688,7 @@
       </c>
       <c r="G223" s="3">
         <f t="shared" si="3"/>
-        <v>-21</v>
+        <v>-20.9</v>
       </c>
       <c r="H223" s="4" t="s">
         <v>285</v>
@@ -15473,7 +15743,7 @@
       </c>
       <c r="G224" s="3">
         <f t="shared" si="3"/>
-        <v>-34.299999999999997</v>
+        <v>-34.200000000000003</v>
       </c>
       <c r="H224" s="4" t="s">
         <v>287</v>
@@ -15528,7 +15798,7 @@
       </c>
       <c r="G225" s="3">
         <f t="shared" si="3"/>
-        <v>65.7</v>
+        <v>65.8</v>
       </c>
       <c r="H225" s="6" t="s">
         <v>288</v>
@@ -15583,7 +15853,7 @@
       </c>
       <c r="G226" s="3">
         <f t="shared" si="3"/>
-        <v>-3.1000000000000005</v>
+        <v>-3.0000000000000009</v>
       </c>
       <c r="H226" s="4" t="s">
         <v>941</v>
@@ -15638,7 +15908,7 @@
       </c>
       <c r="G227" s="3">
         <f t="shared" si="3"/>
-        <v>-11.7</v>
+        <v>-11.599999999999998</v>
       </c>
       <c r="H227" s="4" t="s">
         <v>919</v>
@@ -15693,7 +15963,7 @@
       </c>
       <c r="G228" s="3">
         <f t="shared" si="3"/>
-        <v>-12.8</v>
+        <v>-12.7</v>
       </c>
       <c r="H228" s="4" t="s">
         <v>938</v>
@@ -15748,7 +16018,7 @@
       </c>
       <c r="G229" s="3">
         <f t="shared" si="3"/>
-        <v>-10.100000000000001</v>
+        <v>-10</v>
       </c>
       <c r="H229" t="s">
         <v>916</v>
@@ -15803,7 +16073,7 @@
       </c>
       <c r="G230" s="3">
         <f t="shared" si="3"/>
-        <v>-18.400000000000002</v>
+        <v>-18.3</v>
       </c>
       <c r="H230" s="4" t="s">
         <v>924</v>
@@ -15858,7 +16128,7 @@
       </c>
       <c r="G231" s="3">
         <f t="shared" si="3"/>
-        <v>-34.4</v>
+        <v>-34.300000000000004</v>
       </c>
       <c r="H231" s="4" t="s">
         <v>917</v>
@@ -15913,7 +16183,7 @@
       </c>
       <c r="G232" s="3">
         <f t="shared" si="3"/>
-        <v>-45.599999999999994</v>
+        <v>-45.5</v>
       </c>
       <c r="H232" s="4" t="s">
         <v>939</v>
@@ -15968,7 +16238,7 @@
       </c>
       <c r="G233" s="3">
         <f t="shared" si="3"/>
-        <v>-3.3</v>
+        <v>-3.2</v>
       </c>
       <c r="H233" s="4" t="s">
         <v>765</v>
@@ -16024,7 +16294,7 @@
       </c>
       <c r="G234" s="3">
         <f t="shared" si="3"/>
-        <v>-21.3</v>
+        <v>-21.2</v>
       </c>
       <c r="H234" s="4" t="s">
         <v>764</v>
@@ -16080,7 +16350,7 @@
       </c>
       <c r="G235" s="3">
         <f t="shared" si="3"/>
-        <v>-4.8999999999999995</v>
+        <v>-4.8</v>
       </c>
       <c r="H235" s="4" t="s">
         <v>299</v>
@@ -16135,7 +16405,7 @@
       </c>
       <c r="G236" s="3">
         <f t="shared" si="3"/>
-        <v>12.8</v>
+        <v>12.899999999999999</v>
       </c>
       <c r="H236" s="4" t="s">
         <v>301</v>
@@ -16191,7 +16461,7 @@
       </c>
       <c r="G237" s="3">
         <f t="shared" si="3"/>
-        <v>-45.599999999999994</v>
+        <v>-45.5</v>
       </c>
       <c r="H237" s="4" t="s">
         <v>304</v>
@@ -16246,7 +16516,7 @@
       </c>
       <c r="G238" s="3">
         <f t="shared" si="3"/>
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="H238" s="6" t="s">
         <v>305</v>
@@ -16301,7 +16571,7 @@
       </c>
       <c r="G239" s="3">
         <f t="shared" si="3"/>
-        <v>-5.8</v>
+        <v>-5.7</v>
       </c>
       <c r="H239" s="4" t="s">
         <v>802</v>
@@ -16356,7 +16626,7 @@
       </c>
       <c r="G240" s="3">
         <f t="shared" si="3"/>
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="H240" s="6" t="s">
         <v>307</v>
@@ -16411,7 +16681,7 @@
       </c>
       <c r="G241" s="3">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="H241" t="s">
         <v>800</v>
@@ -16466,7 +16736,7 @@
       </c>
       <c r="G242" s="3">
         <f t="shared" si="3"/>
-        <v>10.199999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="K242" t="s">
         <v>662</v>
@@ -16515,7 +16785,7 @@
       </c>
       <c r="G243" s="3">
         <f t="shared" si="3"/>
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="K243" t="s">
         <v>662</v>
@@ -16564,7 +16834,7 @@
       </c>
       <c r="G244" s="3">
         <f t="shared" si="3"/>
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="H244" t="s">
         <v>311</v>
@@ -16620,7 +16890,7 @@
       </c>
       <c r="G245" s="3">
         <f t="shared" si="3"/>
-        <v>-4.3999999999999995</v>
+        <v>-4.3</v>
       </c>
       <c r="H245" s="4" t="s">
         <v>707</v>
@@ -16675,7 +16945,7 @@
       </c>
       <c r="G246" s="3">
         <f t="shared" si="3"/>
-        <v>16.600000000000001</v>
+        <v>16.7</v>
       </c>
       <c r="H246" t="s">
         <v>313</v>
@@ -16731,7 +17001,7 @@
       </c>
       <c r="G247" s="3">
         <f t="shared" si="3"/>
-        <v>-21.900000000000002</v>
+        <v>-21.8</v>
       </c>
       <c r="H247" s="4" t="s">
         <v>709</v>
@@ -16786,7 +17056,7 @@
       </c>
       <c r="G248" s="3">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="H248" t="s">
         <v>315</v>
@@ -16842,7 +17112,7 @@
       </c>
       <c r="G249" s="3">
         <f t="shared" si="3"/>
-        <v>14.600000000000001</v>
+        <v>14.7</v>
       </c>
       <c r="H249" s="6" t="s">
         <v>316</v>
@@ -16898,7 +17168,7 @@
       </c>
       <c r="G250" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="H250" s="4" t="s">
         <v>712</v>
@@ -16953,7 +17223,7 @@
       </c>
       <c r="G251" s="3">
         <f t="shared" si="3"/>
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="H251" t="s">
         <v>318</v>
@@ -17005,7 +17275,7 @@
       </c>
       <c r="G252" s="3">
         <f t="shared" si="3"/>
-        <v>7.1</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="H252" t="s">
         <v>319</v>
@@ -17060,7 +17330,7 @@
       </c>
       <c r="G253" s="3">
         <f t="shared" si="3"/>
-        <v>59</v>
+        <v>59.099999999999994</v>
       </c>
       <c r="H253" t="s">
         <v>320</v>
@@ -17116,7 +17386,7 @@
       </c>
       <c r="G254" s="3">
         <f t="shared" si="3"/>
-        <v>16.899999999999999</v>
+        <v>17</v>
       </c>
       <c r="H254" t="s">
         <v>714</v>
@@ -17172,7 +17442,7 @@
       </c>
       <c r="G255" s="3">
         <f t="shared" si="3"/>
-        <v>32.099999999999994</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="H255" s="4" t="s">
         <v>716</v>
@@ -17228,7 +17498,7 @@
       </c>
       <c r="G256" s="3">
         <f t="shared" si="3"/>
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="H256" t="s">
         <v>323</v>
@@ -17283,7 +17553,7 @@
       </c>
       <c r="G257" s="3">
         <f t="shared" si="3"/>
-        <v>6.3000000000000007</v>
+        <v>6.4</v>
       </c>
       <c r="H257" t="s">
         <v>777</v>
@@ -17338,7 +17608,7 @@
       </c>
       <c r="G258" s="3">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="H258" t="s">
         <v>325</v>
@@ -17392,8 +17662,8 @@
         <v>-1.8000000000000043</v>
       </c>
       <c r="G259" s="3">
-        <f t="shared" ref="G259:G322" si="4">E259+6.7+1.5</f>
-        <v>-1.8999999999999995</v>
+        <f t="shared" ref="G259:G322" si="4">E259+6.8+1.5</f>
+        <v>-1.7999999999999998</v>
       </c>
       <c r="H259" s="4" t="s">
         <v>832</v>
@@ -17448,7 +17718,7 @@
       </c>
       <c r="G260" s="3">
         <f t="shared" si="4"/>
-        <v>-5.7</v>
+        <v>-5.6000000000000005</v>
       </c>
       <c r="H260" s="4" t="s">
         <v>833</v>
@@ -17503,7 +17773,7 @@
       </c>
       <c r="G261" s="3">
         <f t="shared" si="4"/>
-        <v>3.9000000000000004</v>
+        <v>4</v>
       </c>
       <c r="H261" t="s">
         <v>328</v>
@@ -17558,7 +17828,7 @@
       </c>
       <c r="G262" s="3">
         <f t="shared" si="4"/>
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="H262" t="s">
         <v>329</v>
@@ -17613,7 +17883,7 @@
       </c>
       <c r="G263" s="3">
         <f t="shared" si="4"/>
-        <v>50.400000000000006</v>
+        <v>50.5</v>
       </c>
       <c r="H263" t="s">
         <v>330</v>
@@ -17668,7 +17938,7 @@
       </c>
       <c r="G264" s="3">
         <f t="shared" si="4"/>
-        <v>14.600000000000001</v>
+        <v>14.7</v>
       </c>
       <c r="H264" t="s">
         <v>331</v>
@@ -17723,7 +17993,7 @@
       </c>
       <c r="G265" s="3">
         <f t="shared" si="4"/>
-        <v>54.1</v>
+        <v>54.199999999999996</v>
       </c>
       <c r="H265" s="4" t="s">
         <v>838</v>
@@ -17778,7 +18048,7 @@
       </c>
       <c r="G266" s="3">
         <f t="shared" si="4"/>
-        <v>52.2</v>
+        <v>52.3</v>
       </c>
       <c r="H266" t="s">
         <v>333</v>
@@ -17833,7 +18103,7 @@
       </c>
       <c r="G267" s="3">
         <f t="shared" si="4"/>
-        <v>48.800000000000004</v>
+        <v>48.9</v>
       </c>
       <c r="H267" t="s">
         <v>334</v>
@@ -17888,7 +18158,7 @@
       </c>
       <c r="G268" s="3">
         <f t="shared" si="4"/>
-        <v>68.599999999999994</v>
+        <v>68.7</v>
       </c>
       <c r="H268" s="4" t="s">
         <v>842</v>
@@ -17943,7 +18213,7 @@
       </c>
       <c r="G269" s="3">
         <f t="shared" si="4"/>
-        <v>-16.2</v>
+        <v>-16.099999999999998</v>
       </c>
       <c r="H269" s="4" t="s">
         <v>844</v>
@@ -17998,7 +18268,7 @@
       </c>
       <c r="G270" s="3">
         <f t="shared" si="4"/>
-        <v>71.8</v>
+        <v>71.900000000000006</v>
       </c>
       <c r="H270" s="4" t="s">
         <v>845</v>
@@ -18053,7 +18323,7 @@
       </c>
       <c r="G271" s="3">
         <f t="shared" si="4"/>
-        <v>67.5</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="H271" s="4" t="s">
         <v>847</v>
@@ -18108,7 +18378,7 @@
       </c>
       <c r="G272" s="3">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="H272" s="6" t="s">
         <v>339</v>
@@ -18163,7 +18433,7 @@
       </c>
       <c r="G273" s="3">
         <f t="shared" si="4"/>
-        <v>56.5</v>
+        <v>56.599999999999994</v>
       </c>
       <c r="H273" s="6" t="s">
         <v>340</v>
@@ -18218,7 +18488,7 @@
       </c>
       <c r="G274" s="3">
         <f t="shared" si="4"/>
-        <v>41.300000000000004</v>
+        <v>41.4</v>
       </c>
       <c r="H274" s="6" t="s">
         <v>341</v>
@@ -18273,7 +18543,7 @@
       </c>
       <c r="G275" s="3">
         <f t="shared" si="4"/>
-        <v>8.8000000000000007</v>
+        <v>8.8999999999999986</v>
       </c>
       <c r="H275" s="4" t="s">
         <v>852</v>
@@ -18328,7 +18598,7 @@
       </c>
       <c r="G276" s="3">
         <f t="shared" si="4"/>
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="H276" s="6" t="s">
         <v>343</v>
@@ -18383,7 +18653,7 @@
       </c>
       <c r="G277" s="3">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="H277" s="6" t="s">
         <v>344</v>
@@ -18439,7 +18709,7 @@
       </c>
       <c r="G278" s="3">
         <f t="shared" si="4"/>
-        <v>22.400000000000002</v>
+        <v>22.500000000000004</v>
       </c>
       <c r="H278" s="6" t="s">
         <v>345</v>
@@ -18494,7 +18764,7 @@
       </c>
       <c r="G279" s="3">
         <f t="shared" si="4"/>
-        <v>-12.5</v>
+        <v>-12.399999999999999</v>
       </c>
       <c r="H279" s="4" t="s">
         <v>856</v>
@@ -18549,7 +18819,7 @@
       </c>
       <c r="G280" s="3">
         <f t="shared" si="4"/>
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="H280" s="6" t="s">
         <v>347</v>
@@ -18604,7 +18874,7 @@
       </c>
       <c r="G281" s="3">
         <f t="shared" si="4"/>
-        <v>-12.8</v>
+        <v>-12.7</v>
       </c>
       <c r="H281" s="4" t="s">
         <v>859</v>
@@ -18659,7 +18929,7 @@
       </c>
       <c r="G282" s="3">
         <f t="shared" si="4"/>
-        <v>-14.900000000000002</v>
+        <v>-14.8</v>
       </c>
       <c r="H282" s="4" t="s">
         <v>860</v>
@@ -18714,7 +18984,7 @@
       </c>
       <c r="G283" s="3">
         <f t="shared" si="4"/>
-        <v>26.599999999999998</v>
+        <v>26.7</v>
       </c>
       <c r="H283" s="6" t="s">
         <v>861</v>
@@ -18769,7 +19039,7 @@
       </c>
       <c r="G284" s="3">
         <f t="shared" si="4"/>
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="H284" s="6" t="s">
         <v>351</v>
@@ -18824,7 +19094,7 @@
       </c>
       <c r="G285" s="3">
         <f t="shared" si="4"/>
-        <v>-3.3999999999999995</v>
+        <v>-3.3</v>
       </c>
       <c r="H285" t="s">
         <v>352</v>
@@ -18880,7 +19150,7 @@
       </c>
       <c r="G286" s="3">
         <f t="shared" si="4"/>
-        <v>42.5</v>
+        <v>42.599999999999994</v>
       </c>
       <c r="H286" t="s">
         <v>354</v>
@@ -18936,7 +19206,7 @@
       </c>
       <c r="G287" s="3">
         <f t="shared" si="4"/>
-        <v>-5.3999999999999995</v>
+        <v>-5.3</v>
       </c>
       <c r="H287" s="4" t="s">
         <v>357</v>
@@ -18991,7 +19261,7 @@
       </c>
       <c r="G288" s="3">
         <f t="shared" si="4"/>
-        <v>53.5</v>
+        <v>53.599999999999994</v>
       </c>
       <c r="H288" s="6" t="s">
         <v>358</v>
@@ -19047,7 +19317,7 @@
       </c>
       <c r="G289" s="3">
         <f t="shared" si="4"/>
-        <v>-9.6000000000000014</v>
+        <v>-9.5</v>
       </c>
       <c r="H289" s="4" t="s">
         <v>361</v>
@@ -19102,7 +19372,7 @@
       </c>
       <c r="G290" s="3">
         <f t="shared" si="4"/>
-        <v>-8.8000000000000007</v>
+        <v>-8.6999999999999993</v>
       </c>
       <c r="H290" s="4" t="s">
         <v>363</v>
@@ -19157,7 +19427,7 @@
       </c>
       <c r="G291" s="3">
         <f t="shared" si="4"/>
-        <v>-5.6000000000000005</v>
+        <v>-5.5000000000000009</v>
       </c>
       <c r="H291" s="4" t="s">
         <v>365</v>
@@ -19212,7 +19482,7 @@
       </c>
       <c r="G292" s="3">
         <f t="shared" si="4"/>
-        <v>-11.400000000000002</v>
+        <v>-11.3</v>
       </c>
       <c r="H292" s="4" t="s">
         <v>368</v>
@@ -19267,7 +19537,7 @@
       </c>
       <c r="G293" s="3">
         <f t="shared" si="4"/>
-        <v>-7.6000000000000014</v>
+        <v>-7.5</v>
       </c>
       <c r="H293" s="4" t="s">
         <v>370</v>
@@ -19322,7 +19592,7 @@
       </c>
       <c r="G294" s="3">
         <f t="shared" si="4"/>
-        <v>-9.5</v>
+        <v>-9.3999999999999986</v>
       </c>
       <c r="H294" s="4" t="s">
         <v>372</v>
@@ -19377,7 +19647,7 @@
       </c>
       <c r="G295" s="3">
         <f t="shared" si="4"/>
-        <v>-1.2999999999999998</v>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="H295" s="4" t="s">
         <v>374</v>
@@ -19432,7 +19702,7 @@
       </c>
       <c r="G296" s="3">
         <f t="shared" si="4"/>
-        <v>54.400000000000006</v>
+        <v>54.5</v>
       </c>
       <c r="H296" s="6" t="s">
         <v>375</v>
@@ -19488,7 +19758,7 @@
       </c>
       <c r="G297" s="3">
         <f t="shared" si="4"/>
-        <v>-8.6000000000000014</v>
+        <v>-8.5</v>
       </c>
       <c r="H297" s="4" t="s">
         <v>378</v>
@@ -19543,7 +19813,7 @@
       </c>
       <c r="G298" s="3">
         <f t="shared" si="4"/>
-        <v>-6.8999999999999986</v>
+        <v>-6.8000000000000007</v>
       </c>
       <c r="H298" s="4" t="s">
         <v>380</v>
@@ -19598,7 +19868,7 @@
       </c>
       <c r="G299" s="3">
         <f t="shared" si="4"/>
-        <v>-28.599999999999998</v>
+        <v>-28.499999999999996</v>
       </c>
       <c r="H299" s="4" t="s">
         <v>896</v>
@@ -19653,7 +19923,7 @@
       </c>
       <c r="G300" s="3">
         <f t="shared" si="4"/>
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H300" s="6" t="s">
         <v>382</v>
@@ -19709,7 +19979,7 @@
       </c>
       <c r="G301" s="3">
         <f t="shared" si="4"/>
-        <v>-33.9</v>
+        <v>-33.800000000000004</v>
       </c>
       <c r="H301" s="4" t="s">
         <v>385</v>
@@ -19765,7 +20035,7 @@
       </c>
       <c r="G302" s="3">
         <f t="shared" si="4"/>
-        <v>48.400000000000006</v>
+        <v>48.5</v>
       </c>
       <c r="H302" t="s">
         <v>386</v>
@@ -19821,7 +20091,7 @@
       </c>
       <c r="G303" s="3">
         <f t="shared" si="4"/>
-        <v>-34.4</v>
+        <v>-34.300000000000004</v>
       </c>
       <c r="H303" s="4" t="s">
         <v>389</v>
@@ -19877,7 +20147,7 @@
       </c>
       <c r="G304" s="3">
         <f t="shared" si="4"/>
-        <v>-15.5</v>
+        <v>-15.399999999999999</v>
       </c>
       <c r="H304" s="4" t="s">
         <v>391</v>
@@ -19933,7 +20203,7 @@
       </c>
       <c r="G305" s="3">
         <f t="shared" si="4"/>
-        <v>-26.400000000000002</v>
+        <v>-26.3</v>
       </c>
       <c r="H305" s="4" t="s">
         <v>393</v>
@@ -19989,7 +20259,7 @@
       </c>
       <c r="G306" s="3">
         <f t="shared" si="4"/>
-        <v>-2.8</v>
+        <v>-2.7</v>
       </c>
       <c r="H306" s="4" t="s">
         <v>395</v>
@@ -20045,7 +20315,7 @@
       </c>
       <c r="G307" s="3">
         <f t="shared" si="4"/>
-        <v>-7.3999999999999986</v>
+        <v>-7.3000000000000007</v>
       </c>
       <c r="H307" s="4" t="s">
         <v>397</v>
@@ -20101,7 +20371,7 @@
       </c>
       <c r="G308" s="3">
         <f t="shared" si="4"/>
-        <v>-2.2999999999999998</v>
+        <v>-2.2000000000000002</v>
       </c>
       <c r="H308" t="s">
         <v>398</v>
@@ -20157,7 +20427,7 @@
       </c>
       <c r="G309" s="3">
         <f t="shared" si="4"/>
-        <v>0.5</v>
+        <v>0.59999999999999964</v>
       </c>
       <c r="H309" s="4" t="s">
         <v>401</v>
@@ -20213,7 +20483,7 @@
       </c>
       <c r="G310" s="3">
         <f t="shared" si="4"/>
-        <v>63.2</v>
+        <v>63.3</v>
       </c>
       <c r="H310" t="s">
         <v>402</v>
@@ -20269,7 +20539,7 @@
       </c>
       <c r="G311" s="3">
         <f t="shared" si="4"/>
-        <v>-21.8</v>
+        <v>-21.7</v>
       </c>
       <c r="H311" s="4" t="s">
         <v>405</v>
@@ -20324,7 +20594,7 @@
       </c>
       <c r="G312" s="3">
         <f t="shared" si="4"/>
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="H312" t="s">
         <v>406</v>
@@ -20380,7 +20650,7 @@
       </c>
       <c r="G313" s="3">
         <f t="shared" si="4"/>
-        <v>-12.100000000000001</v>
+        <v>-12</v>
       </c>
       <c r="H313" s="4" t="s">
         <v>409</v>
@@ -20435,7 +20705,7 @@
       </c>
       <c r="G314" s="3">
         <f t="shared" si="4"/>
-        <v>-1.7999999999999998</v>
+        <v>-1.7000000000000002</v>
       </c>
       <c r="H314" s="4" t="s">
         <v>411</v>
@@ -20490,7 +20760,7 @@
       </c>
       <c r="G315" s="3">
         <f t="shared" si="4"/>
-        <v>-13.3</v>
+        <v>-13.2</v>
       </c>
       <c r="K315" t="s">
         <v>678</v>
@@ -20539,7 +20809,7 @@
       </c>
       <c r="G316" s="3">
         <f t="shared" si="4"/>
-        <v>-47.4</v>
+        <v>-47.300000000000004</v>
       </c>
       <c r="K316" t="s">
         <v>678</v>
@@ -20588,7 +20858,7 @@
       </c>
       <c r="G317" s="3">
         <f t="shared" si="4"/>
-        <v>-36.599999999999994</v>
+        <v>-36.5</v>
       </c>
       <c r="K317" t="s">
         <v>678</v>
@@ -20637,7 +20907,7 @@
       </c>
       <c r="G318" s="3">
         <f t="shared" si="4"/>
-        <v>-24.7</v>
+        <v>-24.599999999999998</v>
       </c>
       <c r="K318" t="s">
         <v>678</v>
@@ -20686,7 +20956,7 @@
       </c>
       <c r="G319" s="3">
         <f t="shared" si="4"/>
-        <v>-10</v>
+        <v>-9.8999999999999986</v>
       </c>
       <c r="K319" t="s">
         <v>678</v>
@@ -20735,7 +21005,7 @@
       </c>
       <c r="G320" s="3">
         <f t="shared" si="4"/>
-        <v>45.800000000000004</v>
+        <v>45.9</v>
       </c>
       <c r="H320" s="6" t="s">
         <v>417</v>
@@ -20791,7 +21061,7 @@
       </c>
       <c r="G321" s="3">
         <f t="shared" si="4"/>
-        <v>-18.900000000000002</v>
+        <v>-18.8</v>
       </c>
       <c r="H321" s="4" t="s">
         <v>420</v>
@@ -20847,7 +21117,7 @@
       </c>
       <c r="G322" s="3">
         <f t="shared" si="4"/>
-        <v>53.800000000000004</v>
+        <v>53.9</v>
       </c>
       <c r="H322" s="6" t="s">
         <v>421</v>
@@ -20902,8 +21172,8 @@
         <v>12.700000000000003</v>
       </c>
       <c r="G323" s="3">
-        <f t="shared" ref="G323:G386" si="5">E323+6.7+1.5</f>
-        <v>20.2</v>
+        <f t="shared" ref="G323:G386" si="5">E323+6.8+1.5</f>
+        <v>20.3</v>
       </c>
       <c r="H323" s="6" t="s">
         <v>423</v>
@@ -20959,7 +21229,7 @@
       </c>
       <c r="G324" s="3">
         <f t="shared" si="5"/>
-        <v>16.8</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="H324" s="6" t="s">
         <v>425</v>
@@ -21015,7 +21285,7 @@
       </c>
       <c r="G325" s="3">
         <f t="shared" si="5"/>
-        <v>19.5</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="H325" s="6" t="s">
         <v>427</v>
@@ -21071,7 +21341,7 @@
       </c>
       <c r="G326" s="3">
         <f t="shared" si="5"/>
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="H326" s="4" t="s">
         <v>430</v>
@@ -21126,7 +21396,7 @@
       </c>
       <c r="G327" s="3">
         <f t="shared" si="5"/>
-        <v>43.900000000000006</v>
+        <v>44</v>
       </c>
       <c r="H327" t="s">
         <v>431</v>
@@ -21182,7 +21452,7 @@
       </c>
       <c r="G328" s="3">
         <f t="shared" si="5"/>
-        <v>85.5</v>
+        <v>85.6</v>
       </c>
       <c r="H328" s="6" t="s">
         <v>434</v>
@@ -21235,7 +21505,7 @@
       </c>
       <c r="G329" s="3">
         <f t="shared" si="5"/>
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="H329" t="s">
         <v>435</v>
@@ -21291,7 +21561,7 @@
       </c>
       <c r="G330" s="3">
         <f t="shared" si="5"/>
-        <v>36.800000000000004</v>
+        <v>36.9</v>
       </c>
       <c r="H330" s="6" t="s">
         <v>437</v>
@@ -21347,7 +21617,7 @@
       </c>
       <c r="G331" s="3">
         <f t="shared" si="5"/>
-        <v>19.600000000000001</v>
+        <v>19.7</v>
       </c>
       <c r="H331" t="s">
         <v>439</v>
@@ -21403,7 +21673,7 @@
       </c>
       <c r="G332" s="3">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="H332" s="4" t="s">
         <v>442</v>
@@ -21459,7 +21729,7 @@
       </c>
       <c r="G333" s="3">
         <f t="shared" si="5"/>
-        <v>-0.29999999999999982</v>
+        <v>-0.20000000000000018</v>
       </c>
       <c r="H333" s="4" t="s">
         <v>444</v>
@@ -21515,7 +21785,7 @@
       </c>
       <c r="G334" s="3">
         <f t="shared" si="5"/>
-        <v>-29.7</v>
+        <v>-29.599999999999998</v>
       </c>
       <c r="H334" s="4" t="s">
         <v>446</v>
@@ -21571,7 +21841,7 @@
       </c>
       <c r="G335" s="3">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>3.0999999999999996</v>
       </c>
       <c r="H335" s="4" t="s">
         <v>448</v>
@@ -21627,7 +21897,7 @@
       </c>
       <c r="G336" s="3">
         <f t="shared" si="5"/>
-        <v>-13.2</v>
+        <v>-13.099999999999998</v>
       </c>
       <c r="H336" s="4" t="s">
         <v>450</v>
@@ -21683,7 +21953,7 @@
       </c>
       <c r="G337" s="3">
         <f t="shared" si="5"/>
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="H337" s="6" t="s">
         <v>451</v>
@@ -21739,7 +22009,7 @@
       </c>
       <c r="G338" s="3">
         <f t="shared" si="5"/>
-        <v>-37.299999999999997</v>
+        <v>-37.200000000000003</v>
       </c>
       <c r="H338" s="4" t="s">
         <v>454</v>
@@ -21795,7 +22065,7 @@
       </c>
       <c r="G339" s="3">
         <f t="shared" si="5"/>
-        <v>-25.2</v>
+        <v>-25.099999999999998</v>
       </c>
       <c r="H339" s="4" t="s">
         <v>456</v>
@@ -21851,7 +22121,7 @@
       </c>
       <c r="G340" s="3">
         <f t="shared" si="5"/>
-        <v>-29.8</v>
+        <v>-29.7</v>
       </c>
       <c r="H340" s="4" t="s">
         <v>458</v>
@@ -21907,7 +22177,7 @@
       </c>
       <c r="G341" s="3">
         <f t="shared" si="5"/>
-        <v>-14.600000000000001</v>
+        <v>-14.5</v>
       </c>
       <c r="H341" s="4" t="s">
         <v>460</v>
@@ -21963,7 +22233,7 @@
       </c>
       <c r="G342" s="3">
         <f t="shared" si="5"/>
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="H342" t="s">
         <v>461</v>
@@ -22019,7 +22289,7 @@
       </c>
       <c r="G343" s="3">
         <f t="shared" si="5"/>
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="K343" t="s">
         <v>662</v>
@@ -22068,7 +22338,7 @@
       </c>
       <c r="G344" s="3">
         <f t="shared" si="5"/>
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="K344" t="s">
         <v>662</v>
@@ -22117,7 +22387,7 @@
       </c>
       <c r="G345" s="3">
         <f t="shared" si="5"/>
-        <v>-4.8999999999999995</v>
+        <v>-4.8</v>
       </c>
       <c r="H345" s="4" t="s">
         <v>873</v>
@@ -22172,7 +22442,7 @@
       </c>
       <c r="G346" s="3">
         <f t="shared" si="5"/>
-        <v>-5.8</v>
+        <v>-5.7</v>
       </c>
       <c r="H346" s="4" t="s">
         <v>875</v>
@@ -22227,7 +22497,7 @@
       </c>
       <c r="G347" s="3">
         <f t="shared" si="5"/>
-        <v>-34.799999999999997</v>
+        <v>-34.700000000000003</v>
       </c>
       <c r="H347" s="4" t="s">
         <v>799</v>
@@ -22282,7 +22552,7 @@
       </c>
       <c r="G348" s="3">
         <f t="shared" si="5"/>
-        <v>-15.400000000000002</v>
+        <v>-15.3</v>
       </c>
       <c r="H348" s="4" t="s">
         <v>786</v>
@@ -22337,7 +22607,7 @@
       </c>
       <c r="G349" s="3">
         <f t="shared" si="5"/>
-        <v>-14.600000000000001</v>
+        <v>-14.5</v>
       </c>
       <c r="H349" s="4" t="s">
         <v>798</v>
@@ -22392,7 +22662,7 @@
       </c>
       <c r="G350" s="3">
         <f t="shared" si="5"/>
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="H350" t="s">
         <v>784</v>
@@ -22447,7 +22717,7 @@
       </c>
       <c r="G351" s="3">
         <f t="shared" si="5"/>
-        <v>-18.2</v>
+        <v>-18.099999999999998</v>
       </c>
       <c r="H351" s="4" t="s">
         <v>788</v>
@@ -22502,7 +22772,7 @@
       </c>
       <c r="G352" s="3">
         <f t="shared" si="5"/>
-        <v>-21</v>
+        <v>-20.9</v>
       </c>
       <c r="H352" s="4" t="s">
         <v>725</v>
@@ -22559,7 +22829,7 @@
       </c>
       <c r="G353" s="3">
         <f t="shared" si="5"/>
-        <v>-49.6</v>
+        <v>-49.500000000000007</v>
       </c>
       <c r="H353" s="4" t="s">
         <v>947</v>
@@ -22615,7 +22885,7 @@
       </c>
       <c r="G354" s="3">
         <f t="shared" si="5"/>
-        <v>-25.600000000000005</v>
+        <v>-25.500000000000004</v>
       </c>
       <c r="H354" s="4" t="s">
         <v>948</v>
@@ -22671,7 +22941,7 @@
       </c>
       <c r="G355" s="3">
         <f t="shared" si="5"/>
-        <v>-27.500000000000004</v>
+        <v>-27.400000000000002</v>
       </c>
       <c r="H355" s="4" t="s">
         <v>949</v>
@@ -22727,7 +22997,7 @@
       </c>
       <c r="G356" s="3">
         <f t="shared" si="5"/>
-        <v>-15.700000000000006</v>
+        <v>-15.600000000000005</v>
       </c>
       <c r="H356" s="4" t="s">
         <v>955</v>
@@ -22783,7 +23053,7 @@
       </c>
       <c r="G357" s="3">
         <f t="shared" si="5"/>
-        <v>-14.900000000000002</v>
+        <v>-14.8</v>
       </c>
       <c r="H357" s="4" t="s">
         <v>958</v>
@@ -22839,7 +23109,7 @@
       </c>
       <c r="G358" s="3">
         <f t="shared" si="5"/>
-        <v>-18.3</v>
+        <v>-18.2</v>
       </c>
       <c r="H358" s="4" t="s">
         <v>956</v>
@@ -22895,7 +23165,7 @@
       </c>
       <c r="G359" s="3">
         <f t="shared" si="5"/>
-        <v>-14.2</v>
+        <v>-14.099999999999998</v>
       </c>
       <c r="H359" s="4" t="s">
         <v>954</v>
@@ -22951,7 +23221,7 @@
       </c>
       <c r="G360" s="3">
         <f t="shared" si="5"/>
-        <v>-11.999999999999996</v>
+        <v>-11.899999999999995</v>
       </c>
       <c r="H360" s="4" t="s">
         <v>952</v>
@@ -23007,7 +23277,7 @@
       </c>
       <c r="G361" s="3">
         <f t="shared" si="5"/>
-        <v>-12.900000000000002</v>
+        <v>-12.8</v>
       </c>
       <c r="H361" s="4" t="s">
         <v>950</v>
@@ -23062,7 +23332,7 @@
       </c>
       <c r="G362" s="3">
         <f t="shared" si="5"/>
-        <v>-41.199999999999996</v>
+        <v>-41.1</v>
       </c>
       <c r="H362" s="4" t="s">
         <v>483</v>
@@ -23117,7 +23387,7 @@
       </c>
       <c r="G363" s="3">
         <f t="shared" si="5"/>
-        <v>-14.600000000000001</v>
+        <v>-14.5</v>
       </c>
       <c r="H363" s="4" t="s">
         <v>485</v>
@@ -23173,7 +23443,7 @@
       </c>
       <c r="G364" s="3">
         <f t="shared" si="5"/>
-        <v>-15.100000000000001</v>
+        <v>-15</v>
       </c>
       <c r="H364" s="4" t="s">
         <v>488</v>
@@ -23228,7 +23498,7 @@
       </c>
       <c r="G365" s="3">
         <f t="shared" si="5"/>
-        <v>-16.400000000000002</v>
+        <v>-16.3</v>
       </c>
       <c r="H365" s="4" t="s">
         <v>490</v>
@@ -23283,7 +23553,7 @@
       </c>
       <c r="G366" s="3">
         <f t="shared" si="5"/>
-        <v>-13.3</v>
+        <v>-13.2</v>
       </c>
       <c r="H366" s="4" t="s">
         <v>492</v>
@@ -23338,7 +23608,7 @@
       </c>
       <c r="G367" s="3">
         <f t="shared" si="5"/>
-        <v>-14.600000000000001</v>
+        <v>-14.5</v>
       </c>
       <c r="H367" s="4" t="s">
         <v>494</v>
@@ -23393,7 +23663,7 @@
       </c>
       <c r="G368" s="3">
         <f t="shared" si="5"/>
-        <v>31.599999999999998</v>
+        <v>31.7</v>
       </c>
       <c r="H368" t="s">
         <v>495</v>
@@ -23449,7 +23719,7 @@
       </c>
       <c r="G369" s="3">
         <f t="shared" si="5"/>
-        <v>-19.400000000000002</v>
+        <v>-19.3</v>
       </c>
       <c r="H369" s="4" t="s">
         <v>498</v>
@@ -23505,7 +23775,7 @@
       </c>
       <c r="G370" s="3">
         <f t="shared" si="5"/>
-        <v>-11.600000000000001</v>
+        <v>-11.5</v>
       </c>
       <c r="H370" s="4" t="s">
         <v>500</v>
@@ -23561,7 +23831,7 @@
       </c>
       <c r="G371" s="3">
         <f t="shared" si="5"/>
-        <v>-14.3</v>
+        <v>-14.2</v>
       </c>
       <c r="H371" s="4" t="s">
         <v>503</v>
@@ -23617,7 +23887,7 @@
       </c>
       <c r="G372" s="3">
         <f t="shared" si="5"/>
-        <v>-26.099999999999998</v>
+        <v>-25.999999999999996</v>
       </c>
       <c r="H372" s="4" t="s">
         <v>506</v>
@@ -23672,7 +23942,7 @@
       </c>
       <c r="G373" s="3">
         <f t="shared" si="5"/>
-        <v>-15.600000000000001</v>
+        <v>-15.5</v>
       </c>
       <c r="H373" s="4" t="s">
         <v>509</v>
@@ -23727,7 +23997,7 @@
       </c>
       <c r="G374" s="3">
         <f t="shared" si="5"/>
-        <v>-37.9</v>
+        <v>-37.800000000000004</v>
       </c>
       <c r="H374" s="4" t="s">
         <v>511</v>
@@ -23782,7 +24052,7 @@
       </c>
       <c r="G375" s="3">
         <f t="shared" si="5"/>
-        <v>-16</v>
+        <v>-15.899999999999999</v>
       </c>
       <c r="H375" s="4" t="s">
         <v>811</v>
@@ -23837,7 +24107,7 @@
       </c>
       <c r="G376" s="3">
         <f t="shared" si="5"/>
-        <v>-9.6000000000000014</v>
+        <v>-9.5</v>
       </c>
       <c r="H376" s="4" t="s">
         <v>514</v>
@@ -23892,7 +24162,7 @@
       </c>
       <c r="G377" s="3">
         <f t="shared" si="5"/>
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="H377" t="s">
         <v>515</v>
@@ -23949,7 +24219,7 @@
       </c>
       <c r="G378" s="3">
         <f t="shared" si="5"/>
-        <v>-9.8000000000000007</v>
+        <v>-9.6999999999999993</v>
       </c>
       <c r="H378" s="4" t="s">
         <v>518</v>
@@ -24004,7 +24274,7 @@
       </c>
       <c r="G379" s="3">
         <f t="shared" si="5"/>
-        <v>63</v>
+        <v>63.099999999999994</v>
       </c>
       <c r="H379" t="s">
         <v>520</v>
@@ -24060,7 +24330,7 @@
       </c>
       <c r="G380" s="3">
         <f t="shared" si="5"/>
-        <v>-43.4</v>
+        <v>-43.300000000000004</v>
       </c>
       <c r="H380" s="4" t="s">
         <v>523</v>
@@ -24116,7 +24386,7 @@
       </c>
       <c r="G381" s="3">
         <f t="shared" si="5"/>
-        <v>36.6</v>
+        <v>36.699999999999996</v>
       </c>
       <c r="H381" t="s">
         <v>525</v>
@@ -24172,7 +24442,7 @@
       </c>
       <c r="G382" s="3">
         <f t="shared" si="5"/>
-        <v>-13.600000000000001</v>
+        <v>-13.5</v>
       </c>
       <c r="H382" s="4" t="s">
         <v>528</v>
@@ -24228,7 +24498,7 @@
       </c>
       <c r="G383" s="3">
         <f t="shared" si="5"/>
-        <v>-13.900000000000002</v>
+        <v>-13.8</v>
       </c>
       <c r="H383" s="4" t="s">
         <v>531</v>
@@ -24284,7 +24554,7 @@
       </c>
       <c r="G384" s="3">
         <f t="shared" si="5"/>
-        <v>-6.4999999999999991</v>
+        <v>-6.3999999999999995</v>
       </c>
       <c r="H384" s="4" t="s">
         <v>534</v>
@@ -24340,7 +24610,7 @@
       </c>
       <c r="G385" s="3">
         <f t="shared" si="5"/>
-        <v>-7.8000000000000007</v>
+        <v>-7.6999999999999993</v>
       </c>
       <c r="H385" s="4" t="s">
         <v>537</v>
@@ -24395,7 +24665,7 @@
       </c>
       <c r="G386" s="3">
         <f t="shared" si="5"/>
-        <v>-15.8</v>
+        <v>-15.7</v>
       </c>
       <c r="H386" s="4" t="s">
         <v>539</v>
@@ -24449,8 +24719,8 @@
         <v>-18.5</v>
       </c>
       <c r="G387" s="3">
-        <f t="shared" ref="G387:G436" si="6">E387+6.7+1.5</f>
-        <v>-15.5</v>
+        <f t="shared" ref="G387:G436" si="6">E387+6.8+1.5</f>
+        <v>-15.399999999999999</v>
       </c>
       <c r="H387" s="4" t="s">
         <v>541</v>
@@ -24505,7 +24775,7 @@
       </c>
       <c r="G388" s="3">
         <f t="shared" si="6"/>
-        <v>-12.900000000000002</v>
+        <v>-12.8</v>
       </c>
       <c r="H388" s="4" t="s">
         <v>543</v>
@@ -24560,7 +24830,7 @@
       </c>
       <c r="G389" s="3">
         <f t="shared" si="6"/>
-        <v>-2.1000000000000005</v>
+        <v>-2.0000000000000009</v>
       </c>
       <c r="H389" t="s">
         <v>544</v>
@@ -24616,7 +24886,7 @@
       </c>
       <c r="G390" s="3">
         <f t="shared" si="6"/>
-        <v>38.6</v>
+        <v>38.699999999999996</v>
       </c>
       <c r="H390" s="6" t="s">
         <v>546</v>
@@ -24672,7 +24942,7 @@
       </c>
       <c r="G391" s="3">
         <f t="shared" si="6"/>
-        <v>48.900000000000006</v>
+        <v>49</v>
       </c>
       <c r="H391" s="4" t="s">
         <v>549</v>
@@ -24728,7 +24998,7 @@
       </c>
       <c r="G392" s="3">
         <f t="shared" si="6"/>
-        <v>-13.600000000000001</v>
+        <v>-13.5</v>
       </c>
       <c r="H392" s="4" t="s">
         <v>552</v>
@@ -24783,7 +25053,7 @@
       </c>
       <c r="G393" s="3">
         <f t="shared" si="6"/>
-        <v>-9.5</v>
+        <v>-9.3999999999999986</v>
       </c>
       <c r="H393" s="4" t="s">
         <v>553</v>
@@ -24839,7 +25109,7 @@
       </c>
       <c r="G394" s="3">
         <f t="shared" si="6"/>
-        <v>40.700000000000003</v>
+        <v>40.799999999999997</v>
       </c>
       <c r="H394" s="4" t="s">
         <v>556</v>
@@ -24895,7 +25165,7 @@
       </c>
       <c r="G395" s="3">
         <f t="shared" si="6"/>
-        <v>-1.8999999999999995</v>
+        <v>-1.7999999999999998</v>
       </c>
       <c r="H395" t="s">
         <v>558</v>
@@ -24951,7 +25221,7 @@
       </c>
       <c r="G396" s="3">
         <f t="shared" si="6"/>
-        <v>-2.2000000000000002</v>
+        <v>-2.1000000000000005</v>
       </c>
       <c r="H396" s="4" t="s">
         <v>560</v>
@@ -25007,7 +25277,7 @@
       </c>
       <c r="G397" s="3">
         <f t="shared" si="6"/>
-        <v>-16.7</v>
+        <v>-16.599999999999998</v>
       </c>
       <c r="H397" s="4" t="s">
         <v>563</v>
@@ -25062,7 +25332,7 @@
       </c>
       <c r="G398" s="3">
         <f t="shared" si="6"/>
-        <v>64.400000000000006</v>
+        <v>64.5</v>
       </c>
       <c r="H398" t="s">
         <v>564</v>
@@ -25118,7 +25388,7 @@
       </c>
       <c r="G399" s="3">
         <f t="shared" si="6"/>
-        <v>-12.7</v>
+        <v>-12.599999999999998</v>
       </c>
       <c r="H399" s="4" t="s">
         <v>567</v>
@@ -25174,7 +25444,7 @@
       </c>
       <c r="G400" s="3">
         <f t="shared" si="6"/>
-        <v>31.8</v>
+        <v>31.900000000000002</v>
       </c>
       <c r="H400" s="4" t="s">
         <v>876</v>
@@ -25229,7 +25499,7 @@
       </c>
       <c r="G401" s="3">
         <f t="shared" si="6"/>
-        <v>-20.7</v>
+        <v>-20.599999999999998</v>
       </c>
       <c r="H401" s="4" t="s">
         <v>878</v>
@@ -25284,7 +25554,7 @@
       </c>
       <c r="G402" s="3">
         <f t="shared" si="6"/>
-        <v>-33.099999999999994</v>
+        <v>-33</v>
       </c>
       <c r="H402" s="4" t="s">
         <v>879</v>
@@ -25339,7 +25609,7 @@
       </c>
       <c r="G403" s="3">
         <f t="shared" si="6"/>
-        <v>-24.2</v>
+        <v>-24.099999999999998</v>
       </c>
       <c r="H403" s="4" t="s">
         <v>880</v>
@@ -25394,7 +25664,7 @@
       </c>
       <c r="G404" s="3">
         <f t="shared" si="6"/>
-        <v>43</v>
+        <v>43.099999999999994</v>
       </c>
       <c r="H404" s="4" t="s">
         <v>573</v>
@@ -25450,7 +25720,7 @@
       </c>
       <c r="G405" s="3">
         <f t="shared" si="6"/>
-        <v>3.3000000000000016</v>
+        <v>3.4000000000000012</v>
       </c>
       <c r="H405" s="4" t="s">
         <v>906</v>
@@ -25506,7 +25776,7 @@
       </c>
       <c r="G406" s="3">
         <f t="shared" si="6"/>
-        <v>8.0000000000000036</v>
+        <v>8.100000000000005</v>
       </c>
       <c r="H406" s="4" t="s">
         <v>903</v>
@@ -25562,7 +25832,7 @@
       </c>
       <c r="G407" s="3">
         <f t="shared" si="6"/>
-        <v>42.800000000000011</v>
+        <v>42.900000000000006</v>
       </c>
       <c r="H407" t="s">
         <v>576</v>
@@ -25618,7 +25888,7 @@
       </c>
       <c r="G408" s="3">
         <f t="shared" si="6"/>
-        <v>40.800000000000011</v>
+        <v>40.900000000000006</v>
       </c>
       <c r="H408" t="s">
         <v>577</v>
@@ -25674,7 +25944,7 @@
       </c>
       <c r="G409" s="3">
         <f t="shared" si="6"/>
-        <v>-3.9999999999999956</v>
+        <v>-3.8999999999999959</v>
       </c>
       <c r="H409" s="4" t="s">
         <v>905</v>
@@ -25730,7 +26000,7 @@
       </c>
       <c r="G410" s="3">
         <f t="shared" si="6"/>
-        <v>-15.8</v>
+        <v>-15.7</v>
       </c>
       <c r="H410" s="4" t="s">
         <v>899</v>
@@ -25786,7 +26056,7 @@
       </c>
       <c r="G411" s="3">
         <f t="shared" si="6"/>
-        <v>11.099999999999998</v>
+        <v>11.2</v>
       </c>
       <c r="H411" t="s">
         <v>580</v>
@@ -25842,7 +26112,7 @@
       </c>
       <c r="G412" s="3">
         <f t="shared" si="6"/>
-        <v>57.400000000000006</v>
+        <v>57.5</v>
       </c>
       <c r="H412" t="s">
         <v>581</v>
@@ -25898,7 +26168,7 @@
       </c>
       <c r="G413" s="3">
         <f t="shared" si="6"/>
-        <v>-35.700000000000003</v>
+        <v>-35.600000000000009</v>
       </c>
       <c r="H413" s="4" t="s">
         <v>907</v>
@@ -25954,7 +26224,7 @@
       </c>
       <c r="G414" s="3">
         <f t="shared" si="6"/>
-        <v>16.500000000000004</v>
+        <v>16.600000000000005</v>
       </c>
       <c r="H414" t="s">
         <v>583</v>
@@ -26010,7 +26280,7 @@
       </c>
       <c r="G415" s="3">
         <f t="shared" si="6"/>
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="H415" t="s">
         <v>584</v>
@@ -26065,7 +26335,7 @@
       </c>
       <c r="G416" s="3">
         <f t="shared" si="6"/>
-        <v>36.700000000000003</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="H416" t="s">
         <v>585</v>
@@ -26120,7 +26390,7 @@
       </c>
       <c r="G417" s="3">
         <f t="shared" si="6"/>
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="H417" t="s">
         <v>586</v>
@@ -26175,7 +26445,7 @@
       </c>
       <c r="G418" s="3">
         <f t="shared" si="6"/>
-        <v>4.9000000000000004</v>
+        <v>5</v>
       </c>
       <c r="H418" t="s">
         <v>587</v>
@@ -26230,7 +26500,7 @@
       </c>
       <c r="G419" s="3">
         <f t="shared" si="6"/>
-        <v>-12.400000000000002</v>
+        <v>-12.3</v>
       </c>
       <c r="H419" s="4" t="s">
         <v>932</v>
@@ -26285,7 +26555,7 @@
       </c>
       <c r="G420" s="3">
         <f t="shared" si="6"/>
-        <v>-2.4999999999999991</v>
+        <v>-2.3999999999999995</v>
       </c>
       <c r="H420" s="4" t="s">
         <v>963</v>
@@ -26340,7 +26610,7 @@
       </c>
       <c r="G421" s="3">
         <f t="shared" si="6"/>
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="H421" t="s">
         <v>590</v>
@@ -26395,7 +26665,7 @@
       </c>
       <c r="G422" s="3">
         <f t="shared" si="6"/>
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="H422" t="s">
         <v>591</v>
@@ -26450,7 +26720,7 @@
       </c>
       <c r="G423" s="3">
         <f t="shared" si="6"/>
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="H423" t="s">
         <v>592</v>
@@ -26502,7 +26772,7 @@
       </c>
       <c r="G424" s="3">
         <f t="shared" si="6"/>
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="H424" t="s">
         <v>593</v>
@@ -26557,7 +26827,7 @@
       </c>
       <c r="G425" s="3">
         <f t="shared" si="6"/>
-        <v>26.099999999999998</v>
+        <v>26.2</v>
       </c>
       <c r="H425" t="s">
         <v>594</v>
@@ -26612,7 +26882,7 @@
       </c>
       <c r="G426" s="3">
         <f t="shared" si="6"/>
-        <v>-36.199999999999996</v>
+        <v>-36.1</v>
       </c>
       <c r="H426" s="4" t="s">
         <v>596</v>
@@ -26667,7 +26937,7 @@
       </c>
       <c r="G427" s="3">
         <f t="shared" si="6"/>
-        <v>-31.4</v>
+        <v>-31.300000000000004</v>
       </c>
       <c r="H427" s="4" t="s">
         <v>598</v>
@@ -26722,7 +26992,7 @@
       </c>
       <c r="G428" s="3">
         <f t="shared" si="6"/>
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H428" s="4" t="s">
         <v>975</v>
@@ -26777,7 +27047,7 @@
       </c>
       <c r="G429" s="3">
         <f t="shared" si="6"/>
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="H429" t="s">
         <v>601</v>
@@ -26829,7 +27099,7 @@
       </c>
       <c r="G430" s="3">
         <f t="shared" si="6"/>
-        <v>0.79999999999999982</v>
+        <v>0.89999999999999947</v>
       </c>
       <c r="H430" s="4" t="s">
         <v>979</v>
@@ -26884,7 +27154,7 @@
       </c>
       <c r="G431" s="3">
         <f t="shared" si="6"/>
-        <v>59.6</v>
+        <v>59.699999999999996</v>
       </c>
       <c r="H431" t="s">
         <v>603</v>
@@ -26939,7 +27209,7 @@
       </c>
       <c r="G432" s="3">
         <f t="shared" si="6"/>
-        <v>-13.900000000000002</v>
+        <v>-13.8</v>
       </c>
       <c r="H432" s="4" t="s">
         <v>989</v>
@@ -26994,7 +27264,7 @@
       </c>
       <c r="G433" s="3">
         <f t="shared" si="6"/>
-        <v>-8.1999999999999993</v>
+        <v>-8.0999999999999979</v>
       </c>
       <c r="I433" t="s">
         <v>605</v>
@@ -27046,7 +27316,7 @@
       </c>
       <c r="G434" s="3">
         <f t="shared" si="6"/>
-        <v>-14.3</v>
+        <v>-14.2</v>
       </c>
       <c r="H434" s="4" t="s">
         <v>992</v>
@@ -27101,7 +27371,7 @@
       </c>
       <c r="G435" s="3">
         <f t="shared" si="6"/>
-        <v>-8</v>
+        <v>-7.8999999999999986</v>
       </c>
       <c r="H435" s="4" t="s">
         <v>993</v>
@@ -27156,7 +27426,13 @@
       </c>
       <c r="G436" s="3">
         <f t="shared" si="6"/>
-        <v>-38</v>
+        <v>-37.900000000000006</v>
+      </c>
+      <c r="H436" s="4" t="s">
+        <v>1029</v>
+      </c>
+      <c r="I436" s="4" t="s">
+        <v>1031</v>
       </c>
       <c r="K436" t="s">
         <v>678</v>
@@ -27177,7 +27453,7 @@
         <v>699</v>
       </c>
       <c r="T436" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/House Model Data.xlsx
+++ b/inputs/House Model Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Developer/house_model_python/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D7FFD67-6D83-DA46-A7A6-7D4224C1BC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D66EF3A-7FB4-6944-960A-906C4E3120A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5582" uniqueCount="1032">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5583" uniqueCount="1033">
   <si>
     <t>State</t>
   </si>
@@ -3169,6 +3169,9 @@
   </si>
   <si>
     <t>Gray, Chuck</t>
+  </si>
+  <si>
+    <t>Martin, James</t>
   </si>
 </sst>
 </file>
@@ -9531,6 +9534,9 @@
         <f t="shared" si="1"/>
         <v>-7.9000000000000021</v>
       </c>
+      <c r="H109" s="4" t="s">
+        <v>1032</v>
+      </c>
       <c r="I109" t="s">
         <v>118</v>
       </c>

--- a/inputs/House Model Data.xlsx
+++ b/inputs/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Developer/house_model_python/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82DB4E9C-645B-D24C-A8F0-DCA465173517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E699E1-3BE9-6C49-BB56-2DD85A88FA11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5596" uniqueCount="1041">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5597" uniqueCount="1043">
   <si>
     <t>State</t>
   </si>
@@ -3196,6 +3196,12 @@
   </si>
   <si>
     <t>Smith, Brad</t>
+  </si>
+  <si>
+    <t>R_vs_I</t>
+  </si>
+  <si>
+    <t>Meline, Spencer</t>
   </si>
 </sst>
 </file>
@@ -4070,7 +4076,7 @@
         <v>699</v>
       </c>
       <c r="T9" t="s">
-        <v>701</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.2">
@@ -26791,6 +26797,9 @@
       <c r="H423" t="s">
         <v>591</v>
       </c>
+      <c r="I423" s="4" t="s">
+        <v>1042</v>
+      </c>
       <c r="K423" t="s">
         <v>671</v>
       </c>
@@ -26813,7 +26822,7 @@
         <v>697</v>
       </c>
       <c r="T423" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="424" spans="1:20" x14ac:dyDescent="0.2">

--- a/inputs/House Model Data.xlsx
+++ b/inputs/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Developer/house_model_python/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E699E1-3BE9-6C49-BB56-2DD85A88FA11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{230E8CFD-42B6-5D4E-8581-8C96AAF9D0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5597" uniqueCount="1043">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5609" uniqueCount="1050">
   <si>
     <t>State</t>
   </si>
@@ -3202,6 +3202,27 @@
   </si>
   <si>
     <t>Meline, Spencer</t>
+  </si>
+  <si>
+    <t>Grossi, Gary</t>
+  </si>
+  <si>
+    <t>Stalcup, Thomas</t>
+  </si>
+  <si>
+    <t>Clark, Kathrine</t>
+  </si>
+  <si>
+    <t>Koh, Dan</t>
+  </si>
+  <si>
+    <t>Jones, Micah Quincey</t>
+  </si>
+  <si>
+    <t>Burke, Robert</t>
+  </si>
+  <si>
+    <t>Macallister, Tyler</t>
   </si>
 </sst>
 </file>
@@ -14074,6 +14095,9 @@
         <f t="shared" si="2"/>
         <v>31.900000000000002</v>
       </c>
+      <c r="H192" t="s">
+        <v>690</v>
+      </c>
       <c r="K192" t="s">
         <v>661</v>
       </c>
@@ -14096,7 +14120,7 @@
         <v>698</v>
       </c>
       <c r="T192" t="s">
-        <v>701</v>
+        <v>769</v>
       </c>
     </row>
     <row r="193" spans="1:20" x14ac:dyDescent="0.2">
@@ -14123,6 +14147,12 @@
         <f t="shared" si="2"/>
         <v>27.1</v>
       </c>
+      <c r="H193" t="s">
+        <v>252</v>
+      </c>
+      <c r="I193" s="4" t="s">
+        <v>1043</v>
+      </c>
       <c r="K193" t="s">
         <v>661</v>
       </c>
@@ -14145,7 +14175,7 @@
         <v>698</v>
       </c>
       <c r="T193" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="194" spans="1:20" x14ac:dyDescent="0.2">
@@ -14172,6 +14202,12 @@
         <f t="shared" si="2"/>
         <v>27.900000000000002</v>
       </c>
+      <c r="H194" t="s">
+        <v>253</v>
+      </c>
+      <c r="I194" s="4" t="s">
+        <v>1044</v>
+      </c>
       <c r="K194" t="s">
         <v>661</v>
       </c>
@@ -14194,7 +14230,7 @@
         <v>698</v>
       </c>
       <c r="T194" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="195" spans="1:20" x14ac:dyDescent="0.2">
@@ -14221,6 +14257,9 @@
         <f t="shared" ref="G195:G258" si="3">E195+6.8+1.5</f>
         <v>53.199999999999996</v>
       </c>
+      <c r="H195" t="s">
+        <v>1045</v>
+      </c>
       <c r="K195" t="s">
         <v>661</v>
       </c>
@@ -14243,7 +14282,7 @@
         <v>698</v>
       </c>
       <c r="T195" t="s">
-        <v>701</v>
+        <v>769</v>
       </c>
     </row>
     <row r="196" spans="1:20" x14ac:dyDescent="0.2">
@@ -14270,6 +14309,12 @@
         <f t="shared" si="3"/>
         <v>28.900000000000002</v>
       </c>
+      <c r="H196" s="4" t="s">
+        <v>1046</v>
+      </c>
+      <c r="I196" s="4" t="s">
+        <v>1047</v>
+      </c>
       <c r="K196" t="s">
         <v>661</v>
       </c>
@@ -14292,7 +14337,7 @@
         <v>698</v>
       </c>
       <c r="T196" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="197" spans="1:20" x14ac:dyDescent="0.2">
@@ -14319,6 +14364,9 @@
         <f t="shared" si="3"/>
         <v>71</v>
       </c>
+      <c r="H197" t="s">
+        <v>256</v>
+      </c>
       <c r="K197" t="s">
         <v>661</v>
       </c>
@@ -14341,7 +14389,7 @@
         <v>698</v>
       </c>
       <c r="T197" t="s">
-        <v>701</v>
+        <v>769</v>
       </c>
     </row>
     <row r="198" spans="1:20" x14ac:dyDescent="0.2">
@@ -14368,6 +14416,9 @@
         <f t="shared" si="3"/>
         <v>34.5</v>
       </c>
+      <c r="I198" s="4" t="s">
+        <v>1048</v>
+      </c>
       <c r="K198" t="s">
         <v>661</v>
       </c>
@@ -14416,6 +14467,12 @@
       <c r="G199" s="3">
         <f t="shared" si="3"/>
         <v>19</v>
+      </c>
+      <c r="H199" t="s">
+        <v>258</v>
+      </c>
+      <c r="I199" s="4" t="s">
+        <v>1049</v>
       </c>
       <c r="K199" t="s">
         <v>661</v>

--- a/inputs/House Model Data.xlsx
+++ b/inputs/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Developer/house_model_python/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{230E8CFD-42B6-5D4E-8581-8C96AAF9D0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5880301F-56C2-3A49-8CE7-516D7DD90714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5609" uniqueCount="1050">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5611" uniqueCount="1050">
   <si>
     <t>State</t>
   </si>
@@ -14046,6 +14046,9 @@
         <f t="shared" si="2"/>
         <v>22.1</v>
       </c>
+      <c r="H191" t="s">
+        <v>251</v>
+      </c>
       <c r="K191" t="s">
         <v>661</v>
       </c>
@@ -14068,7 +14071,7 @@
         <v>698</v>
       </c>
       <c r="T191" t="s">
-        <v>701</v>
+        <v>769</v>
       </c>
     </row>
     <row r="192" spans="1:20" x14ac:dyDescent="0.2">
@@ -14416,6 +14419,9 @@
         <f t="shared" si="3"/>
         <v>34.5</v>
       </c>
+      <c r="H198" t="s">
+        <v>257</v>
+      </c>
       <c r="I198" s="4" t="s">
         <v>1048</v>
       </c>
@@ -15889,15 +15895,16 @@
         <v>693</v>
       </c>
       <c r="E225" s="3">
-        <v>57.5</v>
+        <f>77.7-20.5</f>
+        <v>57.2</v>
       </c>
       <c r="F225" s="3">
-        <f>78.6-19.8</f>
-        <v>58.8</v>
+        <f>78.4-20</f>
+        <v>58.400000000000006</v>
       </c>
       <c r="G225" s="3">
         <f t="shared" si="3"/>
-        <v>65.8</v>
+        <v>65.5</v>
       </c>
       <c r="H225" s="6" t="s">
         <v>288</v>
@@ -15944,15 +15951,16 @@
         <v>692</v>
       </c>
       <c r="E226" s="3">
-        <v>-11.3</v>
+        <f>45.2-53.1</f>
+        <v>-7.8999999999999986</v>
       </c>
       <c r="F226" s="3">
-        <f>43.6-54.7</f>
-        <v>-11.100000000000001</v>
+        <f>45.3-53.1</f>
+        <v>-7.8000000000000043</v>
       </c>
       <c r="G226" s="3">
         <f t="shared" si="3"/>
-        <v>-3.0000000000000009</v>
+        <v>0.40000000000000124</v>
       </c>
       <c r="H226" s="4" t="s">
         <v>940</v>
@@ -15999,15 +16007,16 @@
         <v>692</v>
       </c>
       <c r="E227" s="3">
-        <v>-19.899999999999999</v>
+        <f>35.9-62.6</f>
+        <v>-26.700000000000003</v>
       </c>
       <c r="F227" s="3">
-        <f>39.8-58.2</f>
-        <v>-18.400000000000006</v>
+        <f>36-62.1</f>
+        <v>-26.1</v>
       </c>
       <c r="G227" s="3">
         <f t="shared" si="3"/>
-        <v>-11.599999999999998</v>
+        <v>-18.400000000000002</v>
       </c>
       <c r="H227" s="4" t="s">
         <v>918</v>
@@ -16054,15 +16063,16 @@
         <v>692</v>
       </c>
       <c r="E228" s="3">
-        <v>-21</v>
+        <f>28.3-70.4</f>
+        <v>-42.100000000000009</v>
       </c>
       <c r="F228" s="3">
-        <f>39.7-58.5</f>
-        <v>-18.799999999999997</v>
+        <f>29.2-68.8</f>
+        <v>-39.599999999999994</v>
       </c>
       <c r="G228" s="3">
         <f t="shared" si="3"/>
-        <v>-12.7</v>
+        <v>-33.800000000000011</v>
       </c>
       <c r="H228" s="4" t="s">
         <v>937</v>
@@ -16109,15 +16119,16 @@
         <v>693</v>
       </c>
       <c r="E229" s="3">
-        <v>-18.3</v>
+        <f>60.8-37.4</f>
+        <v>23.4</v>
       </c>
       <c r="F229" s="3">
-        <f>41.9-56.1</f>
-        <v>-14.200000000000003</v>
+        <f>62.2-35.8</f>
+        <v>26.400000000000006</v>
       </c>
       <c r="G229" s="3">
         <f t="shared" si="3"/>
-        <v>-10</v>
+        <v>31.7</v>
       </c>
       <c r="H229" t="s">
         <v>915</v>
@@ -16164,15 +16175,16 @@
         <v>692</v>
       </c>
       <c r="E230" s="3">
-        <v>-26.6</v>
+        <f>30-68.6</f>
+        <v>-38.599999999999994</v>
       </c>
       <c r="F230" s="3">
-        <f>36.7-61.5</f>
-        <v>-24.799999999999997</v>
+        <f>30.6-67.7</f>
+        <v>-37.1</v>
       </c>
       <c r="G230" s="3">
         <f t="shared" si="3"/>
-        <v>-18.3</v>
+        <v>-30.299999999999994</v>
       </c>
       <c r="H230" s="4" t="s">
         <v>923</v>
@@ -16219,6 +16231,7 @@
         <v>692</v>
       </c>
       <c r="E231" s="3">
+        <f>28.1-70.7</f>
         <v>-42.6</v>
       </c>
       <c r="F231" s="3">
@@ -16274,15 +16287,16 @@
         <v>692</v>
       </c>
       <c r="E232" s="3">
-        <v>-53.8</v>
+        <f>22.6-76.5</f>
+        <v>-53.9</v>
       </c>
       <c r="F232" s="3">
         <f>23.6-74.9</f>
         <v>-51.300000000000004</v>
       </c>
       <c r="G232" s="3">
-        <f t="shared" si="3"/>
-        <v>-45.5</v>
+        <f>E232+6.8+1.5</f>
+        <v>-45.6</v>
       </c>
       <c r="H232" s="4" t="s">
         <v>938</v>
